--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_winter_weekend.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_winter_weekend.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cleme\Documents\heig-vd\s5\ResoHT\mini_projet_trey\courbe de charge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E462AD7-80F3-4CD0-8880-ABFA2CBD2BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD56763D-7E48-4882-94D2-7EE0B7C09A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
@@ -634,76 +634,76 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>7903.5434178679898</v>
+        <v>7.90354341786799</v>
       </c>
       <c r="C3">
-        <v>2597.7690960442301</v>
+        <v>2.5977690960442299</v>
       </c>
       <c r="D3">
-        <v>11697.749122020999</v>
+        <v>11.697749122020999</v>
       </c>
       <c r="E3">
-        <v>3844.8642027783199</v>
+        <v>3.8448642027783202</v>
       </c>
       <c r="F3">
-        <v>1707.9849810103999</v>
+        <v>1.7079849810104</v>
       </c>
       <c r="G3">
-        <v>561.38751514234298</v>
+        <v>0.56138751514234297</v>
       </c>
       <c r="H3">
-        <v>5336.83547094188</v>
+        <v>5.3368354709418799</v>
       </c>
       <c r="I3">
-        <v>1754.1329912533399</v>
+        <v>1.7541329912533401</v>
       </c>
       <c r="J3">
-        <v>2374.75378757515</v>
+        <v>2.3747537875751501</v>
       </c>
       <c r="K3">
-        <v>780.54382368925405</v>
+        <v>0.78054382368925401</v>
       </c>
       <c r="L3">
-        <v>8542.4184018035994</v>
+        <v>8.5424184018035998</v>
       </c>
       <c r="M3">
-        <v>2807.7571484602699</v>
+        <v>2.8077571484602699</v>
       </c>
       <c r="N3">
-        <v>12023.2783707414</v>
+        <v>12.0232783707414</v>
       </c>
       <c r="O3">
-        <v>3951.86049260354</v>
+        <v>3.9518604926035401</v>
       </c>
       <c r="P3">
-        <v>7069.9402471609801</v>
+        <v>7.0699402471609796</v>
       </c>
       <c r="Q3">
-        <v>2323.7769838061399</v>
+        <v>2.3237769838061402</v>
       </c>
       <c r="R3">
-        <v>750.12445161290304</v>
+        <v>0.75012445161290298</v>
       </c>
       <c r="S3">
-        <v>246.55398415117199</v>
+        <v>0.246553984151172</v>
       </c>
       <c r="T3">
-        <v>4874.9706352705398</v>
+        <v>4.8749706352705404</v>
       </c>
       <c r="U3">
-        <v>1602.3253610271299</v>
+        <v>1.60232536102713</v>
       </c>
       <c r="V3">
-        <v>1831.7583870967701</v>
+        <v>1.83175838709677</v>
       </c>
       <c r="W3">
-        <v>602.06986636678096</v>
+        <v>0.60206986636678095</v>
       </c>
       <c r="X3">
-        <v>2089.12754032258</v>
+        <v>2.08912754032258</v>
       </c>
       <c r="Y3">
-        <v>686.66301619544595</v>
+        <v>0.68666301619544601</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -758,76 +758,76 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="B4">
-        <v>7474.1785694615</v>
+        <v>7.4741785694615004</v>
       </c>
       <c r="C4">
-        <v>2456.6436950504899</v>
+        <v>2.4566436950504902</v>
       </c>
       <c r="D4">
-        <v>11132.8272530389</v>
+        <v>11.132827253038901</v>
       </c>
       <c r="E4">
-        <v>3659.1833637759701</v>
+        <v>3.6591833637759699</v>
       </c>
       <c r="F4">
-        <v>1662.9796923685999</v>
+        <v>1.6629796923686</v>
       </c>
       <c r="G4">
-        <v>546.59499211679702</v>
+        <v>0.54659499211679696</v>
       </c>
       <c r="H4">
-        <v>5033.4146292585101</v>
+        <v>5.0334146292585098</v>
       </c>
       <c r="I4">
-        <v>1654.4033834120301</v>
+        <v>1.65440338341203</v>
       </c>
       <c r="J4">
-        <v>2239.7393587174302</v>
+        <v>2.2397393587174301</v>
       </c>
       <c r="K4">
-        <v>736.16672695392003</v>
+        <v>0.73616672695392005</v>
       </c>
       <c r="L4">
-        <v>8056.7471092184296</v>
+        <v>8.0567471092184295</v>
       </c>
       <c r="M4">
-        <v>2648.1247142458501</v>
+        <v>2.6481247142458502</v>
       </c>
       <c r="N4">
-        <v>11339.706006012</v>
+        <v>11.339706006011999</v>
       </c>
       <c r="O4">
-        <v>3727.1811215774401</v>
+        <v>3.72718112157744</v>
       </c>
       <c r="P4">
-        <v>6667.9853373413398</v>
+        <v>6.6679853373413396</v>
       </c>
       <c r="Q4">
-        <v>2191.6607939498199</v>
+        <v>2.1916607939498198</v>
       </c>
       <c r="R4">
-        <v>740.99051612903202</v>
+        <v>0.740990516129032</v>
       </c>
       <c r="S4">
-        <v>243.551804739895</v>
+        <v>0.24355180473989499</v>
       </c>
       <c r="T4">
-        <v>4597.8086913827601</v>
+        <v>4.5978086913827596</v>
       </c>
       <c r="U4">
-        <v>1511.2266355107399</v>
+        <v>1.51122663551074</v>
       </c>
       <c r="V4">
-        <v>1809.4538709677399</v>
+        <v>1.8094538709677399</v>
       </c>
       <c r="W4">
-        <v>594.73872644146195</v>
+        <v>0.59473872644146197</v>
       </c>
       <c r="X4">
-        <v>2063.6891532258001</v>
+        <v>2.0636891532258002</v>
       </c>
       <c r="Y4">
-        <v>678.30182269534998</v>
+        <v>0.67830182269535</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -882,76 +882,76 @@
         <v>2.0833333333333301E-2</v>
       </c>
       <c r="B5">
-        <v>7076.4789797659796</v>
+        <v>7.0764789797659802</v>
       </c>
       <c r="C5">
-        <v>2325.9261612814098</v>
+        <v>2.3259261612814099</v>
       </c>
       <c r="D5">
-        <v>10621.5562144493</v>
+        <v>10.621556214449299</v>
       </c>
       <c r="E5">
-        <v>3491.1366999532702</v>
+        <v>3.49113669995327</v>
       </c>
       <c r="F5">
-        <v>1628.9029095287301</v>
+        <v>1.62890290952873</v>
       </c>
       <c r="G5">
-        <v>535.394495241698</v>
+        <v>0.53539449524169802</v>
       </c>
       <c r="H5">
-        <v>4750.22184368737</v>
+        <v>4.7502218436873704</v>
       </c>
       <c r="I5">
-        <v>1561.3224160934701</v>
+        <v>1.56132241609347</v>
       </c>
       <c r="J5">
-        <v>2113.7258917835602</v>
+        <v>2.11372589178356</v>
       </c>
       <c r="K5">
-        <v>694.74810333427604</v>
+        <v>0.69474810333427595</v>
       </c>
       <c r="L5">
-        <v>7603.4539028056097</v>
+        <v>7.6034539028056098</v>
       </c>
       <c r="M5">
-        <v>2499.1344423123901</v>
+        <v>2.49913444231239</v>
       </c>
       <c r="N5">
-        <v>10701.7051322645</v>
+        <v>10.7017051322645</v>
       </c>
       <c r="O5">
-        <v>3517.48037528641</v>
+        <v>3.5174803752864099</v>
       </c>
       <c r="P5">
-        <v>6292.8274215096799</v>
+        <v>6.2928274215096804</v>
       </c>
       <c r="Q5">
-        <v>2068.3523500839201</v>
+        <v>2.06835235008392</v>
       </c>
       <c r="R5">
-        <v>737.56529032258004</v>
+        <v>0.73756529032258</v>
       </c>
       <c r="S5">
-        <v>242.425987460665</v>
+        <v>0.24242598746066499</v>
       </c>
       <c r="T5">
-        <v>4339.1242104208404</v>
+        <v>4.3391242104208398</v>
       </c>
       <c r="U5">
-        <v>1426.2011583621099</v>
+        <v>1.4262011583621099</v>
       </c>
       <c r="V5">
-        <v>1801.08967741935</v>
+        <v>1.8010896774193501</v>
       </c>
       <c r="W5">
-        <v>591.98954896946702</v>
+        <v>0.59198954896946698</v>
       </c>
       <c r="X5">
-        <v>2054.14975806451</v>
+        <v>2.0541497580645101</v>
       </c>
       <c r="Y5">
-        <v>675.16637513281296</v>
+        <v>0.67516637513281297</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -1006,76 +1006,76 @@
         <v>3.125E-2</v>
       </c>
       <c r="B6">
-        <v>6674.0691856616404</v>
+        <v>6.6740691856616401</v>
       </c>
       <c r="C6">
-        <v>2193.6604581910201</v>
+        <v>2.1936604581910202</v>
       </c>
       <c r="D6">
-        <v>10101.0873526098</v>
+        <v>10.101087352609801</v>
       </c>
       <c r="E6">
-        <v>3320.0668578261002</v>
+        <v>3.3200668578261001</v>
       </c>
       <c r="F6">
-        <v>1594.4838421197201</v>
+        <v>1.5944838421197201</v>
       </c>
       <c r="G6">
-        <v>524.08149486927596</v>
+        <v>0.52408149486927602</v>
       </c>
       <c r="H6">
-        <v>4463.6577154308598</v>
+        <v>4.4636577154308599</v>
       </c>
       <c r="I6">
-        <v>1467.1333420211199</v>
+        <v>1.4671333420211199</v>
       </c>
       <c r="J6">
-        <v>1986.2122645290499</v>
+        <v>1.9862122645290501</v>
       </c>
       <c r="K6">
-        <v>652.83640086201603</v>
+        <v>0.652836400862016</v>
       </c>
       <c r="L6">
-        <v>7144.7643486973902</v>
+        <v>7.1447643486973904</v>
       </c>
       <c r="M6">
-        <v>2348.37047666544</v>
+        <v>2.3483704766654401</v>
       </c>
       <c r="N6">
-        <v>10056.10901002</v>
+        <v>10.05610901002</v>
       </c>
       <c r="O6">
-        <v>3305.28319153953</v>
+        <v>3.30528319153954</v>
       </c>
       <c r="P6">
-        <v>5913.2033400133496</v>
+        <v>5.9132033400133501</v>
       </c>
       <c r="Q6">
-        <v>1943.57594855295</v>
+        <v>1.94357594855295</v>
       </c>
       <c r="R6">
-        <v>734.14006451612897</v>
+        <v>0.73414006451612901</v>
       </c>
       <c r="S6">
-        <v>241.30017018143599</v>
+        <v>0.24130017018143601</v>
       </c>
       <c r="T6">
-        <v>4077.3601523046</v>
+        <v>4.0773601523045997</v>
       </c>
       <c r="U6">
-        <v>1340.1634731521899</v>
+        <v>1.3401634731521901</v>
       </c>
       <c r="V6">
-        <v>1792.72548387096</v>
+        <v>1.7927254838709601</v>
       </c>
       <c r="W6">
-        <v>589.24037149747301</v>
+        <v>0.58924037149747299</v>
       </c>
       <c r="X6">
-        <v>2044.61036290322</v>
+        <v>2.04461036290322</v>
       </c>
       <c r="Y6">
-        <v>672.03092757027696</v>
+        <v>0.67203092757027705</v>
       </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -1130,76 +1130,76 @@
         <v>4.1666666666666699E-2</v>
       </c>
       <c r="B7">
-        <v>6221.8341216626804</v>
+        <v>6.2218341216626802</v>
       </c>
       <c r="C7">
-        <v>2045.01798085001</v>
+        <v>2.0450179808500102</v>
       </c>
       <c r="D7">
-        <v>9500.5095419587396</v>
+        <v>9.5005095419587402</v>
       </c>
       <c r="E7">
-        <v>3122.6664775419599</v>
+        <v>3.1226664775419599</v>
       </c>
       <c r="F7">
-        <v>1549.5420903096499</v>
+        <v>1.54954209030965</v>
       </c>
       <c r="G7">
-        <v>509.309855390412</v>
+        <v>0.50930985539041196</v>
       </c>
       <c r="H7">
-        <v>4143.3801603206402</v>
+        <v>4.1433801603206399</v>
       </c>
       <c r="I7">
-        <v>1361.8632004108399</v>
+        <v>1.36186320041084</v>
       </c>
       <c r="J7">
-        <v>1843.6970340681301</v>
+        <v>1.84369703406813</v>
       </c>
       <c r="K7">
-        <v>605.99390986360902</v>
+        <v>0.60599390986360901</v>
       </c>
       <c r="L7">
-        <v>6632.1113176352701</v>
+        <v>6.6321113176352702</v>
       </c>
       <c r="M7">
-        <v>2179.86957388356</v>
+        <v>2.1798695738835598</v>
       </c>
       <c r="N7">
-        <v>9334.5604028056096</v>
+        <v>9.3345604028056108</v>
       </c>
       <c r="O7">
-        <v>3068.1216332342101</v>
+        <v>3.0681216332342101</v>
       </c>
       <c r="P7">
-        <v>5488.9176018704002</v>
+        <v>5.4889176018703996</v>
       </c>
       <c r="Q7">
-        <v>1804.11997037128</v>
+        <v>1.80411997037128</v>
       </c>
       <c r="R7">
-        <v>726.14787096774205</v>
+        <v>0.72614787096774203</v>
       </c>
       <c r="S7">
-        <v>238.673263196568</v>
+        <v>0.23867326319656801</v>
       </c>
       <c r="T7">
-        <v>3784.8003226452902</v>
+        <v>3.7848003226452902</v>
       </c>
       <c r="U7">
-        <v>1244.0037073293299</v>
+        <v>1.24400370732933</v>
       </c>
       <c r="V7">
-        <v>1773.20903225806</v>
+        <v>1.77320903225806</v>
       </c>
       <c r="W7">
-        <v>582.82562406281897</v>
+        <v>0.58282562406281901</v>
       </c>
       <c r="X7">
-        <v>2022.35177419354</v>
+        <v>2.02235177419354</v>
       </c>
       <c r="Y7">
-        <v>664.71488325769201</v>
+        <v>0.66471488325769201</v>
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
@@ -1254,76 +1254,76 @@
         <v>5.2083333333333301E-2</v>
       </c>
       <c r="B8">
-        <v>5759.1574391686599</v>
+        <v>5.7591574391686597</v>
       </c>
       <c r="C8">
-        <v>1892.9435094773401</v>
+        <v>1.8929435094773399</v>
       </c>
       <c r="D8">
-        <v>8870.5662077212492</v>
+        <v>8.8705662077212502</v>
       </c>
       <c r="E8">
-        <v>2915.6141164147198</v>
+        <v>2.9156141164147198</v>
       </c>
       <c r="F8">
-        <v>1501.2533298451699</v>
+        <v>1.50125332984517</v>
       </c>
       <c r="G8">
-        <v>493.438107366949</v>
+        <v>0.49343810736694899</v>
       </c>
       <c r="H8">
-        <v>3816.3599198396801</v>
+        <v>3.8163599198396798</v>
       </c>
       <c r="I8">
-        <v>1254.3768452929801</v>
+        <v>1.25437684529298</v>
       </c>
       <c r="J8">
-        <v>1698.1814829659299</v>
+        <v>1.6981814829659301</v>
       </c>
       <c r="K8">
-        <v>558.16526115997203</v>
+        <v>0.558165261159972</v>
       </c>
       <c r="L8">
-        <v>6108.66559118236</v>
+        <v>6.1086655911823602</v>
       </c>
       <c r="M8">
-        <v>2007.82128367468</v>
+        <v>2.00782128367468</v>
       </c>
       <c r="N8">
-        <v>8597.8212985971895</v>
+        <v>8.5978212985971894</v>
       </c>
       <c r="O8">
-        <v>2825.96720001719</v>
+        <v>2.8259672000171898</v>
       </c>
       <c r="P8">
-        <v>5055.69953239813</v>
+        <v>5.0556995323981297</v>
       </c>
       <c r="Q8">
-        <v>1661.7280768594701</v>
+        <v>1.66172807685947</v>
       </c>
       <c r="R8">
-        <v>716.44306451612897</v>
+        <v>0.71644306451612905</v>
       </c>
       <c r="S8">
-        <v>235.48344757208599</v>
+        <v>0.235483447572086</v>
       </c>
       <c r="T8">
-        <v>3486.0813386773498</v>
+        <v>3.4860813386773501</v>
       </c>
       <c r="U8">
-        <v>1145.8195253838901</v>
+        <v>1.1458195253838901</v>
       </c>
       <c r="V8">
-        <v>1749.5104838709599</v>
+        <v>1.7495104838709601</v>
       </c>
       <c r="W8">
-        <v>575.03628789216805</v>
+        <v>0.57503628789216799</v>
       </c>
       <c r="X8">
-        <v>1995.32348790322</v>
+        <v>1.99532348790322</v>
       </c>
       <c r="Y8">
-        <v>655.83111516383894</v>
+        <v>0.65583111516383996</v>
       </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
@@ -1378,76 +1378,76 @@
         <v>6.25E-2</v>
       </c>
       <c r="B9">
-        <v>5323.7207734501199</v>
+        <v>5.3237207734501197</v>
       </c>
       <c r="C9">
-        <v>1749.8223986435701</v>
+        <v>1.7498223986435699</v>
       </c>
       <c r="D9">
-        <v>8266.5697023368393</v>
+        <v>8.2665697023368399</v>
       </c>
       <c r="E9">
-        <v>2717.09006551128</v>
+        <v>2.7170900655112802</v>
       </c>
       <c r="F9">
-        <v>1452.35583727939</v>
+        <v>1.4523558372793901</v>
       </c>
       <c r="G9">
-        <v>477.36627877747702</v>
+        <v>0.477366278777477</v>
       </c>
       <c r="H9">
-        <v>3509.5677354709401</v>
+        <v>3.5095677354709398</v>
       </c>
       <c r="I9">
-        <v>1153.53913069787</v>
+        <v>1.15353913069787</v>
       </c>
       <c r="J9">
-        <v>1561.66689378757</v>
+        <v>1.56166689378757</v>
       </c>
       <c r="K9">
-        <v>513.29508557202303</v>
+        <v>0.51329508557202297</v>
       </c>
       <c r="L9">
-        <v>5617.5979509017998</v>
+        <v>5.6175979509017999</v>
       </c>
       <c r="M9">
-        <v>1846.4151557467701</v>
+        <v>1.8464151557467701</v>
       </c>
       <c r="N9">
-        <v>7906.6536853707403</v>
+        <v>7.9066536853707401</v>
       </c>
       <c r="O9">
-        <v>2598.7913915352401</v>
+        <v>2.5987913915352401</v>
       </c>
       <c r="P9">
-        <v>4649.2784569138203</v>
+        <v>4.6492784569138204</v>
       </c>
       <c r="Q9">
-        <v>1528.1439293380799</v>
+        <v>1.5281439293380801</v>
       </c>
       <c r="R9">
-        <v>705.02564516128996</v>
+        <v>0.70502564516128996</v>
       </c>
       <c r="S9">
-        <v>231.730723307989</v>
+        <v>0.23173072330798899</v>
       </c>
       <c r="T9">
-        <v>3205.8398176352698</v>
+        <v>3.2058398176352698</v>
       </c>
       <c r="U9">
-        <v>1053.7085918062101</v>
+        <v>1.0537085918062099</v>
       </c>
       <c r="V9">
-        <v>1721.6298387096699</v>
+        <v>1.72162983870967</v>
       </c>
       <c r="W9">
-        <v>565.87236298552</v>
+        <v>0.56587236298552002</v>
       </c>
       <c r="X9">
-        <v>1963.52550403225</v>
+        <v>1.9635255040322499</v>
       </c>
       <c r="Y9">
-        <v>645.37962328871799</v>
+        <v>0.64537962328871801</v>
       </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -1502,76 +1502,76 @@
         <v>7.2916666666666699E-2</v>
       </c>
       <c r="B10">
-        <v>4958.9371738638501</v>
+        <v>4.9589371738638501</v>
       </c>
       <c r="C10">
-        <v>1629.9238276296401</v>
+        <v>1.6299238276296399</v>
       </c>
       <c r="D10">
-        <v>7752.5777605460999</v>
+        <v>7.7525777605461004</v>
       </c>
       <c r="E10">
-        <v>2548.1490840546498</v>
+        <v>2.5481490840546499</v>
       </c>
       <c r="F10">
-        <v>1408.59261325069</v>
+        <v>1.4085926132506901</v>
       </c>
       <c r="G10">
-        <v>462.98200264786101</v>
+        <v>0.46298200264786099</v>
       </c>
       <c r="H10">
-        <v>3253.3456913827599</v>
+        <v>3.2533456913827599</v>
       </c>
       <c r="I10">
-        <v>1069.32301740965</v>
+        <v>1.06932301740965</v>
       </c>
       <c r="J10">
-        <v>1447.65470941883</v>
+        <v>1.4476547094188299</v>
       </c>
       <c r="K10">
-        <v>475.82109277329698</v>
+        <v>0.47582109277329698</v>
       </c>
       <c r="L10">
-        <v>5207.4755260520997</v>
+        <v>5.2074755260521002</v>
       </c>
       <c r="M10">
-        <v>1711.61443352126</v>
+        <v>1.71161443352126</v>
       </c>
       <c r="N10">
-        <v>7329.4147995991898</v>
+        <v>7.3294147995991903</v>
       </c>
       <c r="O10">
-        <v>2409.0621448909701</v>
+        <v>2.4090621448909699</v>
       </c>
       <c r="P10">
-        <v>4309.8498663994596</v>
+        <v>4.3098498663994604</v>
       </c>
       <c r="Q10">
-        <v>1416.57914679275</v>
+        <v>1.41657914679275</v>
       </c>
       <c r="R10">
-        <v>693.60822580645095</v>
+        <v>0.69360822580645098</v>
       </c>
       <c r="S10">
-        <v>227.977999043892</v>
+        <v>0.22797799904389199</v>
       </c>
       <c r="T10">
-        <v>2971.7919539078098</v>
+        <v>2.9717919539078101</v>
       </c>
       <c r="U10">
-        <v>976.78077914793505</v>
+        <v>0.97678077914793504</v>
       </c>
       <c r="V10">
-        <v>1693.7491935483799</v>
+        <v>1.6937491935483799</v>
       </c>
       <c r="W10">
-        <v>556.70843807887195</v>
+        <v>0.55670843807887205</v>
       </c>
       <c r="X10">
-        <v>1931.7275201612899</v>
+        <v>1.93172752016129</v>
       </c>
       <c r="Y10">
-        <v>634.92813141359795</v>
+        <v>0.63492813141359805</v>
       </c>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
@@ -1626,76 +1626,76 @@
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="B11">
-        <v>4703.8498885836198</v>
+        <v>4.70384988858362</v>
       </c>
       <c r="C11">
-        <v>1546.0806915247999</v>
+        <v>1.5460806915248</v>
       </c>
       <c r="D11">
-        <v>7378.0826614253101</v>
+        <v>7.3780826614253101</v>
       </c>
       <c r="E11">
-        <v>2425.0584975062602</v>
+        <v>2.4250584975062601</v>
       </c>
       <c r="F11">
-        <v>1376.25185366701</v>
+        <v>1.3762518536670101</v>
       </c>
       <c r="G11">
-        <v>452.352109023293</v>
+        <v>0.45235210902329298</v>
       </c>
       <c r="H11">
-        <v>3074.66452905811</v>
+        <v>3.0746645290581101</v>
       </c>
       <c r="I11">
-        <v>1010.59335945865</v>
+        <v>1.01059335945865</v>
       </c>
       <c r="J11">
-        <v>1368.1462124248401</v>
+        <v>1.36814621242484</v>
       </c>
       <c r="K11">
-        <v>449.68791358471202</v>
+        <v>0.449687913584712</v>
       </c>
       <c r="L11">
-        <v>4921.4690981963904</v>
+        <v>4.9214690981963898</v>
       </c>
       <c r="M11">
-        <v>1617.6086667060999</v>
+        <v>1.6176086667061</v>
       </c>
       <c r="N11">
-        <v>6926.8666292585103</v>
+        <v>6.9268666292585097</v>
       </c>
       <c r="O11">
-        <v>2276.75095973116</v>
+        <v>2.2767509597311602</v>
       </c>
       <c r="P11">
-        <v>4073.1430861723402</v>
+        <v>4.0731430861723403</v>
       </c>
       <c r="Q11">
-        <v>1338.7773905440299</v>
+        <v>1.3387773905440301</v>
       </c>
       <c r="R11">
-        <v>684.47429032258003</v>
+        <v>0.68447429032258</v>
       </c>
       <c r="S11">
-        <v>224.97581963261399</v>
+        <v>0.22497581963261401</v>
       </c>
       <c r="T11">
-        <v>2808.5743647294498</v>
+        <v>2.8085743647294499</v>
       </c>
       <c r="U11">
-        <v>923.13375189939597</v>
+        <v>0.92313375189939595</v>
       </c>
       <c r="V11">
-        <v>1671.44467741935</v>
+        <v>1.6714446774193501</v>
       </c>
       <c r="W11">
-        <v>549.37729815355397</v>
+        <v>0.54937729815355396</v>
       </c>
       <c r="X11">
-        <v>1906.28913306451</v>
+        <v>1.90628913306451</v>
       </c>
       <c r="Y11">
-        <v>626.56693791350096</v>
+        <v>0.62656693791350104</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -1750,76 +1750,76 @@
         <v>9.375E-2</v>
       </c>
       <c r="B12">
-        <v>4539.2776967483296</v>
+        <v>4.5392776967483304</v>
       </c>
       <c r="C12">
-        <v>1491.9884279140899</v>
+        <v>1.49198842791409</v>
       </c>
       <c r="D12">
-        <v>7122.1727052304404</v>
+        <v>7.1221727052304402</v>
       </c>
       <c r="E12">
-        <v>2340.9449625479901</v>
+        <v>2.3409449625479901</v>
       </c>
       <c r="F12">
-        <v>1353.0769404130799</v>
+        <v>1.35307694041308</v>
       </c>
       <c r="G12">
-        <v>444.73488339782801</v>
+        <v>0.44473488339782802</v>
       </c>
       <c r="H12">
-        <v>2960.0388777555099</v>
+        <v>2.96003887775551</v>
       </c>
       <c r="I12">
-        <v>972.917729829716</v>
+        <v>0.97291772982971603</v>
       </c>
       <c r="J12">
-        <v>1317.1407615230401</v>
+        <v>1.3171407615230399</v>
       </c>
       <c r="K12">
-        <v>432.92323259580797</v>
+        <v>0.43292323259580801</v>
       </c>
       <c r="L12">
-        <v>4737.9932765531003</v>
+        <v>4.7379932765530999</v>
       </c>
       <c r="M12">
-        <v>1557.3030804473201</v>
+        <v>1.55730308044732</v>
       </c>
       <c r="N12">
-        <v>6668.6281803607199</v>
+        <v>6.6686281803607201</v>
       </c>
       <c r="O12">
-        <v>2191.8720862324099</v>
+        <v>2.1918720862324101</v>
       </c>
       <c r="P12">
-        <v>3921.29345357381</v>
+        <v>3.92129345357381</v>
       </c>
       <c r="Q12">
-        <v>1288.86682993164</v>
+        <v>1.2888668299316399</v>
       </c>
       <c r="R12">
-        <v>677.05296774193505</v>
+        <v>0.67705296774193502</v>
       </c>
       <c r="S12">
-        <v>222.536548860951</v>
+        <v>0.22253654886095101</v>
       </c>
       <c r="T12">
-        <v>2703.8687414829601</v>
+        <v>2.7038687414829599</v>
       </c>
       <c r="U12">
-        <v>888.71867781542699</v>
+        <v>0.88871867781542702</v>
       </c>
       <c r="V12">
-        <v>1653.3222580645099</v>
+        <v>1.6533222580645099</v>
       </c>
       <c r="W12">
-        <v>543.42074696423197</v>
+        <v>0.54342074696423204</v>
       </c>
       <c r="X12">
-        <v>1885.6204435483801</v>
+        <v>1.8856204435483801</v>
       </c>
       <c r="Y12">
-        <v>619.77346819467198</v>
+        <v>0.61977346819467205</v>
       </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -1874,76 +1874,76 @@
         <v>0.104166666666667</v>
       </c>
       <c r="B13">
-        <v>4432.2491674962803</v>
+        <v>4.4322491674962796</v>
       </c>
       <c r="C13">
-        <v>1456.80985154827</v>
+        <v>1.4568098515482699</v>
       </c>
       <c r="D13">
-        <v>6947.0557284331499</v>
+        <v>6.94705572843315</v>
       </c>
       <c r="E13">
-        <v>2283.3867957277398</v>
+        <v>2.2833867957277398</v>
       </c>
       <c r="F13">
-        <v>1336.6718815049401</v>
+        <v>1.3366718815049401</v>
       </c>
       <c r="G13">
-        <v>439.34280129019999</v>
+        <v>0.43934280129019998</v>
       </c>
       <c r="H13">
-        <v>2885.8693386773498</v>
+        <v>2.8858693386773502</v>
       </c>
       <c r="I13">
-        <v>948.53938124628303</v>
+        <v>0.94853938124628401</v>
       </c>
       <c r="J13">
-        <v>1284.13723446893</v>
+        <v>1.2841372344689299</v>
       </c>
       <c r="K13">
-        <v>422.07549783828199</v>
+        <v>0.42207549783828202</v>
       </c>
       <c r="L13">
-        <v>4619.2736272544998</v>
+        <v>4.6192736272544996</v>
       </c>
       <c r="M13">
-        <v>1518.2818187504599</v>
+        <v>1.5182818187504601</v>
       </c>
       <c r="N13">
-        <v>6501.53271342685</v>
+        <v>6.5015327134268501</v>
       </c>
       <c r="O13">
-        <v>2136.9504622038098</v>
+        <v>2.13695046220381</v>
       </c>
       <c r="P13">
-        <v>3823.0378089512301</v>
+        <v>3.8230378089512298</v>
       </c>
       <c r="Q13">
-        <v>1256.57176130009</v>
+        <v>1.25657176130009</v>
       </c>
       <c r="R13">
-        <v>671.344258064516</v>
+        <v>0.67134425806451603</v>
       </c>
       <c r="S13">
-        <v>220.660186728903</v>
+        <v>0.220660186728903</v>
       </c>
       <c r="T13">
-        <v>2636.1180440881699</v>
+        <v>2.6361180440881702</v>
       </c>
       <c r="U13">
-        <v>866.45010046697701</v>
+        <v>0.86645010046697701</v>
       </c>
       <c r="V13">
-        <v>1639.3819354838699</v>
+        <v>1.6393819354838699</v>
       </c>
       <c r="W13">
-        <v>538.838784510908</v>
+        <v>0.53883878451090805</v>
       </c>
       <c r="X13">
-        <v>1869.7214516129</v>
+        <v>1.8697214516128999</v>
       </c>
       <c r="Y13">
-        <v>614.54772225711201</v>
+        <v>0.61454772225711196</v>
       </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
@@ -1998,76 +1998,76 @@
         <v>0.114583333333333</v>
       </c>
       <c r="B14">
-        <v>4359.2132787833698</v>
+        <v>4.3592132787833702</v>
       </c>
       <c r="C14">
-        <v>1432.80411582073</v>
+        <v>1.4328041158207301</v>
       </c>
       <c r="D14">
-        <v>6820.79018538115</v>
+        <v>6.8207901853811501</v>
       </c>
       <c r="E14">
-        <v>2241.8853186947699</v>
+        <v>2.24188531869477</v>
       </c>
       <c r="F14">
-        <v>1325.3252540968999</v>
+        <v>1.3253252540969001</v>
       </c>
       <c r="G14">
-        <v>435.61334521379001</v>
+        <v>0.43561334521379003</v>
       </c>
       <c r="H14">
-        <v>2835.29919839679</v>
+        <v>2.8352991983967901</v>
       </c>
       <c r="I14">
-        <v>931.91777993939797</v>
+        <v>0.93191777993939795</v>
       </c>
       <c r="J14">
-        <v>1261.6348296593101</v>
+        <v>1.2616348296593101</v>
       </c>
       <c r="K14">
-        <v>414.67931504905999</v>
+        <v>0.41467931504906003</v>
       </c>
       <c r="L14">
-        <v>4538.3284118236397</v>
+        <v>4.53832841182364</v>
       </c>
       <c r="M14">
-        <v>1491.6764130480601</v>
+        <v>1.49167641304806</v>
       </c>
       <c r="N14">
-        <v>6387.6039859719403</v>
+        <v>6.38760398597194</v>
       </c>
       <c r="O14">
-        <v>2099.50390036612</v>
+        <v>2.0995039003661198</v>
       </c>
       <c r="P14">
-        <v>3756.04532398129</v>
+        <v>3.7560453239812901</v>
       </c>
       <c r="Q14">
-        <v>1234.55239632404</v>
+        <v>1.2345523963240399</v>
       </c>
       <c r="R14">
-        <v>667.34816129032197</v>
+        <v>0.66734816129032204</v>
       </c>
       <c r="S14">
-        <v>219.34673323646899</v>
+        <v>0.219346733236469</v>
       </c>
       <c r="T14">
-        <v>2589.9243867735399</v>
+        <v>2.5899243867735402</v>
       </c>
       <c r="U14">
-        <v>851.26697954757901</v>
+        <v>0.85126697954757902</v>
       </c>
       <c r="V14">
-        <v>1629.62370967741</v>
+        <v>1.62962370967741</v>
       </c>
       <c r="W14">
-        <v>535.63141079358195</v>
+        <v>0.53563141079358201</v>
       </c>
       <c r="X14">
-        <v>1858.5921572580601</v>
+        <v>1.8585921572580599</v>
       </c>
       <c r="Y14">
-        <v>610.88970010081903</v>
+        <v>0.610889700100819</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
@@ -2122,76 +2122,76 @@
         <v>0.125</v>
       </c>
       <c r="B15">
-        <v>4291.2279977050803</v>
+        <v>4.2912279977050796</v>
       </c>
       <c r="C15">
-        <v>1410.4584345441799</v>
+        <v>1.41045843454418</v>
       </c>
       <c r="D15">
-        <v>6710.8662946548702</v>
+        <v>6.7108662946548696</v>
       </c>
       <c r="E15">
-        <v>2205.7550830336299</v>
+        <v>2.2057550830336301</v>
       </c>
       <c r="F15">
-        <v>1315.2083910967001</v>
+        <v>1.3152083910967001</v>
       </c>
       <c r="G15">
-        <v>432.28809315135402</v>
+        <v>0.43228809315135402</v>
       </c>
       <c r="H15">
-        <v>2788.1004008015998</v>
+        <v>2.7881004008015999</v>
       </c>
       <c r="I15">
-        <v>916.40428538630397</v>
+        <v>0.91640428538630403</v>
       </c>
       <c r="J15">
-        <v>1240.63258517034</v>
+        <v>1.2406325851703399</v>
       </c>
       <c r="K15">
-        <v>407.77621111245298</v>
+        <v>0.40777621111245299</v>
       </c>
       <c r="L15">
-        <v>4462.77954408817</v>
+        <v>4.4627795440881703</v>
       </c>
       <c r="M15">
-        <v>1466.8447010591501</v>
+        <v>1.4668447010591501</v>
       </c>
       <c r="N15">
-        <v>6281.27050701402</v>
+        <v>6.2812705070140202</v>
       </c>
       <c r="O15">
-        <v>2064.55377598429</v>
+        <v>2.0645537759842898</v>
       </c>
       <c r="P15">
-        <v>3693.5190046760099</v>
+        <v>3.69351900467601</v>
       </c>
       <c r="Q15">
-        <v>1214.00098901306</v>
+        <v>1.2140009890130601</v>
       </c>
       <c r="R15">
-        <v>663.92293548387102</v>
+        <v>0.66392293548387105</v>
       </c>
       <c r="S15">
-        <v>218.22091595724001</v>
+        <v>0.21822091595724</v>
       </c>
       <c r="T15">
-        <v>2546.8103066132198</v>
+        <v>2.5468103066132199</v>
       </c>
       <c r="U15">
-        <v>837.09606668947401</v>
+        <v>0.83709606668947401</v>
       </c>
       <c r="V15">
-        <v>1621.2595161290301</v>
+        <v>1.62125951612903</v>
       </c>
       <c r="W15">
-        <v>532.88223332158702</v>
+        <v>0.53288223332158702</v>
       </c>
       <c r="X15">
-        <v>1849.05276209677</v>
+        <v>1.8490527620967701</v>
       </c>
       <c r="Y15">
-        <v>607.75425253828303</v>
+        <v>0.60775425253828297</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
@@ -2246,76 +2246,76 @@
         <v>0.13541666666666699</v>
       </c>
       <c r="B16">
-        <v>4228.2933242614199</v>
+        <v>4.2282933242614202</v>
       </c>
       <c r="C16">
-        <v>1389.77280771862</v>
+        <v>1.38977280771862</v>
       </c>
       <c r="D16">
-        <v>6613.8936656255701</v>
+        <v>6.6138936656255698</v>
       </c>
       <c r="E16">
-        <v>2173.8817212342901</v>
+        <v>2.1738817212342898</v>
       </c>
       <c r="F16">
-        <v>1306.3212925043599</v>
+        <v>1.3063212925043599</v>
       </c>
       <c r="G16">
-        <v>429.36704510289201</v>
+        <v>0.42936704510289198</v>
       </c>
       <c r="H16">
-        <v>2744.2729458917802</v>
+        <v>2.7442729458917801</v>
       </c>
       <c r="I16">
-        <v>901.99889758700294</v>
+        <v>0.90199889758700302</v>
       </c>
       <c r="J16">
-        <v>1221.1305010020001</v>
+        <v>1.2211305010019999</v>
       </c>
       <c r="K16">
-        <v>401.36618602845999</v>
+        <v>0.40136618602846003</v>
       </c>
       <c r="L16">
-        <v>4392.6270240480899</v>
+        <v>4.3926270240480898</v>
       </c>
       <c r="M16">
-        <v>1443.7866827837399</v>
+        <v>1.44378668278374</v>
       </c>
       <c r="N16">
-        <v>6182.5322765531</v>
+        <v>6.1825322765530997</v>
       </c>
       <c r="O16">
-        <v>2032.10008905829</v>
+        <v>2.0321000890582899</v>
       </c>
       <c r="P16">
-        <v>3635.4588510354001</v>
+        <v>3.6354588510353998</v>
       </c>
       <c r="Q16">
-        <v>1194.9175393671401</v>
+        <v>1.1949175393671401</v>
       </c>
       <c r="R16">
-        <v>661.06858064516098</v>
+        <v>0.66106858064516105</v>
       </c>
       <c r="S16">
-        <v>217.28273489121599</v>
+        <v>0.217282734891216</v>
       </c>
       <c r="T16">
-        <v>2506.77580360721</v>
+        <v>2.5067758036072099</v>
       </c>
       <c r="U16">
-        <v>823.93736189266201</v>
+        <v>0.82393736189266298</v>
       </c>
       <c r="V16">
-        <v>1614.2893548387001</v>
+        <v>1.6142893548387001</v>
       </c>
       <c r="W16">
-        <v>530.59125209492504</v>
+        <v>0.53059125209492497</v>
       </c>
       <c r="X16">
-        <v>1841.1032661290301</v>
+        <v>1.8411032661290301</v>
       </c>
       <c r="Y16">
-        <v>605.14137956950299</v>
+        <v>0.60514137956950298</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
@@ -2370,76 +2370,76 @@
         <v>0.14583333333333301</v>
       </c>
       <c r="B17">
-        <v>4170.0688552265801</v>
+        <v>4.1700688552265799</v>
       </c>
       <c r="C17">
-        <v>1370.63535021439</v>
+        <v>1.37063535021439</v>
       </c>
       <c r="D17">
-        <v>6525.3759806427597</v>
+        <v>6.5253759806427603</v>
       </c>
       <c r="E17">
-        <v>2144.78736515321</v>
+        <v>2.1447873651532099</v>
       </c>
       <c r="F17">
-        <v>1297.77647848115</v>
+        <v>1.2977764784811501</v>
       </c>
       <c r="G17">
-        <v>426.55850055175398</v>
+        <v>0.42655850055175398</v>
       </c>
       <c r="H17">
-        <v>2703.8168336673298</v>
+        <v>2.7038168336673301</v>
       </c>
       <c r="I17">
-        <v>888.70161654149501</v>
+        <v>0.88870161654149504</v>
       </c>
       <c r="J17">
-        <v>1203.1285771543</v>
+        <v>1.2031285771543001</v>
       </c>
       <c r="K17">
-        <v>395.44923979708199</v>
+        <v>0.39544923979708202</v>
       </c>
       <c r="L17">
-        <v>4327.8708517034001</v>
+        <v>4.3278708517034001</v>
       </c>
       <c r="M17">
-        <v>1422.50235822181</v>
+        <v>1.4225023582218099</v>
       </c>
       <c r="N17">
-        <v>6091.3892945891703</v>
+        <v>6.0913892945891703</v>
       </c>
       <c r="O17">
-        <v>2002.1428395881501</v>
+        <v>2.0021428395881502</v>
       </c>
       <c r="P17">
-        <v>3581.8648630594498</v>
+        <v>3.5818648630594501</v>
       </c>
       <c r="Q17">
-        <v>1177.3020473863</v>
+        <v>1.1773020473863001</v>
       </c>
       <c r="R17">
-        <v>658.21422580645105</v>
+        <v>0.65821422580645095</v>
       </c>
       <c r="S17">
-        <v>216.34455382519101</v>
+        <v>0.21634455382519099</v>
       </c>
       <c r="T17">
-        <v>2469.8208777555101</v>
+        <v>2.46982087775551</v>
       </c>
       <c r="U17">
-        <v>811.79086515714403</v>
+        <v>0.81179086515714405</v>
       </c>
       <c r="V17">
-        <v>1607.3191935483801</v>
+        <v>1.6073191935483799</v>
       </c>
       <c r="W17">
-        <v>528.30027086826306</v>
+        <v>0.52830027086826303</v>
       </c>
       <c r="X17">
-        <v>1833.1537701612899</v>
+        <v>1.8331537701612799</v>
       </c>
       <c r="Y17">
-        <v>602.52850660072295</v>
+        <v>0.60252850660072199</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -2494,76 +2494,76 @@
         <v>0.15625</v>
       </c>
       <c r="B18">
-        <v>4115.5333809231297</v>
+        <v>4.1155333809231296</v>
       </c>
       <c r="C18">
-        <v>1352.7104066424599</v>
+        <v>1.35271040664246</v>
       </c>
       <c r="D18">
-        <v>6441.9228490777195</v>
+        <v>6.4419228490777201</v>
       </c>
       <c r="E18">
-        <v>2117.3576472803802</v>
+        <v>2.1173576472803801</v>
       </c>
       <c r="F18">
-        <v>1286.9115095109501</v>
+        <v>1.28691150951095</v>
       </c>
       <c r="G18">
-        <v>422.98735794798898</v>
+        <v>0.42298735794798897</v>
       </c>
       <c r="H18">
-        <v>2666.7320641282499</v>
+        <v>2.6667320641282499</v>
       </c>
       <c r="I18">
-        <v>876.51244224977802</v>
+        <v>0.87651244224977798</v>
       </c>
       <c r="J18">
-        <v>1186.6268136272499</v>
+        <v>1.18662681362725</v>
       </c>
       <c r="K18">
-        <v>390.02537241831902</v>
+        <v>0.39002537241831903</v>
       </c>
       <c r="L18">
-        <v>4268.5110270540999</v>
+        <v>4.2685110270540996</v>
       </c>
       <c r="M18">
-        <v>1402.9917273733799</v>
+        <v>1.4029917273733801</v>
       </c>
       <c r="N18">
-        <v>6007.8415611222399</v>
+        <v>6.0078415611222402</v>
       </c>
       <c r="O18">
-        <v>1974.6820275738401</v>
+        <v>1.9746820275738399</v>
       </c>
       <c r="P18">
-        <v>3532.7370407481599</v>
+        <v>3.53273704074816</v>
       </c>
       <c r="Q18">
-        <v>1161.1545130705299</v>
+        <v>1.1611545130705301</v>
       </c>
       <c r="R18">
-        <v>653.647258064516</v>
+        <v>0.65364725806451596</v>
       </c>
       <c r="S18">
-        <v>214.84346411955201</v>
+        <v>0.21484346411955299</v>
       </c>
       <c r="T18">
-        <v>2435.94552905811</v>
+        <v>2.43594552905811</v>
       </c>
       <c r="U18">
-        <v>800.65657648291904</v>
+        <v>0.80065657648291899</v>
       </c>
       <c r="V18">
-        <v>1596.16693548387</v>
+        <v>1.5961669354838699</v>
       </c>
       <c r="W18">
-        <v>524.63470090560395</v>
+        <v>0.52463470090560405</v>
       </c>
       <c r="X18">
-        <v>1820.4345766128999</v>
+        <v>1.8204345766129</v>
       </c>
       <c r="Y18">
-        <v>598.347909850674</v>
+        <v>0.59834790985067399</v>
       </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
@@ -2618,76 +2618,76 @@
         <v>0.16666666666666699</v>
       </c>
       <c r="B19">
-        <v>4064.34649812528</v>
+        <v>4.0643464981252801</v>
       </c>
       <c r="C19">
-        <v>1335.88609187315</v>
+        <v>1.3358860918731501</v>
       </c>
       <c r="D19">
-        <v>6364.7854170794499</v>
+        <v>6.3647854170794496</v>
       </c>
       <c r="E19">
-        <v>2092.0037994682302</v>
+        <v>2.0920037994682299</v>
       </c>
       <c r="F19">
-        <v>1272.8389057550501</v>
+        <v>1.27283890575505</v>
       </c>
       <c r="G19">
-        <v>418.36191677494401</v>
+        <v>0.418361916774944</v>
       </c>
       <c r="H19">
-        <v>2633.0186372745402</v>
+        <v>2.6330186372745401</v>
       </c>
       <c r="I19">
-        <v>865.431374711854</v>
+        <v>0.86543137471185405</v>
       </c>
       <c r="J19">
-        <v>1171.6252104208399</v>
+        <v>1.17162521042084</v>
       </c>
       <c r="K19">
-        <v>385.09458389217099</v>
+        <v>0.38509458389217099</v>
       </c>
       <c r="L19">
-        <v>4214.5475501002002</v>
+        <v>4.2145475501001997</v>
       </c>
       <c r="M19">
-        <v>1385.2547902384499</v>
+        <v>1.38525479023845</v>
       </c>
       <c r="N19">
-        <v>5931.8890761522998</v>
+        <v>5.9318890761523004</v>
       </c>
       <c r="O19">
-        <v>1949.7176530153899</v>
+        <v>1.9497176530153899</v>
       </c>
       <c r="P19">
-        <v>3488.0753841015298</v>
+        <v>3.48807538410153</v>
       </c>
       <c r="Q19">
-        <v>1146.4749364198301</v>
+        <v>1.1464749364198299</v>
       </c>
       <c r="R19">
-        <v>646.79680645161295</v>
+        <v>0.64679680645161297</v>
       </c>
       <c r="S19">
-        <v>212.59182956109399</v>
+        <v>0.21259182956109399</v>
       </c>
       <c r="T19">
-        <v>2405.1497575150202</v>
+        <v>2.4051497575150198</v>
       </c>
       <c r="U19">
-        <v>790.53449586998704</v>
+        <v>0.79053449586998703</v>
       </c>
       <c r="V19">
-        <v>1579.4385483870899</v>
+        <v>1.5794385483870901</v>
       </c>
       <c r="W19">
-        <v>519.13634596161501</v>
+        <v>0.51913634596161495</v>
       </c>
       <c r="X19">
-        <v>1801.3557862903201</v>
+        <v>1.80135578629032</v>
       </c>
       <c r="Y19">
-        <v>592.077014725602</v>
+        <v>0.59207701472560204</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
@@ -2742,76 +2742,76 @@
         <v>0.17708333333333301</v>
       </c>
       <c r="B20">
-        <v>4022.9204273708701</v>
+        <v>4.0229204273708703</v>
       </c>
       <c r="C20">
-        <v>1322.2700008761601</v>
+        <v>1.3222700008761601</v>
       </c>
       <c r="D20">
-        <v>6299.1734571930701</v>
+        <v>6.2991734571930698</v>
       </c>
       <c r="E20">
-        <v>2070.43819114395</v>
+        <v>2.0704381911439498</v>
       </c>
       <c r="F20">
-        <v>1260.33835097614</v>
+        <v>1.2603383509761401</v>
       </c>
       <c r="G20">
-        <v>414.25318311319802</v>
+        <v>0.41425318311319798</v>
       </c>
       <c r="H20">
-        <v>2606.0478957915798</v>
+        <v>2.6060478957915798</v>
       </c>
       <c r="I20">
-        <v>856.56652068151504</v>
+        <v>0.85656652068151495</v>
       </c>
       <c r="J20">
-        <v>1159.62392785571</v>
+        <v>1.1596239278557099</v>
       </c>
       <c r="K20">
-        <v>381.14995307125298</v>
+        <v>0.38114995307125299</v>
       </c>
       <c r="L20">
-        <v>4171.3767685370703</v>
+        <v>4.17137676853707</v>
       </c>
       <c r="M20">
-        <v>1371.0652405305</v>
+        <v>1.3710652405304999</v>
       </c>
       <c r="N20">
-        <v>5871.1270881763503</v>
+        <v>5.8711270881763502</v>
       </c>
       <c r="O20">
-        <v>1929.7461533686201</v>
+        <v>1.92974615336862</v>
       </c>
       <c r="P20">
-        <v>3452.3460587842301</v>
+        <v>3.4523460587842298</v>
       </c>
       <c r="Q20">
-        <v>1134.7312750992701</v>
+        <v>1.13473127509927</v>
       </c>
       <c r="R20">
-        <v>640.51722580645105</v>
+        <v>0.64051722580645098</v>
       </c>
       <c r="S20">
-        <v>210.52783121584099</v>
+        <v>0.21052783121584101</v>
       </c>
       <c r="T20">
-        <v>2380.51314028056</v>
+        <v>2.3805131402805602</v>
       </c>
       <c r="U20">
-        <v>782.43683137964103</v>
+        <v>0.78243683137964104</v>
       </c>
       <c r="V20">
-        <v>1564.10419354838</v>
+        <v>1.5641041935483799</v>
       </c>
       <c r="W20">
-        <v>514.09618726295901</v>
+        <v>0.51409618726295903</v>
       </c>
       <c r="X20">
-        <v>1783.8668951612899</v>
+        <v>1.7838668951612899</v>
       </c>
       <c r="Y20">
-        <v>586.32869419428505</v>
+        <v>0.58632869419428502</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
@@ -2866,76 +2866,76 @@
         <v>0.1875</v>
       </c>
       <c r="B21">
-        <v>3997.6673891977498</v>
+        <v>3.9976673891977499</v>
       </c>
       <c r="C21">
-        <v>1313.9697286211799</v>
+        <v>1.31396972862118</v>
       </c>
       <c r="D21">
-        <v>6258.4738884975404</v>
+        <v>6.2584738884975399</v>
       </c>
       <c r="E21">
-        <v>2057.0608898260898</v>
+        <v>2.05706088982609</v>
       </c>
       <c r="F21">
-        <v>1254.1895289368999</v>
+        <v>1.2541895289369001</v>
       </c>
       <c r="G21">
-        <v>412.23216304332601</v>
+        <v>0.41223216304332599</v>
       </c>
       <c r="H21">
-        <v>2589.1911823647201</v>
+        <v>2.5891911823647198</v>
       </c>
       <c r="I21">
-        <v>851.02598691255298</v>
+        <v>0.85102598691255305</v>
       </c>
       <c r="J21">
-        <v>1152.1231262525</v>
+        <v>1.1521231262525</v>
       </c>
       <c r="K21">
-        <v>378.684558808178</v>
+        <v>0.37868455880817897</v>
       </c>
       <c r="L21">
-        <v>4144.39503006012</v>
+        <v>4.14439503006012</v>
       </c>
       <c r="M21">
-        <v>1362.19677196303</v>
+        <v>1.3621967719630299</v>
       </c>
       <c r="N21">
-        <v>5833.1508456913798</v>
+        <v>5.8331508456913799</v>
       </c>
       <c r="O21">
-        <v>1917.2639660893999</v>
+        <v>1.9172639660894</v>
       </c>
       <c r="P21">
-        <v>3430.0152304609201</v>
+        <v>3.4300152304609202</v>
       </c>
       <c r="Q21">
-        <v>1127.39148677392</v>
+        <v>1.1273914867739101</v>
       </c>
       <c r="R21">
-        <v>637.66287096774204</v>
+        <v>0.63766287096774199</v>
       </c>
       <c r="S21">
-        <v>209.589650149817</v>
+        <v>0.20958965014981701</v>
       </c>
       <c r="T21">
-        <v>2365.1152545090099</v>
+        <v>2.3651152545090102</v>
       </c>
       <c r="U21">
-        <v>777.37579107317504</v>
+        <v>0.777375791073175</v>
       </c>
       <c r="V21">
-        <v>1557.13403225806</v>
+        <v>1.55713403225806</v>
       </c>
       <c r="W21">
-        <v>511.805206036296</v>
+        <v>0.51180520603629698</v>
       </c>
       <c r="X21">
-        <v>1775.9173991935399</v>
+        <v>1.77591739919354</v>
       </c>
       <c r="Y21">
-        <v>583.71582122550501</v>
+        <v>0.58371582122550503</v>
       </c>
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
@@ -2990,76 +2990,76 @@
         <v>0.19791666666666699</v>
       </c>
       <c r="B22">
-        <v>3989.6085932833398</v>
+        <v>3.9896085932833398</v>
       </c>
       <c r="C22">
-        <v>1311.3209304972299</v>
+        <v>1.31132093049723</v>
       </c>
       <c r="D22">
-        <v>6247.1830286433196</v>
+        <v>6.2471830286433203</v>
       </c>
       <c r="E22">
-        <v>2053.3497636582101</v>
+        <v>2.0533497636582099</v>
       </c>
       <c r="F22">
-        <v>1257.05487915346</v>
+        <v>1.2570548791534599</v>
       </c>
       <c r="G22">
-        <v>413.17395811528098</v>
+        <v>0.41317395811528101</v>
       </c>
       <c r="H22">
-        <v>2582.4484969939799</v>
+        <v>2.58244849699398</v>
       </c>
       <c r="I22">
-        <v>848.80977340496895</v>
+        <v>0.84880977340496899</v>
       </c>
       <c r="J22">
-        <v>1149.12280561122</v>
+        <v>1.1491228056112199</v>
       </c>
       <c r="K22">
-        <v>377.69840110294899</v>
+        <v>0.377698401102949</v>
       </c>
       <c r="L22">
-        <v>4133.60233466933</v>
+        <v>4.1336023346693302</v>
       </c>
       <c r="M22">
-        <v>1358.6493845360501</v>
+        <v>1.3586493845360501</v>
       </c>
       <c r="N22">
-        <v>5817.9603486973901</v>
+        <v>5.8179603486973903</v>
       </c>
       <c r="O22">
-        <v>1912.2710911777001</v>
+        <v>1.9122710911777001</v>
       </c>
       <c r="P22">
-        <v>3421.0828991315898</v>
+        <v>3.4210828991315898</v>
       </c>
       <c r="Q22">
-        <v>1124.4555714437699</v>
+        <v>1.1244555714437701</v>
       </c>
       <c r="R22">
-        <v>639.946354838709</v>
+        <v>0.63994635483870899</v>
       </c>
       <c r="S22">
-        <v>210.34019500263599</v>
+        <v>0.21034019500263601</v>
       </c>
       <c r="T22">
-        <v>2358.9561002004002</v>
+        <v>2.3589561002004</v>
       </c>
       <c r="U22">
-        <v>775.35137495058905</v>
+        <v>0.77535137495058903</v>
       </c>
       <c r="V22">
-        <v>1562.71016129032</v>
+        <v>1.56271016129032</v>
       </c>
       <c r="W22">
-        <v>513.63799101762595</v>
+        <v>0.51363799101762597</v>
       </c>
       <c r="X22">
-        <v>1782.27699596774</v>
+        <v>1.78227699596774</v>
       </c>
       <c r="Y22">
-        <v>585.80611960052897</v>
+        <v>0.58580611960052897</v>
       </c>
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
@@ -3114,76 +3114,76 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="B23">
-        <v>4005.8370666170999</v>
+        <v>4.0058370666170999</v>
       </c>
       <c r="C23">
-        <v>1316.6549717333601</v>
+        <v>1.31665497173336</v>
       </c>
       <c r="D23">
-        <v>6273.9736503679396</v>
+        <v>6.2739736503679397</v>
       </c>
       <c r="E23">
-        <v>2062.15541518695</v>
+        <v>2.0621554151869499</v>
       </c>
       <c r="F23">
-        <v>1275.48904506593</v>
+        <v>1.27548904506593</v>
       </c>
       <c r="G23">
-        <v>419.23297544294002</v>
+        <v>0.41923297544294003</v>
       </c>
       <c r="H23">
-        <v>2589.1911823647201</v>
+        <v>2.5891911823647198</v>
       </c>
       <c r="I23">
-        <v>851.02598691255298</v>
+        <v>0.85102598691255305</v>
       </c>
       <c r="J23">
-        <v>1152.1231262525</v>
+        <v>1.1521231262525</v>
       </c>
       <c r="K23">
-        <v>378.684558808178</v>
+        <v>0.37868455880817897</v>
       </c>
       <c r="L23">
-        <v>4144.39503006012</v>
+        <v>4.14439503006012</v>
       </c>
       <c r="M23">
-        <v>1362.19677196303</v>
+        <v>1.3621967719630299</v>
       </c>
       <c r="N23">
-        <v>5833.1508456913798</v>
+        <v>5.8331508456913799</v>
       </c>
       <c r="O23">
-        <v>1917.2639660893999</v>
+        <v>1.9172639660894</v>
       </c>
       <c r="P23">
-        <v>3430.0152304609201</v>
+        <v>3.4300152304609202</v>
       </c>
       <c r="Q23">
-        <v>1127.39148677392</v>
+        <v>1.1273914867739101</v>
       </c>
       <c r="R23">
-        <v>651.36377419354801</v>
+        <v>0.65136377419354796</v>
       </c>
       <c r="S23">
-        <v>214.09291926673299</v>
+        <v>0.21409291926673299</v>
       </c>
       <c r="T23">
-        <v>2365.1152545090099</v>
+        <v>2.3651152545090102</v>
       </c>
       <c r="U23">
-        <v>777.37579107317504</v>
+        <v>0.777375791073175</v>
       </c>
       <c r="V23">
-        <v>1590.59080645161</v>
+        <v>1.5905908064516101</v>
       </c>
       <c r="W23">
-        <v>522.801915924274</v>
+        <v>0.52280191592427405</v>
       </c>
       <c r="X23">
-        <v>1814.0749798387001</v>
+        <v>1.8140749798386999</v>
       </c>
       <c r="Y23">
-        <v>596.25761147565004</v>
+        <v>0.59625761147565004</v>
       </c>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
@@ -3238,76 +3238,76 @@
         <v>0.21875</v>
       </c>
       <c r="B24">
-        <v>4051.7438200594702</v>
+        <v>4.0517438200594702</v>
       </c>
       <c r="C24">
-        <v>1331.7437919102299</v>
+        <v>1.33174379191023</v>
       </c>
       <c r="D24">
-        <v>6339.48659900235</v>
+        <v>6.3394865990023499</v>
       </c>
       <c r="E24">
-        <v>2083.68848008648</v>
+        <v>2.0836884800864799</v>
       </c>
       <c r="F24">
-        <v>1311.6092709208699</v>
+        <v>1.31160927092087</v>
       </c>
       <c r="G24">
-        <v>431.105119556928</v>
+        <v>0.43110511955692798</v>
       </c>
       <c r="H24">
-        <v>2612.79058116232</v>
+        <v>2.61279058116232</v>
       </c>
       <c r="I24">
-        <v>858.78273418909998</v>
+        <v>0.85878273418910001</v>
       </c>
       <c r="J24">
-        <v>1162.62424849699</v>
+        <v>1.16262424849699</v>
       </c>
       <c r="K24">
-        <v>382.13611077648198</v>
+        <v>0.38213611077648202</v>
       </c>
       <c r="L24">
-        <v>4182.1694639278503</v>
+        <v>4.1821694639278499</v>
       </c>
       <c r="M24">
-        <v>1374.6126279574901</v>
+        <v>1.37461262795749</v>
       </c>
       <c r="N24">
-        <v>5886.31758517034</v>
+        <v>5.8863175851703398</v>
       </c>
       <c r="O24">
-        <v>1934.7390282803201</v>
+        <v>1.9347390282803201</v>
       </c>
       <c r="P24">
-        <v>3461.2783901135599</v>
+        <v>3.4612783901135602</v>
       </c>
       <c r="Q24">
-        <v>1137.6671904294101</v>
+        <v>1.13766719042941</v>
       </c>
       <c r="R24">
-        <v>673.05687096774204</v>
+        <v>0.67305687096774203</v>
       </c>
       <c r="S24">
-        <v>221.22309536851699</v>
+        <v>0.221223095368517</v>
       </c>
       <c r="T24">
-        <v>2386.6722945891702</v>
+        <v>2.3866722945891699</v>
       </c>
       <c r="U24">
-        <v>784.46124750222805</v>
+        <v>0.78446124750222801</v>
       </c>
       <c r="V24">
-        <v>1643.56403225806</v>
+        <v>1.64356403225806</v>
       </c>
       <c r="W24">
-        <v>540.21337324690603</v>
+        <v>0.54021337324690599</v>
       </c>
       <c r="X24">
-        <v>1874.49114919354</v>
+        <v>1.8744911491935401</v>
       </c>
       <c r="Y24">
-        <v>616.11544603838001</v>
+        <v>0.61611544603837998</v>
       </c>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
@@ -3362,76 +3362,76 @@
         <v>0.22916666666666699</v>
       </c>
       <c r="B25">
-        <v>4143.8422894175401</v>
+        <v>4.14384228941754</v>
       </c>
       <c r="C25">
-        <v>1362.0150948995299</v>
+        <v>1.36201509489953</v>
       </c>
       <c r="D25">
-        <v>6448.8169724772097</v>
+        <v>6.4488169724772098</v>
       </c>
       <c r="E25">
-        <v>2119.62363606093</v>
+        <v>2.11962363606093</v>
       </c>
       <c r="F25">
-        <v>1372.6547692966501</v>
+        <v>1.37265476929665</v>
       </c>
       <c r="G25">
-        <v>451.16980456576999</v>
+        <v>0.45116980456576999</v>
       </c>
       <c r="H25">
-        <v>2663.3607214428798</v>
+        <v>2.6633607214428801</v>
       </c>
       <c r="I25">
-        <v>875.40433549598595</v>
+        <v>0.87540433549598595</v>
       </c>
       <c r="J25">
-        <v>1185.12665330661</v>
+        <v>1.18512665330661</v>
       </c>
       <c r="K25">
-        <v>389.53229356570398</v>
+        <v>0.38953229356570401</v>
       </c>
       <c r="L25">
-        <v>4263.1146793587104</v>
+        <v>4.2631146793587096</v>
       </c>
       <c r="M25">
-        <v>1401.2180336598899</v>
+        <v>1.4012180336598901</v>
       </c>
       <c r="N25">
-        <v>6000.2463126252496</v>
+        <v>6.0002463126252499</v>
       </c>
       <c r="O25">
-        <v>1972.1855901179999</v>
+        <v>1.9721855901180001</v>
       </c>
       <c r="P25">
-        <v>3528.2708750835</v>
+        <v>3.5282708750834999</v>
       </c>
       <c r="Q25">
-        <v>1159.68655540546</v>
+        <v>1.1596865554054601</v>
       </c>
       <c r="R25">
-        <v>709.02174193548399</v>
+        <v>0.70902174193548395</v>
       </c>
       <c r="S25">
-        <v>233.044176800423</v>
+        <v>0.233044176800423</v>
       </c>
       <c r="T25">
-        <v>2432.8659519038001</v>
+        <v>2.4328659519037998</v>
       </c>
       <c r="U25">
-        <v>799.64436842162604</v>
+        <v>0.79964436842162601</v>
       </c>
       <c r="V25">
-        <v>1731.38806451612</v>
+        <v>1.7313880645161199</v>
       </c>
       <c r="W25">
-        <v>569.07973670284696</v>
+        <v>0.56907973670284695</v>
       </c>
       <c r="X25">
-        <v>1974.6547983870901</v>
+        <v>1.9746547983870899</v>
       </c>
       <c r="Y25">
-        <v>649.03764544501098</v>
+        <v>0.64903764544501097</v>
       </c>
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
@@ -3486,76 +3486,76 @@
         <v>0.23958333333333301</v>
       </c>
       <c r="B26">
-        <v>4292.2336899605598</v>
+        <v>4.2922336899605602</v>
       </c>
       <c r="C26">
-        <v>1410.78898960325</v>
+        <v>1.4107889896032499</v>
       </c>
       <c r="D26">
-        <v>6606.41902339219</v>
+        <v>6.6064190233921902</v>
       </c>
       <c r="E26">
-        <v>2171.4249251402798</v>
+        <v>2.17142492514028</v>
       </c>
       <c r="F26">
-        <v>1461.0850690089801</v>
+        <v>1.4610850690089801</v>
       </c>
       <c r="G26">
-        <v>480.23543849741498</v>
+        <v>0.48023543849741501</v>
       </c>
       <c r="H26">
-        <v>2747.6442885771498</v>
+        <v>2.7476442885771499</v>
       </c>
       <c r="I26">
-        <v>903.10700434079604</v>
+        <v>0.90310700434079605</v>
       </c>
       <c r="J26">
-        <v>1222.63066132264</v>
+        <v>1.2226306613226401</v>
       </c>
       <c r="K26">
-        <v>401.85926488107498</v>
+        <v>0.40185926488107498</v>
       </c>
       <c r="L26">
-        <v>4398.0233717434803</v>
+        <v>4.3980233717434798</v>
       </c>
       <c r="M26">
-        <v>1445.56037649723</v>
+        <v>1.44556037649723</v>
       </c>
       <c r="N26">
-        <v>6190.1275250501003</v>
+        <v>6.1901275250500998</v>
       </c>
       <c r="O26">
-        <v>2034.5965265141399</v>
+        <v>2.0345965265141399</v>
       </c>
       <c r="P26">
-        <v>3639.92501670006</v>
+        <v>3.6399250167000599</v>
       </c>
       <c r="Q26">
-        <v>1196.38549703222</v>
+        <v>1.1963854970322201</v>
       </c>
       <c r="R26">
-        <v>760.40012903225795</v>
+        <v>0.76040012903225795</v>
       </c>
       <c r="S26">
-        <v>249.93143598885899</v>
+        <v>0.249931435988859</v>
       </c>
       <c r="T26">
-        <v>2509.8553807615199</v>
+        <v>2.50985538076152</v>
       </c>
       <c r="U26">
-        <v>824.94956995395603</v>
+        <v>0.82494956995395596</v>
       </c>
       <c r="V26">
-        <v>1856.8509677419299</v>
+        <v>1.85685096774193</v>
       </c>
       <c r="W26">
-        <v>610.31739878276403</v>
+        <v>0.61031739878276403</v>
       </c>
       <c r="X26">
-        <v>2117.7457258064501</v>
+        <v>2.1177457258064498</v>
       </c>
       <c r="Y26">
-        <v>696.06935888305497</v>
+        <v>0.69606935888305499</v>
       </c>
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
@@ -3610,76 +3610,76 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>4513.7718607214401</v>
+        <v>4.5137718607214401</v>
       </c>
       <c r="C27">
-        <v>1483.6050650227501</v>
+        <v>1.4836050650227599</v>
       </c>
       <c r="D27">
-        <v>6825.7102153391797</v>
+        <v>6.8257102153391802</v>
       </c>
       <c r="E27">
-        <v>2243.50245433898</v>
+        <v>2.2435024543389801</v>
       </c>
       <c r="F27">
-        <v>1585.0268624749399</v>
+        <v>1.58502686247494</v>
       </c>
       <c r="G27">
-        <v>520.97313597703896</v>
+        <v>0.52097313597703898</v>
       </c>
       <c r="H27">
-        <v>2875.7553106212399</v>
+        <v>2.8757553106212401</v>
       </c>
       <c r="I27">
-        <v>945.21506098490602</v>
+        <v>0.94521506098490604</v>
       </c>
       <c r="J27">
-        <v>1279.6367535070101</v>
+        <v>1.2796367535070099</v>
       </c>
       <c r="K27">
-        <v>420.596261280438</v>
+        <v>0.42059626128043798</v>
       </c>
       <c r="L27">
-        <v>4603.0845841683304</v>
+        <v>4.6030845841683297</v>
       </c>
       <c r="M27">
-        <v>1512.96073760998</v>
+        <v>1.5129607376099801</v>
       </c>
       <c r="N27">
-        <v>6478.7469679358701</v>
+        <v>6.4787469679358702</v>
       </c>
       <c r="O27">
-        <v>2129.4611498362701</v>
+        <v>2.1294611498362701</v>
       </c>
       <c r="P27">
-        <v>3809.6393119572399</v>
+        <v>3.8096393119572398</v>
       </c>
       <c r="Q27">
-        <v>1252.1678883048801</v>
+        <v>1.2521678883048799</v>
       </c>
       <c r="R27">
-        <v>831.75900000000001</v>
+        <v>0.83175900000000003</v>
       </c>
       <c r="S27">
-        <v>273.38596263946602</v>
+        <v>0.27338596263946602</v>
       </c>
       <c r="T27">
-        <v>2626.8793126252499</v>
+        <v>2.6268793126252499</v>
       </c>
       <c r="U27">
-        <v>863.413476283097</v>
+        <v>0.86341347628309695</v>
       </c>
       <c r="V27">
-        <v>2031.105</v>
+        <v>2.0311050000000002</v>
       </c>
       <c r="W27">
-        <v>667.59192944931397</v>
+        <v>0.667591929449314</v>
       </c>
       <c r="X27">
-        <v>2316.4831250000002</v>
+        <v>2.316483125</v>
       </c>
       <c r="Y27">
-        <v>761.39118310256094</v>
+        <v>0.76139118310256104</v>
       </c>
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
@@ -3734,76 +3734,76 @@
         <v>0.26041666666666702</v>
       </c>
       <c r="B28">
-        <v>4811.2354682590903</v>
+        <v>4.8112354682590901</v>
       </c>
       <c r="C28">
-        <v>1581.37662468955</v>
+        <v>1.58137662468955</v>
       </c>
       <c r="D28">
-        <v>7115.11494785178</v>
+        <v>7.1151149478517803</v>
       </c>
       <c r="E28">
-        <v>2338.6251898794098</v>
+        <v>2.3386251898794099</v>
       </c>
       <c r="F28">
-        <v>1763.66242157702</v>
+        <v>1.76366242157702</v>
       </c>
       <c r="G28">
-        <v>579.68780487363097</v>
+        <v>0.57968780487363103</v>
       </c>
       <c r="H28">
-        <v>3044.3224448897699</v>
+        <v>3.0443224448897701</v>
       </c>
       <c r="I28">
-        <v>1000.6203986745199</v>
+        <v>1.0006203986745199</v>
       </c>
       <c r="J28">
-        <v>1354.64476953907</v>
+        <v>1.35464476953907</v>
       </c>
       <c r="K28">
-        <v>445.25020391117903</v>
+        <v>0.44525020391117898</v>
       </c>
       <c r="L28">
-        <v>4872.9019689378702</v>
+        <v>4.8729019689378701</v>
       </c>
       <c r="M28">
-        <v>1601.64542328466</v>
+        <v>1.60164542328466</v>
       </c>
       <c r="N28">
-        <v>6858.5093927855696</v>
+        <v>6.85850939278557</v>
       </c>
       <c r="O28">
-        <v>2254.28302262855</v>
+        <v>2.2542830226285502</v>
       </c>
       <c r="P28">
-        <v>4032.9475951903801</v>
+        <v>4.0329475951903797</v>
       </c>
       <c r="Q28">
-        <v>1325.56577155839</v>
+        <v>1.3255657715583899</v>
       </c>
       <c r="R28">
-        <v>935.65751612903205</v>
+        <v>0.93565751612903203</v>
       </c>
       <c r="S28">
-        <v>307.53575344274799</v>
+        <v>0.30753575344274803</v>
       </c>
       <c r="T28">
-        <v>2780.8581703406799</v>
+        <v>2.7808581703406801</v>
       </c>
       <c r="U28">
-        <v>914.02387934775697</v>
+        <v>0.91402387934775697</v>
       </c>
       <c r="V28">
-        <v>2284.8188709677402</v>
+        <v>2.2848188709677402</v>
       </c>
       <c r="W28">
-        <v>750.98364609981195</v>
+        <v>0.75098364609981205</v>
       </c>
       <c r="X28">
-        <v>2605.8447782257999</v>
+        <v>2.6058447782258001</v>
       </c>
       <c r="Y28">
-        <v>856.49975916616199</v>
+        <v>0.85649975916616194</v>
       </c>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
@@ -3858,76 +3858,76 @@
         <v>0.27083333333333298</v>
       </c>
       <c r="B29">
-        <v>5197.1639911759003</v>
+        <v>5.1971639911759002</v>
       </c>
       <c r="C29">
-        <v>1708.2251959074499</v>
+        <v>1.7082251959074499</v>
       </c>
       <c r="D29">
-        <v>7506.4410679928096</v>
+        <v>7.5064410679928102</v>
       </c>
       <c r="E29">
-        <v>2467.2478655110799</v>
+        <v>2.4672478655110801</v>
       </c>
       <c r="F29">
-        <v>2017.7460671746701</v>
+        <v>2.0177460671746701</v>
       </c>
       <c r="G29">
-        <v>663.20106056747704</v>
+        <v>0.66320106056747696</v>
       </c>
       <c r="H29">
-        <v>3256.71703406813</v>
+        <v>3.2567170340681302</v>
       </c>
       <c r="I29">
-        <v>1070.43112416344</v>
+        <v>1.0704311241634401</v>
       </c>
       <c r="J29">
-        <v>1449.1548697394701</v>
+        <v>1.4491548697394701</v>
       </c>
       <c r="K29">
-        <v>476.31417162591202</v>
+        <v>0.476314171625912</v>
       </c>
       <c r="L29">
-        <v>5212.8718737474901</v>
+        <v>5.2128718737474902</v>
       </c>
       <c r="M29">
-        <v>1713.3881272347501</v>
+        <v>1.71338812723475</v>
       </c>
       <c r="N29">
-        <v>7337.0100480961901</v>
+        <v>7.3370100480961904</v>
       </c>
       <c r="O29">
-        <v>2411.55858234682</v>
+        <v>2.41155858234682</v>
       </c>
       <c r="P29">
-        <v>4314.31603206412</v>
+        <v>4.3143160320641201</v>
       </c>
       <c r="Q29">
-        <v>1418.0471044578201</v>
+        <v>1.41804710445782</v>
       </c>
       <c r="R29">
-        <v>1085.2257096774099</v>
+        <v>1.0852257096774101</v>
       </c>
       <c r="S29">
-        <v>356.69644130241898</v>
+        <v>0.35669644130241901</v>
       </c>
       <c r="T29">
-        <v>2974.8715310621201</v>
+        <v>2.9748715310621199</v>
       </c>
       <c r="U29">
-        <v>977.79298720922804</v>
+        <v>0.97779298720922803</v>
       </c>
       <c r="V29">
-        <v>2650.0553225806402</v>
+        <v>2.65005532258064</v>
       </c>
       <c r="W29">
-        <v>871.03106237690201</v>
+        <v>0.87103106237690198</v>
       </c>
       <c r="X29">
-        <v>3022.3983669354802</v>
+        <v>3.0223983669354801</v>
       </c>
       <c r="Y29">
-        <v>993.41430273024605</v>
+        <v>0.993414302730246</v>
       </c>
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
@@ -3982,76 +3982,76 @@
         <v>0.28125</v>
       </c>
       <c r="B30">
-        <v>5669.9662948477599</v>
+        <v>5.66996629484776</v>
       </c>
       <c r="C30">
-        <v>1863.62779801635</v>
+        <v>1.86362779801635</v>
       </c>
       <c r="D30">
-        <v>8005.3328854852098</v>
+        <v>8.0053328854852097</v>
       </c>
       <c r="E30">
-        <v>2631.2256761246299</v>
+        <v>2.6312256761246302</v>
       </c>
       <c r="F30">
-        <v>2367.0052664199302</v>
+        <v>2.3670052664199299</v>
       </c>
       <c r="G30">
-        <v>777.99700794689295</v>
+        <v>0.77799700794689297</v>
       </c>
       <c r="H30">
-        <v>3506.19639278557</v>
+        <v>3.5061963927855699</v>
       </c>
       <c r="I30">
-        <v>1152.4310239440799</v>
+        <v>1.15243102394408</v>
       </c>
       <c r="J30">
-        <v>1560.1667334669301</v>
+        <v>1.56016673346693</v>
       </c>
       <c r="K30">
-        <v>512.80200671940895</v>
+        <v>0.51280200671940901</v>
       </c>
       <c r="L30">
-        <v>5612.2016032064103</v>
+        <v>5.6122016032064099</v>
       </c>
       <c r="M30">
-        <v>1844.64146203328</v>
+        <v>1.8446414620332801</v>
       </c>
       <c r="N30">
-        <v>7899.05843687374</v>
+        <v>7.89905843687374</v>
       </c>
       <c r="O30">
-        <v>2596.2949540793902</v>
+        <v>2.59629495407939</v>
       </c>
       <c r="P30">
-        <v>4644.8122912491599</v>
+        <v>4.6448122912491598</v>
       </c>
       <c r="Q30">
-        <v>1526.6759716730101</v>
+        <v>1.5266759716730101</v>
       </c>
       <c r="R30">
-        <v>1293.59361290322</v>
+        <v>1.2935936129032199</v>
       </c>
       <c r="S30">
-        <v>425.183659122189</v>
+        <v>0.42518365912218897</v>
       </c>
       <c r="T30">
-        <v>3202.76024048096</v>
+        <v>3.2027602404809601</v>
       </c>
       <c r="U30">
-        <v>1052.69638374492</v>
+        <v>1.0526963837449199</v>
       </c>
       <c r="V30">
-        <v>3158.8770967741898</v>
+        <v>3.1588770967741899</v>
       </c>
       <c r="W30">
-        <v>1038.27269192323</v>
+        <v>1.0382726919232299</v>
       </c>
       <c r="X30">
-        <v>3602.7115725806402</v>
+        <v>3.60271157258064</v>
       </c>
       <c r="Y30">
-        <v>1184.1540294511999</v>
+        <v>1.1841540294512001</v>
       </c>
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
@@ -4106,76 +4106,76 @@
         <v>0.29166666666666702</v>
       </c>
       <c r="B31">
-        <v>6253.9296485228497</v>
+        <v>6.2539296485228499</v>
       </c>
       <c r="C31">
-        <v>2055.5672703762898</v>
+        <v>2.0555672703762902</v>
       </c>
       <c r="D31">
-        <v>8651.0504184931597</v>
+        <v>8.6510504184931598</v>
       </c>
       <c r="E31">
-        <v>2843.4627656596499</v>
+        <v>2.8434627656596501</v>
       </c>
       <c r="F31">
-        <v>2827.0088350087199</v>
+        <v>2.8270088350087201</v>
       </c>
       <c r="G31">
-        <v>929.19286926758298</v>
+        <v>0.92919286926758304</v>
       </c>
       <c r="H31">
-        <v>3806.2458917835602</v>
+        <v>3.80624589178356</v>
       </c>
       <c r="I31">
-        <v>1251.0525250316</v>
+        <v>1.2510525250316</v>
       </c>
       <c r="J31">
-        <v>1693.681002004</v>
+        <v>1.6936810020040001</v>
       </c>
       <c r="K31">
-        <v>556.68602460212696</v>
+        <v>0.55668602460212702</v>
       </c>
       <c r="L31">
-        <v>6092.4765480961896</v>
+        <v>6.0924765480961902</v>
       </c>
       <c r="M31">
-        <v>2002.5002025342001</v>
+        <v>2.0025002025342</v>
       </c>
       <c r="N31">
-        <v>8575.0355531062105</v>
+        <v>8.5750355531062095</v>
       </c>
       <c r="O31">
-        <v>2818.4778876496498</v>
+        <v>2.8184778876496499</v>
       </c>
       <c r="P31">
-        <v>5042.3010354041398</v>
+        <v>5.0423010354041402</v>
       </c>
       <c r="Q31">
-        <v>1657.32420386426</v>
+        <v>1.6573242038642599</v>
       </c>
       <c r="R31">
-        <v>1569.8951612903199</v>
+        <v>1.56989516129032</v>
       </c>
       <c r="S31">
-        <v>515.99958631333595</v>
+        <v>0.51599958631333598</v>
       </c>
       <c r="T31">
-        <v>3476.8426072144198</v>
+        <v>3.4768426072144201</v>
       </c>
       <c r="U31">
-        <v>1142.78290120002</v>
+        <v>1.1427829012000199</v>
       </c>
       <c r="V31">
-        <v>3833.58870967741</v>
+        <v>3.8335887096774099</v>
       </c>
       <c r="W31">
-        <v>1260.03967466411</v>
+        <v>1.26003967466411</v>
       </c>
       <c r="X31">
-        <v>4372.2227822580599</v>
+        <v>4.3722227822580599</v>
       </c>
       <c r="Y31">
-        <v>1437.08013282913</v>
+        <v>1.4370801328291301</v>
       </c>
       <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
@@ -4230,76 +4230,76 @@
         <v>0.30208333333333298</v>
       </c>
       <c r="B32">
-        <v>6956.3211601590201</v>
+        <v>6.9563211601590202</v>
       </c>
       <c r="C32">
-        <v>2286.4321958636601</v>
+        <v>2.28643219586366</v>
       </c>
       <c r="D32">
-        <v>9444.9785117551692</v>
+        <v>9.4449785117551599</v>
       </c>
       <c r="E32">
-        <v>3104.4143105698299</v>
+        <v>3.1044143105698301</v>
       </c>
       <c r="F32">
-        <v>3368.9515967014599</v>
+        <v>3.3689515967014598</v>
       </c>
       <c r="G32">
-        <v>1107.3208409527199</v>
+        <v>1.10732084095272</v>
       </c>
       <c r="H32">
-        <v>4170.3509018036002</v>
+        <v>4.1703509018035998</v>
       </c>
       <c r="I32">
-        <v>1370.7280544411799</v>
+        <v>1.37072805444118</v>
       </c>
       <c r="J32">
-        <v>1855.69831663326</v>
+        <v>1.8556983166332599</v>
       </c>
       <c r="K32">
-        <v>609.93854068452697</v>
+        <v>0.60993854068452702</v>
       </c>
       <c r="L32">
-        <v>6675.2820991983899</v>
+        <v>6.6752820991983901</v>
       </c>
       <c r="M32">
-        <v>2194.0591235914999</v>
+        <v>2.1940591235914999</v>
       </c>
       <c r="N32">
-        <v>9395.3223907815609</v>
+        <v>9.3953223907815602</v>
       </c>
       <c r="O32">
-        <v>3088.0931328809702</v>
+        <v>3.08809313288097</v>
       </c>
       <c r="P32">
-        <v>5524.6469271877004</v>
+        <v>5.5246469271876997</v>
       </c>
       <c r="Q32">
-        <v>1815.8636316918401</v>
+        <v>1.81586363169184</v>
       </c>
       <c r="R32">
-        <v>1894.72074193548</v>
+        <v>1.8947207419354799</v>
       </c>
       <c r="S32">
-        <v>622.76459162689605</v>
+        <v>0.62276459162689601</v>
       </c>
       <c r="T32">
-        <v>3809.4369398797598</v>
+        <v>3.8094369398797601</v>
       </c>
       <c r="U32">
-        <v>1252.10137181968</v>
+        <v>1.2521013718196801</v>
       </c>
       <c r="V32">
-        <v>4626.7930645161196</v>
+        <v>4.6267930645161197</v>
       </c>
       <c r="W32">
-        <v>1520.7533382582501</v>
+        <v>1.5207533382582501</v>
       </c>
       <c r="X32">
-        <v>5276.8754233870904</v>
+        <v>5.2768754233870903</v>
       </c>
       <c r="Y32">
-        <v>1734.42507667632</v>
+        <v>1.7344250766763201</v>
       </c>
       <c r="Z32" s="4"/>
       <c r="AA32" s="4"/>
@@ -4354,76 +4354,76 @@
         <v>0.3125</v>
       </c>
       <c r="B33">
-        <v>7801.8871424461804</v>
+        <v>7.80188714244618</v>
       </c>
       <c r="C33">
-        <v>2564.3562941214</v>
+        <v>2.5643562941214002</v>
       </c>
       <c r="D33">
-        <v>10404.7721729759</v>
+        <v>10.4047721729759</v>
       </c>
       <c r="E33">
-        <v>3419.88323126453</v>
+        <v>3.4198832312645302</v>
       </c>
       <c r="F33">
-        <v>3961.8475941802899</v>
+        <v>3.96184759418029</v>
       </c>
       <c r="G33">
-        <v>1302.1963313481799</v>
+        <v>1.3021963313481799</v>
       </c>
       <c r="H33">
-        <v>4625.4821643286496</v>
+        <v>4.6254821643286501</v>
       </c>
       <c r="I33">
-        <v>1520.32246620315</v>
+        <v>1.52032246620315</v>
       </c>
       <c r="J33">
-        <v>2058.2199599198302</v>
+        <v>2.0582199599198399</v>
       </c>
       <c r="K33">
-        <v>676.50418578752794</v>
+        <v>0.67650418578752802</v>
       </c>
       <c r="L33">
-        <v>7403.7890380761501</v>
+        <v>7.40378903807615</v>
       </c>
       <c r="M33">
-        <v>2433.5077749131301</v>
+        <v>2.4335077749131302</v>
       </c>
       <c r="N33">
-        <v>10420.680937875701</v>
+        <v>10.4206809378757</v>
       </c>
       <c r="O33">
-        <v>3425.1121894201201</v>
+        <v>3.42511218942012</v>
       </c>
       <c r="P33">
-        <v>6127.5792919171599</v>
+        <v>6.1275792919171597</v>
       </c>
       <c r="Q33">
-        <v>2014.0379164763201</v>
+        <v>2.0140379164763198</v>
       </c>
       <c r="R33">
-        <v>2246.37725806451</v>
+        <v>2.2463772580645101</v>
       </c>
       <c r="S33">
-        <v>738.34849896108301</v>
+        <v>0.73834849896108301</v>
       </c>
       <c r="T33">
-        <v>4225.1798557114198</v>
+        <v>4.2251798557114197</v>
       </c>
       <c r="U33">
-        <v>1388.74946009426</v>
+        <v>1.38874946009426</v>
       </c>
       <c r="V33">
-        <v>5485.5169354838699</v>
+        <v>5.4855169354838704</v>
       </c>
       <c r="W33">
-        <v>1803.00222538301</v>
+        <v>1.80300222538301</v>
       </c>
       <c r="X33">
-        <v>6256.2533266129003</v>
+        <v>6.2562533266129003</v>
       </c>
       <c r="Y33">
-        <v>2056.3310264300399</v>
+        <v>2.0563310264300401</v>
       </c>
       <c r="Z33" s="4"/>
       <c r="AA33" s="4"/>
@@ -4478,76 +4478,76 @@
         <v>0.32291666666666702</v>
       </c>
       <c r="B34">
-        <v>8804.9322895791593</v>
+        <v>8.8049322895791597</v>
       </c>
       <c r="C34">
-        <v>2894.0412907608002</v>
+        <v>2.8940412907608</v>
       </c>
       <c r="D34">
-        <v>11535.2371820356</v>
+        <v>11.535237182035599</v>
       </c>
       <c r="E34">
-        <v>3791.4491112033502</v>
+        <v>3.7914491112033502</v>
       </c>
       <c r="F34">
-        <v>4571.3638614729398</v>
+        <v>4.5713638614729399</v>
       </c>
       <c r="G34">
-        <v>1502.53464025522</v>
+        <v>1.50253464025522</v>
       </c>
       <c r="H34">
-        <v>5191.8677354709398</v>
+        <v>5.1918677354709404</v>
       </c>
       <c r="I34">
-        <v>1706.4844008402699</v>
+        <v>1.70648440084027</v>
       </c>
       <c r="J34">
-        <v>2310.2468937875701</v>
+        <v>2.31024689378757</v>
       </c>
       <c r="K34">
-        <v>759.34143302681696</v>
+        <v>0.759341433026817</v>
       </c>
       <c r="L34">
-        <v>8310.3754509017999</v>
+        <v>8.3103754509018</v>
       </c>
       <c r="M34">
-        <v>2731.4883187800501</v>
+        <v>2.7314883187800501</v>
       </c>
       <c r="N34">
-        <v>11696.682685370701</v>
+        <v>11.6966826853707</v>
       </c>
       <c r="O34">
-        <v>3844.5136820021798</v>
+        <v>3.8445136820021801</v>
       </c>
       <c r="P34">
-        <v>6877.8951235804898</v>
+        <v>6.8778951235804904</v>
       </c>
       <c r="Q34">
-        <v>2260.6548042081199</v>
+        <v>2.2606548042081198</v>
       </c>
       <c r="R34">
-        <v>2601.4589999999998</v>
+        <v>2.6014590000000002</v>
       </c>
       <c r="S34">
-        <v>855.05822357449995</v>
+        <v>0.85505822357450001</v>
       </c>
       <c r="T34">
-        <v>4742.5488176352701</v>
+        <v>4.7425488176352699</v>
       </c>
       <c r="U34">
-        <v>1558.80041439152</v>
+        <v>1.55880041439152</v>
       </c>
       <c r="V34">
-        <v>6352.6049999999996</v>
+        <v>6.3526049999999996</v>
       </c>
       <c r="W34">
-        <v>2088.0002899797701</v>
+        <v>2.0880002899797701</v>
       </c>
       <c r="X34">
-        <v>7245.1706249999997</v>
+        <v>7.2451706250000001</v>
       </c>
       <c r="Y34">
-        <v>2381.3724237463098</v>
+        <v>2.3813724237463099</v>
       </c>
       <c r="Z34" s="4"/>
       <c r="AA34" s="4"/>
@@ -4602,76 +4602,76 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="B35">
-        <v>9962.2266502682705</v>
+        <v>9.9622266502682706</v>
       </c>
       <c r="C35">
-        <v>3274.4255521324499</v>
+        <v>3.2744255521324499</v>
       </c>
       <c r="D35">
-        <v>12838.513903618201</v>
+        <v>12.8385139036182</v>
       </c>
       <c r="E35">
-        <v>4219.8154542371603</v>
+        <v>4.2198154542371604</v>
       </c>
       <c r="F35">
-        <v>5153.26578051263</v>
+        <v>5.1532657805126298</v>
       </c>
       <c r="G35">
-        <v>1693.79655181665</v>
+        <v>1.69379655181665</v>
       </c>
       <c r="H35">
-        <v>5879.6216432865704</v>
+        <v>5.87962164328657</v>
       </c>
       <c r="I35">
-        <v>1932.5381786139201</v>
+        <v>1.93253817861392</v>
       </c>
       <c r="J35">
-        <v>2616.2795991983899</v>
+        <v>2.61627959919839</v>
       </c>
       <c r="K35">
-        <v>859.92951896023897</v>
+        <v>0.85992951896023895</v>
       </c>
       <c r="L35">
-        <v>9411.2303807615208</v>
+        <v>9.4112303807615199</v>
       </c>
       <c r="M35">
-        <v>3093.3218363327301</v>
+        <v>3.0933218363327302</v>
       </c>
       <c r="N35">
-        <v>13246.1133787575</v>
+        <v>13.246113378757499</v>
       </c>
       <c r="O35">
-        <v>4353.78692299468</v>
+        <v>4.3537869229946802</v>
       </c>
       <c r="P35">
-        <v>7788.9929191716701</v>
+        <v>7.7889929191716698</v>
       </c>
       <c r="Q35">
-        <v>2560.11816788244</v>
+        <v>2.5601181678824401</v>
       </c>
       <c r="R35">
-        <v>2930.8515483870901</v>
+        <v>2.9308515483870901</v>
       </c>
       <c r="S35">
-        <v>963.32431859369797</v>
+        <v>0.96332431859369805</v>
       </c>
       <c r="T35">
-        <v>5370.7825571142203</v>
+        <v>5.3707825571142198</v>
       </c>
       <c r="U35">
-        <v>1765.2908588953301</v>
+        <v>1.76529085889533</v>
       </c>
       <c r="V35">
-        <v>7156.9616129032202</v>
+        <v>7.1569616129032196</v>
       </c>
       <c r="W35">
-        <v>2352.3795235365601</v>
+        <v>2.3523795235365599</v>
       </c>
       <c r="X35">
-        <v>8162.5424596774101</v>
+        <v>8.1625424596774199</v>
       </c>
       <c r="Y35">
-        <v>2682.89796434354</v>
+        <v>2.6828979643435402</v>
       </c>
       <c r="Z35" s="4"/>
       <c r="AA35" s="4"/>
@@ -4726,76 +4726,76 @@
         <v>0.34375</v>
       </c>
       <c r="B36">
-        <v>11186.666922037601</v>
+        <v>11.186666922037601</v>
       </c>
       <c r="C36">
-        <v>3676.8796072039199</v>
+        <v>3.67687960720392</v>
       </c>
       <c r="D36">
-        <v>14252.985806255299</v>
+        <v>14.2529858062553</v>
       </c>
       <c r="E36">
-        <v>4684.7298858560798</v>
+        <v>4.68472988585608</v>
       </c>
       <c r="F36">
-        <v>5635.6551841586297</v>
+        <v>5.6356551841586304</v>
       </c>
       <c r="G36">
-        <v>1852.3502813017999</v>
+        <v>1.8523502813018</v>
       </c>
       <c r="H36">
-        <v>6644.9164328657298</v>
+        <v>6.6449164328657302</v>
       </c>
       <c r="I36">
-        <v>2184.0784117247899</v>
+        <v>2.1840784117247898</v>
       </c>
       <c r="J36">
-        <v>2956.81599198396</v>
+        <v>2.9568159919839601</v>
       </c>
       <c r="K36">
-        <v>971.85841850380302</v>
+        <v>0.97185841850380295</v>
       </c>
       <c r="L36">
-        <v>10636.2013076152</v>
+        <v>10.636201307615201</v>
       </c>
       <c r="M36">
-        <v>3495.9503092957598</v>
+        <v>3.4959503092957598</v>
       </c>
       <c r="N36">
-        <v>14970.2347875751</v>
+        <v>14.9702347875751</v>
       </c>
       <c r="O36">
-        <v>4920.4782254716201</v>
+        <v>4.9204782254716202</v>
       </c>
       <c r="P36">
-        <v>8802.8125250500998</v>
+        <v>8.8028125250501006</v>
       </c>
       <c r="Q36">
-        <v>2893.3445578533801</v>
+        <v>2.8933445578533799</v>
       </c>
       <c r="R36">
-        <v>3191.1687096774199</v>
+        <v>3.1911687096774202</v>
       </c>
       <c r="S36">
-        <v>1048.88643181511</v>
+        <v>1.0488864318151101</v>
       </c>
       <c r="T36">
-        <v>6069.8465711422796</v>
+        <v>6.0698465711422802</v>
       </c>
       <c r="U36">
-        <v>1995.0620888088899</v>
+        <v>1.9950620888088899</v>
       </c>
       <c r="V36">
-        <v>7792.6403225806398</v>
+        <v>7.79264032258064</v>
       </c>
       <c r="W36">
-        <v>2561.3170114081399</v>
+        <v>2.5613170114081401</v>
       </c>
       <c r="X36">
-        <v>8887.5364919354797</v>
+        <v>8.8875364919354798</v>
       </c>
       <c r="Y36">
-        <v>2921.1919790963002</v>
+        <v>2.9211919790962999</v>
       </c>
       <c r="Z36" s="4"/>
       <c r="AA36" s="4"/>
@@ -4850,76 +4850,76 @@
         <v>0.35416666666666702</v>
       </c>
       <c r="B37">
-        <v>12356.1359521947</v>
+        <v>12.3561359521947</v>
       </c>
       <c r="C37">
-        <v>4061.2654889154901</v>
+        <v>4.06126548891549</v>
       </c>
       <c r="D37">
-        <v>15690.068852909601</v>
+        <v>15.690068852909601</v>
       </c>
       <c r="E37">
-        <v>5157.0762411133401</v>
+        <v>5.15707624111334</v>
       </c>
       <c r="F37">
-        <v>5938.9130342539902</v>
+        <v>5.9389130342539902</v>
       </c>
       <c r="G37">
-        <v>1952.02631639885</v>
+        <v>1.95202631639885</v>
       </c>
       <c r="H37">
-        <v>7420.3252505009996</v>
+        <v>7.4203252505009996</v>
       </c>
       <c r="I37">
-        <v>2438.9429650970401</v>
+        <v>2.43894296509704</v>
       </c>
       <c r="J37">
-        <v>3301.85286573146</v>
+        <v>3.3018528657314601</v>
       </c>
       <c r="K37">
-        <v>1085.2665546052101</v>
+        <v>1.08526655460521</v>
       </c>
       <c r="L37">
-        <v>11877.361277555099</v>
+        <v>11.877361277555099</v>
       </c>
       <c r="M37">
-        <v>3903.8998633992701</v>
+        <v>3.9038998633992699</v>
       </c>
       <c r="N37">
-        <v>16717.141941883699</v>
+        <v>16.7171419418837</v>
       </c>
       <c r="O37">
-        <v>5494.6588403161004</v>
+        <v>5.4946588403160996</v>
       </c>
       <c r="P37">
-        <v>9830.0306279225097</v>
+        <v>9.8300306279225094</v>
       </c>
       <c r="Q37">
-        <v>3230.9748208195201</v>
+        <v>3.2309748208195201</v>
       </c>
       <c r="R37">
-        <v>3335.5990645161201</v>
+        <v>3.3355990645161202</v>
       </c>
       <c r="S37">
-        <v>1096.3583937559299</v>
+        <v>1.09635839375593</v>
       </c>
       <c r="T37">
-        <v>6778.1493166332602</v>
+        <v>6.77814931663326</v>
       </c>
       <c r="U37">
-        <v>2227.8699429063199</v>
+        <v>2.2278699429063198</v>
       </c>
       <c r="V37">
-        <v>8145.3304838709601</v>
+        <v>8.1453304838709606</v>
       </c>
       <c r="W37">
-        <v>2677.2406614772399</v>
+        <v>2.6772406614772399</v>
       </c>
       <c r="X37">
-        <v>9289.7809879032193</v>
+        <v>9.2897809879032192</v>
       </c>
       <c r="Y37">
-        <v>3053.40335131658</v>
+        <v>3.0534033513165801</v>
       </c>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
@@ -4974,76 +4974,76 @@
         <v>0.36458333333333298</v>
       </c>
       <c r="B38">
-        <v>13342.444770734999</v>
+        <v>13.342444770735</v>
       </c>
       <c r="C38">
-        <v>4385.4495203674396</v>
+        <v>4.3854495203674402</v>
       </c>
       <c r="D38">
-        <v>17060.320332521602</v>
+        <v>17.060320332521599</v>
       </c>
       <c r="E38">
-        <v>5607.4561225596299</v>
+        <v>5.60745612255963</v>
       </c>
       <c r="F38">
-        <v>5979.5280887177496</v>
+        <v>5.9795280887177498</v>
       </c>
       <c r="G38">
-        <v>1965.3758392320699</v>
+        <v>1.9653758392320699</v>
       </c>
       <c r="H38">
-        <v>8135.0498997996001</v>
+        <v>8.1350498997996006</v>
       </c>
       <c r="I38">
-        <v>2673.8615969010302</v>
+        <v>2.67386159690103</v>
       </c>
       <c r="J38">
-        <v>3619.88685370741</v>
+        <v>3.6198868537074098</v>
       </c>
       <c r="K38">
-        <v>1189.7992713595499</v>
+        <v>1.18979927135955</v>
       </c>
       <c r="L38">
-        <v>13021.3869889779</v>
+        <v>13.0213869889779</v>
       </c>
       <c r="M38">
-        <v>4279.92293065991</v>
+        <v>4.27992293065991</v>
       </c>
       <c r="N38">
-        <v>18327.334623246399</v>
+        <v>18.327334623246401</v>
       </c>
       <c r="O38">
-        <v>6023.9035809553698</v>
+        <v>6.0239035809553698</v>
       </c>
       <c r="P38">
-        <v>10776.8577488309</v>
+        <v>10.776857748830899</v>
       </c>
       <c r="Q38">
-        <v>3542.1818458144098</v>
+        <v>3.5421818458144099</v>
       </c>
       <c r="R38">
-        <v>3315.0477096774198</v>
+        <v>3.3150477096774198</v>
       </c>
       <c r="S38">
-        <v>1089.6034900805601</v>
+        <v>1.08960349008056</v>
       </c>
       <c r="T38">
-        <v>7431.0196733466901</v>
+        <v>7.4310196733466896</v>
       </c>
       <c r="U38">
-        <v>2442.4580519004799</v>
+        <v>2.4424580519004802</v>
       </c>
       <c r="V38">
-        <v>8095.1453225806399</v>
+        <v>8.09514532258064</v>
       </c>
       <c r="W38">
-        <v>2660.7455966452699</v>
+        <v>2.66074559664527</v>
       </c>
       <c r="X38">
-        <v>9232.54461693548</v>
+        <v>9.2325446169354795</v>
       </c>
       <c r="Y38">
-        <v>3034.5906659413599</v>
+        <v>3.03459066594136</v>
       </c>
       <c r="Z38" s="4"/>
       <c r="AA38" s="4"/>
@@ -5098,76 +5098,76 @@
         <v>0.375</v>
       </c>
       <c r="B39">
-        <v>14073.412376365601</v>
+        <v>14.073412376365599</v>
       </c>
       <c r="C39">
-        <v>4625.7069537388697</v>
+        <v>4.6257069537388702</v>
       </c>
       <c r="D39">
-        <v>18312.047632509599</v>
+        <v>18.3120476325096</v>
       </c>
       <c r="E39">
-        <v>6018.8789900841603</v>
+        <v>6.0188789900841604</v>
       </c>
       <c r="F39">
-        <v>5712.5688601396296</v>
+        <v>5.7125688601396298</v>
       </c>
       <c r="G39">
-        <v>1877.63058406763</v>
+        <v>1.8776305840676299</v>
       </c>
       <c r="H39">
-        <v>8748.6342685370691</v>
+        <v>8.7486342685370708</v>
       </c>
       <c r="I39">
-        <v>2875.53702609124</v>
+        <v>2.8755370260912398</v>
       </c>
       <c r="J39">
-        <v>3892.9160320641199</v>
+        <v>3.8929160320641198</v>
       </c>
       <c r="K39">
-        <v>1279.53962253544</v>
+        <v>1.2795396225354401</v>
       </c>
       <c r="L39">
-        <v>14003.522269539</v>
+        <v>14.003522269538999</v>
       </c>
       <c r="M39">
-        <v>4602.7351865157298</v>
+        <v>4.60273518651573</v>
       </c>
       <c r="N39">
-        <v>19709.669849699399</v>
+        <v>19.709669849699399</v>
       </c>
       <c r="O39">
-        <v>6478.2551979192604</v>
+        <v>6.4782551979192604</v>
       </c>
       <c r="P39">
-        <v>11589.6998997995</v>
+        <v>11.5896998997995</v>
       </c>
       <c r="Q39">
-        <v>3809.3501408571901</v>
+        <v>3.8093501408571901</v>
       </c>
       <c r="R39">
-        <v>3103.2545806451599</v>
+        <v>3.1032545806451601</v>
       </c>
       <c r="S39">
-        <v>1019.99045498156</v>
+        <v>1.0199904549815599</v>
       </c>
       <c r="T39">
-        <v>7991.50271543086</v>
+        <v>7.99150271543086</v>
       </c>
       <c r="U39">
-        <v>2626.6799190558399</v>
+        <v>2.6266799190558401</v>
       </c>
       <c r="V39">
-        <v>7577.9593548387002</v>
+        <v>7.5779593548386996</v>
       </c>
       <c r="W39">
-        <v>2490.7547896269498</v>
+        <v>2.49075478962695</v>
       </c>
       <c r="X39">
-        <v>8642.6920161290309</v>
+        <v>8.6426920161290308</v>
       </c>
       <c r="Y39">
-        <v>2840.7154916578702</v>
+        <v>2.8407154916578699</v>
       </c>
       <c r="Z39" s="4"/>
       <c r="AA39" s="4"/>
@@ -5222,76 +5222,76 @@
         <v>0.38541666666666702</v>
       </c>
       <c r="B40">
-        <v>14588.810505753399</v>
+        <v>14.588810505753401</v>
       </c>
       <c r="C40">
-        <v>4795.1101267075601</v>
+        <v>4.7951101267075602</v>
       </c>
       <c r="D40">
-        <v>19452.599769898501</v>
+        <v>19.452599769898502</v>
       </c>
       <c r="E40">
-        <v>6393.7603487716697</v>
+        <v>6.3937603487716697</v>
       </c>
       <c r="F40">
-        <v>5229.7880564758498</v>
+        <v>5.2297880564758499</v>
       </c>
       <c r="G40">
-        <v>1718.9482076178699</v>
+        <v>1.7189482076178699</v>
       </c>
       <c r="H40">
-        <v>9264.4496993987905</v>
+        <v>9.2644496993987904</v>
       </c>
       <c r="I40">
-        <v>3045.0773594214802</v>
+        <v>3.0450773594214802</v>
       </c>
       <c r="J40">
-        <v>4122.4405611222401</v>
+        <v>4.1224405611222403</v>
       </c>
       <c r="K40">
-        <v>1354.9806869855099</v>
+        <v>1.3549806869855101</v>
       </c>
       <c r="L40">
-        <v>14829.1634669338</v>
+        <v>14.829163466933799</v>
       </c>
       <c r="M40">
-        <v>4874.1103246802404</v>
+        <v>4.87411032468024</v>
       </c>
       <c r="N40">
-        <v>20871.742869739399</v>
+        <v>20.8717428697394</v>
       </c>
       <c r="O40">
-        <v>6860.2101286636298</v>
+        <v>6.8602101286636303</v>
       </c>
       <c r="P40">
-        <v>12273.023246492899</v>
+        <v>12.273023246492899</v>
       </c>
       <c r="Q40">
-        <v>4033.9476636129298</v>
+        <v>4.0339476636129303</v>
       </c>
       <c r="R40">
-        <v>2759.0193870967701</v>
+        <v>2.7590193870967701</v>
       </c>
       <c r="S40">
-        <v>906.84581841903798</v>
+        <v>0.906845818419038</v>
       </c>
       <c r="T40">
-        <v>8462.6780200400699</v>
+        <v>8.4626780200400695</v>
       </c>
       <c r="U40">
-        <v>2781.5477524337002</v>
+        <v>2.7815477524337</v>
       </c>
       <c r="V40">
-        <v>6737.3579032258003</v>
+        <v>6.7373579032258002</v>
       </c>
       <c r="W40">
-        <v>2214.4624536915098</v>
+        <v>2.2144624536915098</v>
       </c>
       <c r="X40">
-        <v>7683.9828024193503</v>
+        <v>7.6839828024193499</v>
       </c>
       <c r="Y40">
-        <v>2525.6030116229699</v>
+        <v>2.52560301162297</v>
       </c>
       <c r="Z40" s="4"/>
       <c r="AA40" s="4"/>
@@ -5346,76 +5346,76 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B41">
-        <v>14960.527439007001</v>
+        <v>14.960527439007</v>
       </c>
       <c r="C41">
-        <v>4917.2875742938604</v>
+        <v>4.9172875742938604</v>
       </c>
       <c r="D41">
-        <v>20515.6218774382</v>
+        <v>20.5156218774382</v>
       </c>
       <c r="E41">
-        <v>6743.1588189737104</v>
+        <v>6.7431588189737104</v>
       </c>
       <c r="F41">
-        <v>4658.9192376688798</v>
+        <v>4.6589192376688802</v>
       </c>
       <c r="G41">
-        <v>1531.31270073378</v>
+        <v>1.5313127007337799</v>
       </c>
       <c r="H41">
-        <v>9699.3529058116201</v>
+        <v>9.6993529058116206</v>
       </c>
       <c r="I41">
-        <v>3188.0231306607002</v>
+        <v>3.1880231306606999</v>
       </c>
       <c r="J41">
-        <v>4315.9612424849702</v>
+        <v>4.3159612424849696</v>
       </c>
       <c r="K41">
-        <v>1418.58785897282</v>
+        <v>1.41858785897282</v>
       </c>
       <c r="L41">
-        <v>15525.2923196392</v>
+        <v>15.525292319639201</v>
       </c>
       <c r="M41">
-        <v>5102.9168137209099</v>
+        <v>5.1029168137209098</v>
       </c>
       <c r="N41">
-        <v>21851.529925851701</v>
+        <v>21.8515299258517</v>
       </c>
       <c r="O41">
-        <v>7182.2505604677099</v>
+        <v>7.1822505604677103</v>
       </c>
       <c r="P41">
-        <v>12849.1586172344</v>
+        <v>12.8491586172344</v>
       </c>
       <c r="Q41">
-        <v>4223.3142024069903</v>
+        <v>4.2233142024069901</v>
       </c>
       <c r="R41">
-        <v>2363.4058064516098</v>
+        <v>2.3634058064516101</v>
       </c>
       <c r="S41">
-        <v>776.813922668077</v>
+        <v>0.77681392266807703</v>
       </c>
       <c r="T41">
-        <v>8859.9434729458899</v>
+        <v>8.8599434729458899</v>
       </c>
       <c r="U41">
-        <v>2912.12259234052</v>
+        <v>2.9121225923405198</v>
       </c>
       <c r="V41">
-        <v>5771.2935483870897</v>
+        <v>5.7712935483870904</v>
       </c>
       <c r="W41">
-        <v>1896.9324556761501</v>
+        <v>1.89693245567615</v>
       </c>
       <c r="X41">
-        <v>6582.1826612903196</v>
+        <v>6.5821826612903198</v>
       </c>
       <c r="Y41">
-        <v>2163.4588181500299</v>
+        <v>2.1634588181500298</v>
       </c>
       <c r="Z41" s="4"/>
       <c r="AA41" s="4"/>
@@ -5470,76 +5470,76 @@
         <v>0.40625</v>
       </c>
       <c r="B42">
-        <v>15263.4596445148</v>
+        <v>15.2634596445148</v>
       </c>
       <c r="C42">
-        <v>5016.8565751910401</v>
+        <v>5.0168565751910403</v>
       </c>
       <c r="D42">
-        <v>21523.977615174401</v>
+        <v>21.523977615174399</v>
       </c>
       <c r="E42">
-        <v>7074.5893223334897</v>
+        <v>7.0745893223334901</v>
       </c>
       <c r="F42">
-        <v>4123.6008490367803</v>
+        <v>4.1236008490367801</v>
       </c>
       <c r="G42">
-        <v>1355.3620551804499</v>
+        <v>1.3553620551804499</v>
       </c>
       <c r="H42">
-        <v>10073.5719438877</v>
+        <v>10.0735719438877</v>
       </c>
       <c r="I42">
-        <v>3311.0229803316502</v>
+        <v>3.31102298033165</v>
       </c>
       <c r="J42">
-        <v>4482.4790380761497</v>
+        <v>4.4824790380761499</v>
       </c>
       <c r="K42">
-        <v>1473.31961161307</v>
+        <v>1.47331961161307</v>
       </c>
       <c r="L42">
-        <v>16124.2869138276</v>
+        <v>16.1242869138276</v>
       </c>
       <c r="M42">
-        <v>5299.7968159186903</v>
+        <v>5.2997968159186897</v>
       </c>
       <c r="N42">
-        <v>22694.602509018001</v>
+        <v>22.694602509018001</v>
       </c>
       <c r="O42">
-        <v>7459.35511806657</v>
+        <v>7.4593551180665703</v>
       </c>
       <c r="P42">
-        <v>13344.903006012</v>
+        <v>13.344903006012</v>
       </c>
       <c r="Q42">
-        <v>4386.25750322978</v>
+        <v>4.3862575032297801</v>
       </c>
       <c r="R42">
-        <v>1994.62316129032</v>
+        <v>1.99462316129032</v>
       </c>
       <c r="S42">
-        <v>655.60092893774402</v>
+        <v>0.65560092893774402</v>
       </c>
       <c r="T42">
-        <v>9201.7765370741399</v>
+        <v>9.2017765370741404</v>
       </c>
       <c r="U42">
-        <v>3024.4776871440699</v>
+        <v>3.0244776871440702</v>
       </c>
       <c r="V42">
-        <v>4870.7487096774103</v>
+        <v>4.87074870967741</v>
       </c>
       <c r="W42">
-        <v>1600.9376811914201</v>
+        <v>1.60093768119142</v>
       </c>
       <c r="X42">
-        <v>5555.1077822580601</v>
+        <v>5.5551077822580597</v>
       </c>
       <c r="Y42">
-        <v>1825.87563058363</v>
+        <v>1.8258756305836299</v>
       </c>
       <c r="Z42" s="4"/>
       <c r="AA42" s="4"/>
@@ -5594,76 +5594,76 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B43">
-        <v>15559.623708837</v>
+        <v>15.559623708837</v>
       </c>
       <c r="C43">
-        <v>5114.20099565892</v>
+        <v>5.1142009956589201</v>
       </c>
       <c r="D43">
-        <v>22507.849115664601</v>
+        <v>22.507849115664602</v>
       </c>
       <c r="E43">
-        <v>7397.9722460830899</v>
+        <v>7.3979722460830901</v>
       </c>
       <c r="F43">
-        <v>3725.8295351994302</v>
+        <v>3.7258295351994302</v>
       </c>
       <c r="G43">
-        <v>1224.6209468259999</v>
+        <v>1.2246209468260001</v>
       </c>
       <c r="H43">
-        <v>10403.9635270541</v>
+        <v>10.403963527054101</v>
       </c>
       <c r="I43">
-        <v>3419.6174422033</v>
+        <v>3.4196174422032999</v>
       </c>
       <c r="J43">
-        <v>4629.4947494989901</v>
+        <v>4.6294947494989902</v>
       </c>
       <c r="K43">
-        <v>1521.64133916932</v>
+        <v>1.52164133916932</v>
       </c>
       <c r="L43">
-        <v>16653.128987975899</v>
+        <v>16.653128987975901</v>
       </c>
       <c r="M43">
-        <v>5473.6187998410596</v>
+        <v>5.4736187998410601</v>
       </c>
       <c r="N43">
-        <v>23438.936861723399</v>
+        <v>23.438936861723398</v>
       </c>
       <c r="O43">
-        <v>7704.00598873944</v>
+        <v>7.7040059887394401</v>
       </c>
       <c r="P43">
-        <v>13782.5872411489</v>
+        <v>13.782587241148899</v>
       </c>
       <c r="Q43">
-        <v>4530.1173544066596</v>
+        <v>4.5301173544066602</v>
       </c>
       <c r="R43">
-        <v>1717.17987096774</v>
+        <v>1.7171798709677399</v>
       </c>
       <c r="S43">
-        <v>564.40972932018803</v>
+        <v>0.56440972932018796</v>
       </c>
       <c r="T43">
-        <v>9503.5750981963902</v>
+        <v>9.5035750981963893</v>
       </c>
       <c r="U43">
-        <v>3123.6740771507998</v>
+        <v>3.1236740771507998</v>
       </c>
       <c r="V43">
-        <v>4193.2490322580597</v>
+        <v>4.19324903225806</v>
       </c>
       <c r="W43">
-        <v>1378.25430595987</v>
+        <v>1.37825430595987</v>
       </c>
       <c r="X43">
-        <v>4782.4167741935398</v>
+        <v>4.7824167741935399</v>
       </c>
       <c r="Y43">
-        <v>1571.9043780181901</v>
+        <v>1.5719043780181901</v>
       </c>
       <c r="Z43" s="4"/>
       <c r="AA43" s="4"/>
@@ -5718,76 +5718,76 @@
         <v>0.42708333333333298</v>
       </c>
       <c r="B44">
-        <v>15880.3444874587</v>
+        <v>15.8803444874587</v>
       </c>
       <c r="C44">
-        <v>5219.6168177924801</v>
+        <v>5.2196168177924802</v>
       </c>
       <c r="D44">
-        <v>23461.2175008296</v>
+        <v>23.461217500829601</v>
       </c>
       <c r="E44">
-        <v>7711.3292806668796</v>
+        <v>7.7113292806668801</v>
       </c>
       <c r="F44">
-        <v>3475.6463221200402</v>
+        <v>3.4756463221200402</v>
       </c>
       <c r="G44">
-        <v>1142.3897013042299</v>
+        <v>1.1423897013042299</v>
       </c>
       <c r="H44">
-        <v>10710.7557114228</v>
+        <v>10.7107557114228</v>
       </c>
       <c r="I44">
-        <v>3520.4551567984099</v>
+        <v>3.5204551567984099</v>
       </c>
       <c r="J44">
-        <v>4766.0093386773497</v>
+        <v>4.7660093386773497</v>
       </c>
       <c r="K44">
-        <v>1566.5115147572701</v>
+        <v>1.5665115147572699</v>
       </c>
       <c r="L44">
-        <v>17144.196628256501</v>
+        <v>17.144196628256498</v>
       </c>
       <c r="M44">
-        <v>5635.02492776897</v>
+        <v>5.6350249277689697</v>
       </c>
       <c r="N44">
-        <v>24130.104474949901</v>
+        <v>24.130104474949899</v>
       </c>
       <c r="O44">
-        <v>7931.1817972213803</v>
+        <v>7.9311817972213898</v>
       </c>
       <c r="P44">
-        <v>14189.008316633201</v>
+        <v>14.189008316633201</v>
       </c>
       <c r="Q44">
-        <v>4663.7015019280498</v>
+        <v>4.6637015019280499</v>
       </c>
       <c r="R44">
-        <v>1536.2137741935401</v>
+        <v>1.53621377419354</v>
       </c>
       <c r="S44">
-        <v>504.92904973424999</v>
+        <v>0.50492904973425001</v>
       </c>
       <c r="T44">
-        <v>9783.8166192384706</v>
+        <v>9.7838166192384701</v>
       </c>
       <c r="U44">
-        <v>3215.7850107284798</v>
+        <v>3.2157850107284802</v>
       </c>
       <c r="V44">
-        <v>3751.3408064516102</v>
+        <v>3.7513408064516098</v>
       </c>
       <c r="W44">
-        <v>1233.0060961895001</v>
+        <v>1.2330060961895</v>
       </c>
       <c r="X44">
-        <v>4278.4187298387096</v>
+        <v>4.2784187298387097</v>
       </c>
       <c r="Y44">
-        <v>1406.24823179752</v>
+        <v>1.40624823179752</v>
       </c>
       <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
@@ -5842,76 +5842,76 @@
         <v>0.4375</v>
       </c>
       <c r="B45">
-        <v>16232.2637226388</v>
+        <v>16.232263722638798</v>
       </c>
       <c r="C45">
-        <v>5335.2870767028598</v>
+        <v>5.3352870767028602</v>
       </c>
       <c r="D45">
-        <v>24362.361965391501</v>
+        <v>24.3623619653915</v>
       </c>
       <c r="E45">
-        <v>8007.5211426382702</v>
+        <v>8.0075211426382698</v>
       </c>
       <c r="F45">
-        <v>3354.5535070544302</v>
+        <v>3.3545535070544301</v>
       </c>
       <c r="G45">
-        <v>1102.5884177408</v>
+        <v>1.1025884177408001</v>
       </c>
       <c r="H45">
-        <v>11004.0625250501</v>
+        <v>11.004062525050101</v>
       </c>
       <c r="I45">
-        <v>3616.8604443783502</v>
+        <v>3.6168604443783501</v>
       </c>
       <c r="J45">
-        <v>4896.5232865731396</v>
+        <v>4.8965232865731396</v>
       </c>
       <c r="K45">
-        <v>1609.4093749347601</v>
+        <v>1.60940937493476</v>
       </c>
       <c r="L45">
-        <v>17613.678877755501</v>
+        <v>17.6136788777555</v>
       </c>
       <c r="M45">
-        <v>5789.3362808429101</v>
+        <v>5.7893362808429103</v>
       </c>
       <c r="N45">
-        <v>24790.8910941883</v>
+        <v>24.7908910941883</v>
       </c>
       <c r="O45">
-        <v>8148.3718558799501</v>
+        <v>8.1483718558799492</v>
       </c>
       <c r="P45">
-        <v>14577.5647294589</v>
+        <v>14.577564729458899</v>
       </c>
       <c r="Q45">
-        <v>4791.4138187891604</v>
+        <v>4.7914138187891604</v>
       </c>
       <c r="R45">
-        <v>1439.16570967741</v>
+        <v>1.43916570967741</v>
       </c>
       <c r="S45">
-        <v>473.03089348942598</v>
+        <v>0.47303089348942601</v>
       </c>
       <c r="T45">
-        <v>10051.739831663301</v>
+        <v>10.0517398316633</v>
       </c>
       <c r="U45">
-        <v>3303.8471120609902</v>
+        <v>3.30384711206099</v>
       </c>
       <c r="V45">
-        <v>3514.3553225806399</v>
+        <v>3.5143553225806401</v>
       </c>
       <c r="W45">
-        <v>1155.1127344829899</v>
+        <v>1.1551127344829899</v>
       </c>
       <c r="X45">
-        <v>4008.13586693548</v>
+        <v>4.0081358669354801</v>
       </c>
       <c r="Y45">
-        <v>1317.4105508589901</v>
+        <v>1.3174105508589899</v>
       </c>
       <c r="Z45" s="4"/>
       <c r="AA45" s="4"/>
@@ -5966,76 +5966,76 @@
         <v>0.44791666666666702</v>
       </c>
       <c r="B46">
-        <v>16641.204377496899</v>
+        <v>16.641204377496901</v>
       </c>
       <c r="C46">
-        <v>5469.6993699161503</v>
+        <v>5.4696993699161602</v>
       </c>
       <c r="D46">
-        <v>25213.791184881102</v>
+        <v>25.213791184881099</v>
       </c>
       <c r="E46">
-        <v>8287.3723937693594</v>
+        <v>8.2873723937693597</v>
       </c>
       <c r="F46">
-        <v>3346.3100053736498</v>
+        <v>3.3463100053736499</v>
       </c>
       <c r="G46">
-        <v>1099.87890976731</v>
+        <v>1.0998789097673101</v>
       </c>
       <c r="H46">
-        <v>11307.483366733401</v>
+        <v>11.3074833667334</v>
       </c>
       <c r="I46">
-        <v>3716.5900522196598</v>
+        <v>3.7165900522196602</v>
       </c>
       <c r="J46">
-        <v>5031.5377154308599</v>
+        <v>5.0315377154308596</v>
       </c>
       <c r="K46">
-        <v>1653.7864716700899</v>
+        <v>1.6537864716700901</v>
       </c>
       <c r="L46">
-        <v>18099.3501703406</v>
+        <v>18.0993501703406</v>
       </c>
       <c r="M46">
-        <v>5948.96871505733</v>
+        <v>5.9489687150573296</v>
       </c>
       <c r="N46">
-        <v>25474.463458917799</v>
+        <v>25.4744634589178</v>
       </c>
       <c r="O46">
-        <v>8373.0512269060491</v>
+        <v>8.3730512269060497</v>
       </c>
       <c r="P46">
-        <v>14979.5196392785</v>
+        <v>14.9795196392785</v>
       </c>
       <c r="Q46">
-        <v>4923.5300086454699</v>
+        <v>4.9235300086454696</v>
       </c>
       <c r="R46">
-        <v>1414.0473870967701</v>
+        <v>1.41404738709677</v>
       </c>
       <c r="S46">
-        <v>464.774900108412</v>
+        <v>0.46477490010841199</v>
       </c>
       <c r="T46">
-        <v>10328.901775551099</v>
+        <v>10.328901775551</v>
       </c>
       <c r="U46">
-        <v>3394.9458375773802</v>
+        <v>3.3949458375773802</v>
       </c>
       <c r="V46">
-        <v>3453.0179032258002</v>
+        <v>3.4530179032257999</v>
       </c>
       <c r="W46">
-        <v>1134.95209968836</v>
+        <v>1.13495209968836</v>
       </c>
       <c r="X46">
-        <v>3938.18030241935</v>
+        <v>3.93818030241935</v>
       </c>
       <c r="Y46">
-        <v>1294.41726873373</v>
+        <v>1.2944172687337301</v>
       </c>
       <c r="Z46" s="4"/>
       <c r="AA46" s="4"/>
@@ -6090,76 +6090,76 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="B47">
-        <v>17102.685769345098</v>
+        <v>17.102685769345101</v>
       </c>
       <c r="C47">
-        <v>5621.3809682524798</v>
+        <v>5.6213809682524802</v>
       </c>
       <c r="D47">
-        <v>25987.933736144401</v>
+        <v>25.987933736144399</v>
       </c>
       <c r="E47">
-        <v>8541.8207455122192</v>
+        <v>8.5418207455122204</v>
       </c>
       <c r="F47">
-        <v>3427.29614600168</v>
+        <v>3.4272961460016802</v>
       </c>
       <c r="G47">
-        <v>1126.4977669315199</v>
+        <v>1.1264977669315199</v>
       </c>
       <c r="H47">
-        <v>11624.3895791583</v>
+        <v>11.624389579158301</v>
       </c>
       <c r="I47">
-        <v>3820.75208707615</v>
+        <v>3.82075208707615</v>
       </c>
       <c r="J47">
-        <v>5172.5527855711398</v>
+        <v>5.1725527855711402</v>
       </c>
       <c r="K47">
-        <v>1700.1358838158801</v>
+        <v>1.70013588381588</v>
       </c>
       <c r="L47">
-        <v>18606.606853707399</v>
+        <v>18.606606853707401</v>
       </c>
       <c r="M47">
-        <v>6115.69592412572</v>
+        <v>6.1156959241257196</v>
       </c>
       <c r="N47">
-        <v>26188.4168176352</v>
+        <v>26.188416817635201</v>
       </c>
       <c r="O47">
-        <v>8607.7163477555405</v>
+        <v>8.6077163477555398</v>
       </c>
       <c r="P47">
-        <v>15399.3392117568</v>
+        <v>15.3993392117568</v>
       </c>
       <c r="Q47">
-        <v>5061.51802916207</v>
+        <v>5.0615180291620696</v>
       </c>
       <c r="R47">
-        <v>1445.4452903225799</v>
+        <v>1.4454452903225801</v>
       </c>
       <c r="S47">
-        <v>475.094891834679</v>
+        <v>0.47509489183467901</v>
       </c>
       <c r="T47">
-        <v>10618.382028056099</v>
+        <v>10.6183820280561</v>
       </c>
       <c r="U47">
-        <v>3490.0933953389399</v>
+        <v>3.4900933953389401</v>
       </c>
       <c r="V47">
-        <v>3529.6896774193501</v>
+        <v>3.5296896774193498</v>
       </c>
       <c r="W47">
-        <v>1160.1528931816499</v>
+        <v>1.16015289318165</v>
       </c>
       <c r="X47">
-        <v>4025.6247580645099</v>
+        <v>4.0256247580645104</v>
       </c>
       <c r="Y47">
-        <v>1323.15887139031</v>
+        <v>1.32315887139031</v>
       </c>
       <c r="Z47" s="4"/>
       <c r="AA47" s="4"/>
@@ -6214,76 +6214,76 @@
         <v>0.46875</v>
       </c>
       <c r="B48">
-        <v>17575.455908397402</v>
+        <v>17.575455908397402</v>
       </c>
       <c r="C48">
-        <v>5776.7729983621703</v>
+        <v>5.7767729983621701</v>
       </c>
       <c r="D48">
-        <v>26662.4215853393</v>
+        <v>26.662421585339299</v>
       </c>
       <c r="E48">
-        <v>8763.5141806788797</v>
+        <v>8.7635141806788805</v>
       </c>
       <c r="F48">
-        <v>3549.6515544799199</v>
+        <v>3.5496515544799201</v>
       </c>
       <c r="G48">
-        <v>1166.7140448809901</v>
+        <v>1.1667140448809901</v>
       </c>
       <c r="H48">
-        <v>11937.9244488977</v>
+        <v>11.9379244488977</v>
       </c>
       <c r="I48">
-        <v>3923.80601517884</v>
+        <v>3.9238060151788399</v>
       </c>
       <c r="J48">
-        <v>5312.0676953907796</v>
+        <v>5.3120676953907804</v>
       </c>
       <c r="K48">
-        <v>1745.99221710906</v>
+        <v>1.7459922171090601</v>
       </c>
       <c r="L48">
-        <v>19108.467189378702</v>
+        <v>19.1084671893787</v>
       </c>
       <c r="M48">
-        <v>6280.6494394806195</v>
+        <v>6.2806494394806203</v>
       </c>
       <c r="N48">
-        <v>26894.774927855698</v>
+        <v>26.8947749278557</v>
       </c>
       <c r="O48">
-        <v>8839.8850311491806</v>
+        <v>8.8398850311491799</v>
       </c>
       <c r="P48">
-        <v>15814.6926185704</v>
+        <v>15.814692618570399</v>
       </c>
       <c r="Q48">
-        <v>5198.0380920136004</v>
+        <v>5.1980380920135998</v>
       </c>
       <c r="R48">
-        <v>1503.67412903225</v>
+        <v>1.50367412903225</v>
       </c>
       <c r="S48">
-        <v>494.23378558157401</v>
+        <v>0.49423378558157399</v>
       </c>
       <c r="T48">
-        <v>10904.7827034068</v>
+        <v>10.9047827034068</v>
       </c>
       <c r="U48">
-        <v>3584.22874503921</v>
+        <v>3.5842287450392099</v>
       </c>
       <c r="V48">
-        <v>3671.8809677419299</v>
+        <v>3.67188096774193</v>
       </c>
       <c r="W48">
-        <v>1206.88891020555</v>
+        <v>1.20688891020555</v>
       </c>
       <c r="X48">
-        <v>4187.7944758064496</v>
+        <v>4.1877944758064496</v>
       </c>
       <c r="Y48">
-        <v>1376.4614799534199</v>
+        <v>1.3764614799534201</v>
       </c>
       <c r="Z48" s="4"/>
       <c r="AA48" s="4"/>
@@ -6338,76 +6338,76 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B49">
-        <v>18005.438363792098</v>
+        <v>18.005438363792098</v>
       </c>
       <c r="C49">
-        <v>5918.10139695618</v>
+        <v>5.91810139695618</v>
       </c>
       <c r="D49">
-        <v>27212.2086426856</v>
+        <v>27.212208642685599</v>
       </c>
       <c r="E49">
-        <v>8944.2204476616607</v>
+        <v>8.9442204476616602</v>
       </c>
       <c r="F49">
-        <v>3655.9564888244199</v>
+        <v>3.6559564888244198</v>
       </c>
       <c r="G49">
-        <v>1201.65478710211</v>
+        <v>1.2016547871021099</v>
       </c>
       <c r="H49">
-        <v>12224.488577154299</v>
+        <v>12.2244885771543</v>
       </c>
       <c r="I49">
-        <v>4017.9950892511902</v>
+        <v>4.0179950892511904</v>
       </c>
       <c r="J49">
-        <v>5439.5813226452901</v>
+        <v>5.4395813226452896</v>
       </c>
       <c r="K49">
-        <v>1787.90391958132</v>
+        <v>1.78790391958132</v>
       </c>
       <c r="L49">
-        <v>19567.156743486899</v>
+        <v>19.567156743486901</v>
       </c>
       <c r="M49">
-        <v>6431.4134051275696</v>
+        <v>6.4314134051275698</v>
       </c>
       <c r="N49">
-        <v>27540.371050100199</v>
+        <v>27.540371050100099</v>
       </c>
       <c r="O49">
-        <v>9052.0822148960506</v>
+        <v>9.0520822148960498</v>
       </c>
       <c r="P49">
-        <v>16194.3167000668</v>
+        <v>16.1943167000668</v>
       </c>
       <c r="Q49">
-        <v>5322.8144935445698</v>
+        <v>5.3228144935445698</v>
       </c>
       <c r="R49">
-        <v>1553.3399032258001</v>
+        <v>1.5533399032258</v>
       </c>
       <c r="S49">
-        <v>510.55813613039601</v>
+        <v>0.51055813613039602</v>
       </c>
       <c r="T49">
-        <v>11166.546761523001</v>
+        <v>11.166546761523</v>
       </c>
       <c r="U49">
-        <v>3670.2664302491298</v>
+        <v>3.6702664302491299</v>
       </c>
       <c r="V49">
-        <v>3793.1617741935402</v>
+        <v>3.7931617741935399</v>
       </c>
       <c r="W49">
-        <v>1246.75198354947</v>
+        <v>1.24675198354947</v>
       </c>
       <c r="X49">
-        <v>4326.1157056451602</v>
+        <v>4.3261157056451598</v>
       </c>
       <c r="Y49">
-        <v>1421.9254696102</v>
+        <v>1.4219254696101999</v>
       </c>
       <c r="Z49" s="4"/>
       <c r="AA49" s="4"/>
@@ -6462,76 +6462,76 @@
         <v>0.48958333333333298</v>
       </c>
       <c r="B50">
-        <v>18339.577914344802</v>
+        <v>18.339577914344801</v>
       </c>
       <c r="C50">
-        <v>6027.9277561344597</v>
+        <v>6.02792775613446</v>
       </c>
       <c r="D50">
-        <v>27607.970329443498</v>
+        <v>27.6079703294435</v>
       </c>
       <c r="E50">
-        <v>9074.3010235377405</v>
+        <v>9.0743010235377408</v>
       </c>
       <c r="F50">
-        <v>3691.45364656732</v>
+        <v>3.6914536465673198</v>
       </c>
       <c r="G50">
-        <v>1213.32213863123</v>
+        <v>1.2133221386312301</v>
       </c>
       <c r="H50">
-        <v>12460.4825651302</v>
+        <v>12.460482565130199</v>
       </c>
       <c r="I50">
-        <v>4095.5625620166602</v>
+        <v>4.09556256201666</v>
       </c>
       <c r="J50">
-        <v>5544.5925450901796</v>
+        <v>5.5445925450901798</v>
       </c>
       <c r="K50">
-        <v>1822.4194392643601</v>
+        <v>1.82241943926436</v>
       </c>
       <c r="L50">
-        <v>19944.901082164299</v>
+        <v>19.9449010821643</v>
       </c>
       <c r="M50">
-        <v>6555.5719650721203</v>
+        <v>6.5555719650721196</v>
       </c>
       <c r="N50">
-        <v>28072.038444889698</v>
+        <v>28.072038444889699</v>
       </c>
       <c r="O50">
-        <v>9226.8328368052407</v>
+        <v>9.2268328368052401</v>
       </c>
       <c r="P50">
-        <v>16506.948296593098</v>
+        <v>16.506948296593102</v>
       </c>
       <c r="Q50">
-        <v>5425.5715300994898</v>
+        <v>5.4255715300994902</v>
       </c>
       <c r="R50">
-        <v>1560.7612258064501</v>
+        <v>1.56076122580645</v>
       </c>
       <c r="S50">
-        <v>512.99740690205897</v>
+        <v>0.51299740690205897</v>
       </c>
       <c r="T50">
-        <v>11382.117162324599</v>
+        <v>11.382117162324599</v>
       </c>
       <c r="U50">
-        <v>3741.1209945396499</v>
+        <v>3.7411209945396502</v>
       </c>
       <c r="V50">
-        <v>3811.2841935483798</v>
+        <v>3.8112841935483801</v>
       </c>
       <c r="W50">
-        <v>1252.7085347387899</v>
+        <v>1.2527085347387901</v>
       </c>
       <c r="X50">
-        <v>4346.7843951612804</v>
+        <v>4.3467843951612899</v>
       </c>
       <c r="Y50">
-        <v>1428.71893932903</v>
+        <v>1.42871893932903</v>
       </c>
       <c r="Z50" s="4"/>
       <c r="AA50" s="4"/>
@@ -6586,76 +6586,76 @@
         <v>0.5</v>
       </c>
       <c r="B51">
-        <v>18520.845381666499</v>
+        <v>18.520845381666501</v>
       </c>
       <c r="C51">
-        <v>6087.5074914291499</v>
+        <v>6.0875074914291503</v>
       </c>
       <c r="D51">
-        <v>27819.100376211201</v>
+        <v>27.8191003762112</v>
       </c>
       <c r="E51">
-        <v>9143.6961140359508</v>
+        <v>9.1436961140359596</v>
       </c>
       <c r="F51">
-        <v>3614.90083352188</v>
+        <v>3.61490083352188</v>
       </c>
       <c r="G51">
-        <v>1188.1604457764599</v>
+        <v>1.1881604457764601</v>
       </c>
       <c r="H51">
-        <v>12615.564328657299</v>
+        <v>12.6155643286573</v>
       </c>
       <c r="I51">
-        <v>4146.53547269111</v>
+        <v>4.1465354726911103</v>
       </c>
       <c r="J51">
-        <v>5613.5999198396703</v>
+        <v>5.6135999198396798</v>
       </c>
       <c r="K51">
-        <v>1845.1010664846399</v>
+        <v>1.8451010664846399</v>
       </c>
       <c r="L51">
-        <v>20193.133076152299</v>
+        <v>20.1931330761523</v>
       </c>
       <c r="M51">
-        <v>6637.1618758928198</v>
+        <v>6.6371618758928204</v>
       </c>
       <c r="N51">
-        <v>28421.419875751501</v>
+        <v>28.4214198757515</v>
       </c>
       <c r="O51">
-        <v>9341.6689597741406</v>
+        <v>9.3416689597741396</v>
       </c>
       <c r="P51">
-        <v>16712.391917167599</v>
+        <v>16.712391917167601</v>
       </c>
       <c r="Q51">
-        <v>5493.0975826927097</v>
+        <v>5.4930975826927098</v>
       </c>
       <c r="R51">
-        <v>1501.39064516129</v>
+        <v>1.5013906451612899</v>
       </c>
       <c r="S51">
-        <v>493.48324072875403</v>
+        <v>0.49348324072875399</v>
       </c>
       <c r="T51">
-        <v>11523.777711422799</v>
+        <v>11.523777711422801</v>
       </c>
       <c r="U51">
-        <v>3787.68256535914</v>
+        <v>3.7876825653591402</v>
       </c>
       <c r="V51">
-        <v>3666.3048387096701</v>
+        <v>3.6663048387096699</v>
       </c>
       <c r="W51">
-        <v>1205.0561252242201</v>
+        <v>1.20505612522422</v>
       </c>
       <c r="X51">
-        <v>4181.4348790322501</v>
+        <v>4.18143487903225</v>
       </c>
       <c r="Y51">
-        <v>1374.3711815784</v>
+        <v>1.3743711815784001</v>
       </c>
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
@@ -6710,76 +6710,76 @@
         <v>0.51041666666666696</v>
       </c>
       <c r="B52">
-        <v>18542.994867476798</v>
+        <v>18.5429948674768</v>
       </c>
       <c r="C52">
-        <v>6094.7876753528899</v>
+        <v>6.0947876753528902</v>
       </c>
       <c r="D52">
-        <v>27842.437741588899</v>
+        <v>27.842437741588899</v>
       </c>
       <c r="E52">
-        <v>9151.3667350923606</v>
+        <v>9.1513667350923598</v>
       </c>
       <c r="F52">
-        <v>3457.7656654437901</v>
+        <v>3.45776566544379</v>
       </c>
       <c r="G52">
-        <v>1136.5126136645799</v>
+        <v>1.13651261366458</v>
       </c>
       <c r="H52">
-        <v>12676.2484969939</v>
+        <v>12.6762484969939</v>
       </c>
       <c r="I52">
-        <v>4166.4813942593701</v>
+        <v>4.1664813942593701</v>
       </c>
       <c r="J52">
-        <v>5640.60280561122</v>
+        <v>5.6406028056112198</v>
       </c>
       <c r="K52">
-        <v>1853.9764858317001</v>
+        <v>1.8539764858317</v>
       </c>
       <c r="L52">
-        <v>20290.267334669301</v>
+        <v>20.290267334669299</v>
       </c>
       <c r="M52">
-        <v>6669.0883627356998</v>
+        <v>6.6690883627356996</v>
       </c>
       <c r="N52">
-        <v>28558.1343486974</v>
+        <v>28.558134348697401</v>
       </c>
       <c r="O52">
-        <v>9386.6048339793597</v>
+        <v>9.3866048339793604</v>
       </c>
       <c r="P52">
-        <v>16792.7828991315</v>
+        <v>16.792782899131499</v>
       </c>
       <c r="Q52">
-        <v>5519.52082066398</v>
+        <v>5.5195208206639803</v>
       </c>
       <c r="R52">
-        <v>1396.35038709677</v>
+        <v>1.39635038709677</v>
       </c>
       <c r="S52">
-        <v>458.958177499062</v>
+        <v>0.45895817749906198</v>
       </c>
       <c r="T52">
-        <v>11579.2101002004</v>
+        <v>11.579210100200401</v>
       </c>
       <c r="U52">
-        <v>3805.9023104624198</v>
+        <v>3.8059023104624199</v>
       </c>
       <c r="V52">
-        <v>3409.8029032258</v>
+        <v>3.4098029032257999</v>
       </c>
       <c r="W52">
-        <v>1120.7480160830601</v>
+        <v>1.1207480160830601</v>
       </c>
       <c r="X52">
-        <v>3888.8934274193498</v>
+        <v>3.8888934274193501</v>
       </c>
       <c r="Y52">
-        <v>1278.2174563272899</v>
+        <v>1.2782174563272899</v>
       </c>
       <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
@@ -6834,76 +6834,76 @@
         <v>0.52083333333333304</v>
       </c>
       <c r="B53">
-        <v>18391.777118333401</v>
+        <v>18.391777118333401</v>
       </c>
       <c r="C53">
-        <v>6045.0848047885102</v>
+        <v>6.0450848047885097</v>
       </c>
       <c r="D53">
-        <v>27659.409895232398</v>
+        <v>27.6594098952324</v>
       </c>
       <c r="E53">
-        <v>9091.2083911898808</v>
+        <v>9.0912083911898804</v>
       </c>
       <c r="F53">
-        <v>3266.4635414781101</v>
+        <v>3.2664635414781098</v>
       </c>
       <c r="G53">
-        <v>1073.6346462301101</v>
+        <v>1.0736346462301101</v>
       </c>
       <c r="H53">
-        <v>12618.9356713426</v>
+        <v>12.6189356713426</v>
       </c>
       <c r="I53">
-        <v>4147.6435794448998</v>
+        <v>4.1476435794448996</v>
       </c>
       <c r="J53">
-        <v>5615.1000801603204</v>
+        <v>5.6151000801603201</v>
       </c>
       <c r="K53">
-        <v>1845.59414533725</v>
+        <v>1.84559414533725</v>
       </c>
       <c r="L53">
-        <v>20198.529423847602</v>
+        <v>20.198529423847599</v>
       </c>
       <c r="M53">
-        <v>6638.9355696063103</v>
+        <v>6.6389355696063097</v>
       </c>
       <c r="N53">
-        <v>28429.015124248399</v>
+        <v>28.429015124248401</v>
       </c>
       <c r="O53">
-        <v>9344.1653972299791</v>
+        <v>9.3441653972299807</v>
       </c>
       <c r="P53">
-        <v>16716.858082832299</v>
+        <v>16.716858082832299</v>
       </c>
       <c r="Q53">
-        <v>5494.5655403577903</v>
+        <v>5.4945655403577902</v>
       </c>
       <c r="R53">
-        <v>1277.0383548387099</v>
+        <v>1.2770383548387001</v>
       </c>
       <c r="S53">
-        <v>419.74220893924797</v>
+        <v>0.41974220893924802</v>
       </c>
       <c r="T53">
-        <v>11526.857288577099</v>
+        <v>11.5268572885771</v>
       </c>
       <c r="U53">
-        <v>3788.69477342043</v>
+        <v>3.7886947734204299</v>
       </c>
       <c r="V53">
-        <v>3118.45016129032</v>
+        <v>3.1184501612903199</v>
       </c>
       <c r="W53">
-        <v>1024.98500080859</v>
+        <v>1.0249850008085899</v>
       </c>
       <c r="X53">
-        <v>3556.6044959677401</v>
+        <v>3.5566044959677399</v>
       </c>
       <c r="Y53">
-        <v>1168.9993662322699</v>
+        <v>1.16899936623227</v>
       </c>
       <c r="Z53" s="4"/>
       <c r="AA53" s="4"/>
@@ -6958,76 +6958,76 @@
         <v>0.53125</v>
       </c>
       <c r="B54">
-        <v>18066.392687568601</v>
+        <v>18.066392687568602</v>
       </c>
       <c r="C54">
-        <v>5938.1361143234699</v>
+        <v>5.9381361143234699</v>
       </c>
       <c r="D54">
-        <v>27270.3914054981</v>
+        <v>27.270391405498099</v>
       </c>
       <c r="E54">
-        <v>8963.3441969934993</v>
+        <v>8.9633441969934999</v>
       </c>
       <c r="F54">
-        <v>3086.6617547999199</v>
+        <v>3.0866617547999202</v>
       </c>
       <c r="G54">
-        <v>1014.53665686623</v>
+        <v>1.01453665686623</v>
       </c>
       <c r="H54">
-        <v>12430.1404809619</v>
+        <v>12.430140480961899</v>
       </c>
       <c r="I54">
-        <v>4085.5896012325302</v>
+        <v>4.0855896012325301</v>
       </c>
       <c r="J54">
-        <v>5531.0911022044002</v>
+        <v>5.5310911022043996</v>
       </c>
       <c r="K54">
-        <v>1817.9817295908199</v>
+        <v>1.8179817295908201</v>
       </c>
       <c r="L54">
-        <v>19896.333952905799</v>
+        <v>19.896333952905799</v>
       </c>
       <c r="M54">
-        <v>6539.6087216506703</v>
+        <v>6.5396087216506702</v>
       </c>
       <c r="N54">
-        <v>28003.681208416801</v>
+        <v>28.003681208416801</v>
       </c>
       <c r="O54">
-        <v>9204.3648997026303</v>
+        <v>9.2043648997026306</v>
       </c>
       <c r="P54">
-        <v>16466.752805611199</v>
+        <v>16.4667528056112</v>
       </c>
       <c r="Q54">
-        <v>5412.3599111138501</v>
+        <v>5.4123599111138496</v>
       </c>
       <c r="R54">
-        <v>1173.71070967741</v>
+        <v>1.17371070967741</v>
       </c>
       <c r="S54">
-        <v>385.780054349171</v>
+        <v>0.38578005434917101</v>
       </c>
       <c r="T54">
-        <v>11354.400967935801</v>
+        <v>11.354400967935799</v>
       </c>
       <c r="U54">
-        <v>3732.01112198801</v>
+        <v>3.7320111219880099</v>
       </c>
       <c r="V54">
-        <v>2866.13032258064</v>
+        <v>2.86613032258064</v>
       </c>
       <c r="W54">
-        <v>942.05148040342499</v>
+        <v>0.94205148040342501</v>
       </c>
       <c r="X54">
-        <v>3268.83274193548</v>
+        <v>3.2688327419354799</v>
       </c>
       <c r="Y54">
-        <v>1074.4133647624301</v>
+        <v>1.0744133647624301</v>
       </c>
       <c r="Z54" s="4"/>
       <c r="AA54" s="4"/>
@@ -7082,76 +7082,76 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="B55">
-        <v>17572.398908300402</v>
+        <v>17.5723989083004</v>
       </c>
       <c r="C55">
-        <v>5775.7682110207697</v>
+        <v>5.77576821102077</v>
       </c>
       <c r="D55">
-        <v>26675.787385254898</v>
+        <v>26.6757873852549</v>
       </c>
       <c r="E55">
-        <v>8767.9073066641195</v>
+        <v>8.7679073066641209</v>
       </c>
       <c r="F55">
-        <v>2956.7248491741502</v>
+        <v>2.95672484917415</v>
       </c>
       <c r="G55">
-        <v>971.82846131091503</v>
+        <v>0.97182846131091505</v>
       </c>
       <c r="H55">
-        <v>12103.120240480899</v>
+        <v>12.1031202404809</v>
       </c>
       <c r="I55">
-        <v>3978.1032461146701</v>
+        <v>3.9781032461146699</v>
       </c>
       <c r="J55">
-        <v>5385.5755511021998</v>
+        <v>5.3855755511021997</v>
       </c>
       <c r="K55">
-        <v>1770.1530808871901</v>
+        <v>1.7701530808871899</v>
       </c>
       <c r="L55">
-        <v>19372.888226452898</v>
+        <v>19.372888226452901</v>
       </c>
       <c r="M55">
-        <v>6367.5604314417997</v>
+        <v>6.3675604314417997</v>
       </c>
       <c r="N55">
-        <v>27266.9421042084</v>
+        <v>27.2669421042084</v>
       </c>
       <c r="O55">
-        <v>8962.2104664856106</v>
+        <v>8.9622104664856099</v>
       </c>
       <c r="P55">
-        <v>16033.534736138899</v>
+        <v>16.0335347361389</v>
       </c>
       <c r="Q55">
-        <v>5269.9680176020402</v>
+        <v>5.2699680176020403</v>
       </c>
       <c r="R55">
-        <v>1111.48577419354</v>
+        <v>1.11148577419354</v>
       </c>
       <c r="S55">
-        <v>365.32770710984198</v>
+        <v>0.36532770710984203</v>
       </c>
       <c r="T55">
-        <v>11055.681983967899</v>
+        <v>11.055681983967901</v>
       </c>
       <c r="U55">
-        <v>3633.8269400425702</v>
+        <v>3.6338269400425798</v>
       </c>
       <c r="V55">
-        <v>2714.1808064516099</v>
+        <v>2.7141808064516102</v>
       </c>
       <c r="W55">
-        <v>892.10808966219304</v>
+        <v>0.89210808966219302</v>
       </c>
       <c r="X55">
-        <v>3095.5337298386999</v>
+        <v>3.0955337298386998</v>
       </c>
       <c r="Y55">
-        <v>1017.45273404302</v>
+        <v>1.0174527340430199</v>
       </c>
       <c r="Z55" s="4"/>
       <c r="AA55" s="4"/>
@@ -7206,76 +7206,76 @@
         <v>0.55208333333333304</v>
       </c>
       <c r="B56">
-        <v>16957.5231903161</v>
+        <v>16.957523190316099</v>
       </c>
       <c r="C56">
-        <v>5573.6683358588698</v>
+        <v>5.5736683358588701</v>
       </c>
       <c r="D56">
-        <v>25916.4784298675</v>
+        <v>25.9164784298675</v>
       </c>
       <c r="E56">
-        <v>8518.3345221083091</v>
+        <v>8.5183345221083098</v>
       </c>
       <c r="F56">
-        <v>2869.7681967968101</v>
+        <v>2.8697681967968101</v>
       </c>
       <c r="G56">
-        <v>943.24719183492198</v>
+        <v>0.94324719183492201</v>
       </c>
       <c r="H56">
-        <v>11674.959719438801</v>
+        <v>11.6749597194388</v>
       </c>
       <c r="I56">
-        <v>3837.3736883830302</v>
+        <v>3.8373736883830301</v>
       </c>
       <c r="J56">
-        <v>5195.05519038076</v>
+        <v>5.19505519038076</v>
       </c>
       <c r="K56">
-        <v>1707.5320666051</v>
+        <v>1.7075320666050999</v>
       </c>
       <c r="L56">
-        <v>18687.552069138201</v>
+        <v>18.687552069138199</v>
       </c>
       <c r="M56">
-        <v>6142.3013298281203</v>
+        <v>6.1423013298281202</v>
       </c>
       <c r="N56">
-        <v>26302.345545090098</v>
+        <v>26.302345545090098</v>
       </c>
       <c r="O56">
-        <v>8645.1629095932203</v>
+        <v>8.6451629095932194</v>
       </c>
       <c r="P56">
-        <v>15466.3316967267</v>
+        <v>15.4663316967267</v>
       </c>
       <c r="Q56">
-        <v>5083.5373941381304</v>
+        <v>5.0835373941381299</v>
       </c>
       <c r="R56">
-        <v>1083.51309677419</v>
+        <v>1.0835130967741899</v>
       </c>
       <c r="S56">
-        <v>356.13353266280399</v>
+        <v>0.35613353266280401</v>
       </c>
       <c r="T56">
-        <v>10664.575685370701</v>
+        <v>10.6645756853707</v>
       </c>
       <c r="U56">
-        <v>3505.2765162583401</v>
+        <v>3.5052765162583399</v>
       </c>
       <c r="V56">
-        <v>2645.8732258064501</v>
+        <v>2.6458732258064499</v>
       </c>
       <c r="W56">
-        <v>869.65647364090501</v>
+        <v>0.86965647364090504</v>
       </c>
       <c r="X56">
-        <v>3017.62866935483</v>
+        <v>3.01762866935483</v>
       </c>
       <c r="Y56">
-        <v>991.84657894897805</v>
+        <v>0.99184657894897799</v>
       </c>
       <c r="Z56" s="4"/>
       <c r="AA56" s="4"/>
@@ -7330,76 +7330,76 @@
         <v>0.5625</v>
       </c>
       <c r="B57">
-        <v>16284.9297287801</v>
+        <v>16.284929728780099</v>
       </c>
       <c r="C57">
-        <v>5352.5975558047603</v>
+        <v>5.3525975558047598</v>
       </c>
       <c r="D57">
-        <v>25039.298906652999</v>
+        <v>25.039298906652999</v>
       </c>
       <c r="E57">
-        <v>8230.0195554393304</v>
+        <v>8.2300195554393305</v>
       </c>
       <c r="F57">
-        <v>2811.4015097533702</v>
+        <v>2.8114015097533702</v>
       </c>
       <c r="G57">
-        <v>924.06298953179305</v>
+        <v>0.924062989531793</v>
       </c>
       <c r="H57">
-        <v>11196.2290581162</v>
+        <v>11.196229058116201</v>
       </c>
       <c r="I57">
-        <v>3680.0225293445201</v>
+        <v>3.6800225293445199</v>
       </c>
       <c r="J57">
-        <v>4982.0324248497</v>
+        <v>4.9820324248496997</v>
       </c>
       <c r="K57">
-        <v>1637.5148695338</v>
+        <v>1.6375148695338</v>
       </c>
       <c r="L57">
-        <v>17921.270696392701</v>
+        <v>17.9212706963927</v>
       </c>
       <c r="M57">
-        <v>5890.4368225120397</v>
+        <v>5.89043682251204</v>
       </c>
       <c r="N57">
-        <v>25223.820258517</v>
+        <v>25.223820258517001</v>
       </c>
       <c r="O57">
-        <v>8290.6687908631502</v>
+        <v>8.2906687908631493</v>
       </c>
       <c r="P57">
-        <v>14832.136172344601</v>
+        <v>14.832136172344599</v>
       </c>
       <c r="Q57">
-        <v>4875.0874056981602</v>
+        <v>4.8750874056981601</v>
       </c>
       <c r="R57">
-        <v>1077.23351612903</v>
+        <v>1.0772335161290301</v>
       </c>
       <c r="S57">
-        <v>354.06953431755102</v>
+        <v>0.354069534317551</v>
       </c>
       <c r="T57">
-        <v>10227.275729458899</v>
+        <v>10.227275729458899</v>
       </c>
       <c r="U57">
-        <v>3361.5429715547002</v>
+        <v>3.3615429715546998</v>
       </c>
       <c r="V57">
-        <v>2630.53887096774</v>
+        <v>2.6305388709677402</v>
       </c>
       <c r="W57">
-        <v>864.61631494224901</v>
+        <v>0.864616314942249</v>
       </c>
       <c r="X57">
-        <v>3000.1397782258</v>
+        <v>3.0001397782258001</v>
       </c>
       <c r="Y57">
-        <v>986.09825841766201</v>
+        <v>0.98609825841766197</v>
       </c>
       <c r="Z57" s="4"/>
       <c r="AA57" s="4"/>
@@ -7454,76 +7454,76 @@
         <v>0.57291666666666696</v>
       </c>
       <c r="B58">
-        <v>15622.8333264916</v>
+        <v>15.6228333264916</v>
       </c>
       <c r="C58">
-        <v>5134.9769922764399</v>
+        <v>5.1349769922764397</v>
       </c>
       <c r="D58">
-        <v>24100.571444433099</v>
+        <v>24.100571444433101</v>
       </c>
       <c r="E58">
-        <v>7921.4747595127501</v>
+        <v>7.9214747595127504</v>
       </c>
       <c r="F58">
-        <v>2768.46426453713</v>
+        <v>2.7684642645371298</v>
       </c>
       <c r="G58">
-        <v>909.95019950904896</v>
+        <v>0.90995019950904799</v>
       </c>
       <c r="H58">
-        <v>10720.8697394789</v>
+        <v>10.7208697394789</v>
       </c>
       <c r="I58">
-        <v>3523.7794770597902</v>
+        <v>3.5237794770597901</v>
       </c>
       <c r="J58">
-        <v>4770.5098196392701</v>
+        <v>4.7705098196392699</v>
       </c>
       <c r="K58">
-        <v>1567.9907513151099</v>
+        <v>1.5679907513151099</v>
       </c>
       <c r="L58">
-        <v>17160.385671342599</v>
+        <v>17.160385671342599</v>
       </c>
       <c r="M58">
-        <v>5640.3460089094497</v>
+        <v>5.6403460089094501</v>
       </c>
       <c r="N58">
-        <v>24152.8902204408</v>
+        <v>24.152890220440799</v>
       </c>
       <c r="O58">
-        <v>7938.6711095889204</v>
+        <v>7.9386711095889204</v>
       </c>
       <c r="P58">
-        <v>14202.4068136272</v>
+        <v>14.202406813627199</v>
       </c>
       <c r="Q58">
-        <v>4668.1053749232597</v>
+        <v>4.6681053749232602</v>
       </c>
       <c r="R58">
-        <v>1080.6587419354801</v>
+        <v>1.0806587419354801</v>
       </c>
       <c r="S58">
-        <v>355.19535159677997</v>
+        <v>0.35519535159678001</v>
       </c>
       <c r="T58">
-        <v>9793.0553507013992</v>
+        <v>9.7930553507013993</v>
       </c>
       <c r="U58">
-        <v>3218.82163491236</v>
+        <v>3.2188216349123602</v>
       </c>
       <c r="V58">
-        <v>2638.9030645161201</v>
+        <v>2.63890306451612</v>
       </c>
       <c r="W58">
-        <v>867.36549241424302</v>
+        <v>0.86736549241424299</v>
       </c>
       <c r="X58">
-        <v>3009.67917338709</v>
+        <v>3.0096791733870898</v>
       </c>
       <c r="Y58">
-        <v>989.23370598019801</v>
+        <v>0.989233705980198</v>
       </c>
       <c r="Z58" s="4"/>
       <c r="AA58" s="4"/>
@@ -7578,76 +7578,76 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="B59">
-        <v>15015.557360979999</v>
+        <v>15.015557360980001</v>
       </c>
       <c r="C59">
-        <v>4935.3750349556103</v>
+        <v>4.9353750349556096</v>
       </c>
       <c r="D59">
-        <v>23145.818175350101</v>
+        <v>23.145818175350101</v>
       </c>
       <c r="E59">
-        <v>7607.6625355976203</v>
+        <v>7.60766253559762</v>
       </c>
       <c r="F59">
-        <v>2725.1970349570101</v>
+        <v>2.7251970349570098</v>
       </c>
       <c r="G59">
-        <v>895.72894887093605</v>
+        <v>0.89572894887093601</v>
       </c>
       <c r="H59">
-        <v>10285.966533066099</v>
+        <v>10.2859665330661</v>
       </c>
       <c r="I59">
-        <v>3380.8337058205698</v>
+        <v>3.38083370582057</v>
       </c>
       <c r="J59">
-        <v>4576.98913827655</v>
+        <v>4.5769891382765504</v>
       </c>
       <c r="K59">
-        <v>1504.3835793277999</v>
+        <v>1.5043835793278</v>
       </c>
       <c r="L59">
-        <v>16464.256818637201</v>
+        <v>16.4642568186372</v>
       </c>
       <c r="M59">
-        <v>5411.5395198687802</v>
+        <v>5.4115395198687803</v>
       </c>
       <c r="N59">
-        <v>23173.103164328601</v>
+        <v>23.173103164328602</v>
       </c>
       <c r="O59">
-        <v>7616.6306777848404</v>
+        <v>7.6166306777848396</v>
       </c>
       <c r="P59">
-        <v>13626.2714428857</v>
+        <v>13.626271442885701</v>
       </c>
       <c r="Q59">
-        <v>4478.7388361291996</v>
+        <v>4.4787388361292004</v>
       </c>
       <c r="R59">
-        <v>1081.22961290322</v>
+        <v>1.0812296129032199</v>
       </c>
       <c r="S59">
-        <v>355.38298780998502</v>
+        <v>0.35538298780998501</v>
       </c>
       <c r="T59">
-        <v>9395.7898977955902</v>
+        <v>9.3957898977955896</v>
       </c>
       <c r="U59">
-        <v>3088.2467950055402</v>
+        <v>3.0882467950055399</v>
       </c>
       <c r="V59">
-        <v>2640.2970967741899</v>
+        <v>2.6402970967741899</v>
       </c>
       <c r="W59">
-        <v>867.82368865957505</v>
+        <v>0.86782368865957504</v>
       </c>
       <c r="X59">
-        <v>3011.2690725806401</v>
+        <v>3.0112690725806401</v>
       </c>
       <c r="Y59">
-        <v>989.75628057395397</v>
+        <v>0.98975628057395404</v>
       </c>
       <c r="Z59" s="4"/>
       <c r="AA59" s="4"/>
@@ -7702,76 +7702,76 @@
         <v>0.59375</v>
       </c>
       <c r="B60">
-        <v>14481.6022466546</v>
+        <v>14.481602246654599</v>
       </c>
       <c r="C60">
-        <v>4759.8724759978804</v>
+        <v>4.7598724759978799</v>
       </c>
       <c r="D60">
-        <v>22221.152508389401</v>
+        <v>22.221152508389402</v>
       </c>
       <c r="E60">
-        <v>7303.7396282630398</v>
+        <v>7.30373962826304</v>
       </c>
       <c r="F60">
-        <v>2682.0814794508301</v>
+        <v>2.6820814794508299</v>
       </c>
       <c r="G60">
-        <v>881.55755109009897</v>
+        <v>0.88155755109009903</v>
       </c>
       <c r="H60">
-        <v>9905.0048096192404</v>
+        <v>9.9050048096192391</v>
       </c>
       <c r="I60">
-        <v>3255.6176426420302</v>
+        <v>3.2556176426420298</v>
       </c>
       <c r="J60">
-        <v>4407.4710220440802</v>
+        <v>4.4074710220440796</v>
       </c>
       <c r="K60">
-        <v>1448.6656689823301</v>
+        <v>1.4486656689823301</v>
       </c>
       <c r="L60">
-        <v>15854.4695290581</v>
+        <v>15.8544695290581</v>
       </c>
       <c r="M60">
-        <v>5211.1121302440097</v>
+        <v>5.2111121302440102</v>
       </c>
       <c r="N60">
-        <v>22314.8400841683</v>
+        <v>22.314840084168299</v>
       </c>
       <c r="O60">
-        <v>7334.5332452742896</v>
+        <v>7.3345332452742902</v>
       </c>
       <c r="P60">
-        <v>13121.5947227788</v>
+        <v>13.1215947227788</v>
       </c>
       <c r="Q60">
-        <v>4312.8596199762696</v>
+        <v>4.3128596199762699</v>
       </c>
       <c r="R60">
-        <v>1078.37525806451</v>
+        <v>1.0783752580645101</v>
       </c>
       <c r="S60">
-        <v>354.44480674396101</v>
+        <v>0.35444480674396101</v>
       </c>
       <c r="T60">
-        <v>9047.7976793587204</v>
+        <v>9.0477976793587196</v>
       </c>
       <c r="U60">
-        <v>2973.8672840794102</v>
+        <v>2.97386728407941</v>
       </c>
       <c r="V60">
-        <v>2633.3269354838699</v>
+        <v>2.6333269354838702</v>
       </c>
       <c r="W60">
-        <v>865.53270743291398</v>
+        <v>0.865532707432913</v>
       </c>
       <c r="X60">
-        <v>3003.3195766129002</v>
+        <v>3.0033195766128999</v>
       </c>
       <c r="Y60">
-        <v>987.14340760517405</v>
+        <v>0.98714340760517405</v>
       </c>
       <c r="Z60" s="4"/>
       <c r="AA60" s="4"/>
@@ -7826,76 +7826,76 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="B61">
-        <v>14012.5687843751</v>
+        <v>14.012568784375199</v>
       </c>
       <c r="C61">
-        <v>4605.7086321496299</v>
+        <v>4.6057086321496303</v>
       </c>
       <c r="D61">
-        <v>21361.101291398802</v>
+        <v>21.3611012913988</v>
       </c>
       <c r="E61">
-        <v>7021.0544635984797</v>
+        <v>7.02105446359848</v>
       </c>
       <c r="F61">
-        <v>2641.0954683964701</v>
+        <v>2.64109546839647</v>
       </c>
       <c r="G61">
-        <v>868.08610072184399</v>
+        <v>0.868086100721844</v>
       </c>
       <c r="H61">
-        <v>9571.2418837675305</v>
+        <v>9.5712418837675308</v>
       </c>
       <c r="I61">
-        <v>3145.9150740165801</v>
+        <v>3.14591507401658</v>
       </c>
       <c r="J61">
-        <v>4258.9551503005996</v>
+        <v>4.2589551503005998</v>
       </c>
       <c r="K61">
-        <v>1399.8508625734601</v>
+        <v>1.39985086257346</v>
       </c>
       <c r="L61">
-        <v>15320.2311072144</v>
+        <v>15.320231107214401</v>
       </c>
       <c r="M61">
-        <v>5035.5164526081498</v>
+        <v>5.0355164526081504</v>
       </c>
       <c r="N61">
-        <v>21562.910482965901</v>
+        <v>21.562910482965901</v>
       </c>
       <c r="O61">
-        <v>7087.3859371455801</v>
+        <v>7.0873859371455801</v>
       </c>
       <c r="P61">
-        <v>12679.4443219772</v>
+        <v>12.679444321977201</v>
       </c>
       <c r="Q61">
-        <v>4167.5318111343204</v>
+        <v>4.16753181113432</v>
       </c>
       <c r="R61">
-        <v>1073.80829032258</v>
+        <v>1.0738082903225801</v>
       </c>
       <c r="S61">
-        <v>352.94371703832201</v>
+        <v>0.352943717038322</v>
       </c>
       <c r="T61">
-        <v>8742.9195410821594</v>
+        <v>8.7429195410821592</v>
       </c>
       <c r="U61">
-        <v>2873.6586860113798</v>
+        <v>2.87365868601138</v>
       </c>
       <c r="V61">
-        <v>2622.1746774193498</v>
+        <v>2.6221746774193502</v>
       </c>
       <c r="W61">
-        <v>861.86713747025397</v>
+        <v>0.86186713747025401</v>
       </c>
       <c r="X61">
-        <v>2990.60038306451</v>
+        <v>2.99060038306451</v>
       </c>
       <c r="Y61">
-        <v>982.96281085512499</v>
+        <v>0.98296281085512505</v>
       </c>
       <c r="Z61" s="4"/>
       <c r="AA61" s="4"/>
@@ -7950,76 +7950,76 @@
         <v>0.61458333333333304</v>
       </c>
       <c r="B62">
-        <v>13613.167178550601</v>
+        <v>13.613167178550601</v>
       </c>
       <c r="C62">
-        <v>4474.4316727321902</v>
+        <v>4.47443167273219</v>
       </c>
       <c r="D62">
-        <v>20611.179153083402</v>
+        <v>20.611179153083398</v>
       </c>
       <c r="E62">
-        <v>6774.5669766124602</v>
+        <v>6.7745669766124603</v>
       </c>
       <c r="F62">
-        <v>2602.5812863630399</v>
+        <v>2.6025812863630402</v>
       </c>
       <c r="G62">
-        <v>855.427101263493</v>
+        <v>0.85542710126349297</v>
       </c>
       <c r="H62">
-        <v>9288.0490981963903</v>
+        <v>9.2880490981963906</v>
       </c>
       <c r="I62">
-        <v>3052.8341066980202</v>
+        <v>3.05283410669802</v>
       </c>
       <c r="J62">
-        <v>4132.9416833667301</v>
+        <v>4.1329416833667301</v>
       </c>
       <c r="K62">
-        <v>1358.4322389538099</v>
+        <v>1.3584322389538099</v>
       </c>
       <c r="L62">
-        <v>14866.9379008016</v>
+        <v>14.8669379008016</v>
       </c>
       <c r="M62">
-        <v>4886.5261806747003</v>
+        <v>4.8865261806747</v>
       </c>
       <c r="N62">
-        <v>20924.909609218401</v>
+        <v>20.9249096092184</v>
       </c>
       <c r="O62">
-        <v>6877.6851908545495</v>
+        <v>6.8776851908545504</v>
       </c>
       <c r="P62">
-        <v>12304.2864061456</v>
+        <v>12.3042864061456</v>
       </c>
       <c r="Q62">
-        <v>4044.2233672684201</v>
+        <v>4.0442233672684198</v>
       </c>
       <c r="R62">
-        <v>1067.52870967741</v>
+        <v>1.06752870967741</v>
       </c>
       <c r="S62">
-        <v>350.87971869306898</v>
+        <v>0.350879718693069</v>
       </c>
       <c r="T62">
-        <v>8484.2350601202397</v>
+        <v>8.4842350601202394</v>
       </c>
       <c r="U62">
-        <v>2788.6332088627501</v>
+        <v>2.7886332088627599</v>
       </c>
       <c r="V62">
-        <v>2606.8403225806401</v>
+        <v>2.60684032258064</v>
       </c>
       <c r="W62">
-        <v>856.82697877159796</v>
+        <v>0.85682697877159797</v>
       </c>
       <c r="X62">
-        <v>2973.11149193548</v>
+        <v>2.9731114919354802</v>
       </c>
       <c r="Y62">
-        <v>977.21449032380895</v>
+        <v>0.97721449032380903</v>
       </c>
       <c r="Z62" s="4"/>
       <c r="AA62" s="4"/>
@@ -8074,76 +8074,76 @@
         <v>0.625</v>
       </c>
       <c r="B63">
-        <v>13279.027627997901</v>
+        <v>13.2790276279979</v>
       </c>
       <c r="C63">
-        <v>4364.6053135538996</v>
+        <v>4.3646053135539002</v>
       </c>
       <c r="D63">
-        <v>19998.304030524301</v>
+        <v>19.998304030524299</v>
       </c>
       <c r="E63">
-        <v>6573.1246653677499</v>
+        <v>6.5731246653677502</v>
       </c>
       <c r="F63">
-        <v>2567.0841286201398</v>
+        <v>2.5670841286201398</v>
       </c>
       <c r="G63">
-        <v>843.75974973437303</v>
+        <v>0.84375974973437295</v>
       </c>
       <c r="H63">
-        <v>9052.0551102204408</v>
+        <v>9.0520551102204401</v>
       </c>
       <c r="I63">
-        <v>2975.2666339325601</v>
+        <v>2.9752666339325602</v>
       </c>
       <c r="J63">
-        <v>4027.9304609218402</v>
+        <v>4.0279304609218398</v>
       </c>
       <c r="K63">
-        <v>1323.91671927078</v>
+        <v>1.3239167192707799</v>
       </c>
       <c r="L63">
-        <v>14489.193562124199</v>
+        <v>14.4891935621242</v>
       </c>
       <c r="M63">
-        <v>4762.3676207301496</v>
+        <v>4.7623676207301502</v>
       </c>
       <c r="N63">
-        <v>20393.242214428799</v>
+        <v>20.393242214428799</v>
       </c>
       <c r="O63">
-        <v>6702.9345689453603</v>
+        <v>6.7029345689453601</v>
       </c>
       <c r="P63">
-        <v>11991.6548096192</v>
+        <v>11.991654809619201</v>
       </c>
       <c r="Q63">
-        <v>3941.4663307135002</v>
+        <v>3.9414663307134998</v>
       </c>
       <c r="R63">
-        <v>1060.10738709677</v>
+        <v>1.0601073870967701</v>
       </c>
       <c r="S63">
-        <v>348.440447921405</v>
+        <v>0.34844044792140499</v>
       </c>
       <c r="T63">
-        <v>8268.6646593186306</v>
+        <v>8.2686646593186293</v>
       </c>
       <c r="U63">
-        <v>2717.77864457223</v>
+        <v>2.7177786445722298</v>
       </c>
       <c r="V63">
-        <v>2588.7179032258</v>
+        <v>2.5887179032257999</v>
       </c>
       <c r="W63">
-        <v>850.87042758227699</v>
+        <v>0.85087042758227704</v>
       </c>
       <c r="X63">
-        <v>2952.4428024193498</v>
+        <v>2.9524428024193501</v>
       </c>
       <c r="Y63">
-        <v>970.42102060497996</v>
+        <v>0.97042102060498003</v>
       </c>
       <c r="Z63" s="4"/>
       <c r="AA63" s="4"/>
@@ -8198,76 +8198,76 @@
         <v>0.63541666666666696</v>
       </c>
       <c r="B64">
-        <v>12993.011331210801</v>
+        <v>12.9930113312108</v>
       </c>
       <c r="C64">
-        <v>4270.5963029778504</v>
+        <v>4.2705963029778502</v>
       </c>
       <c r="D64">
-        <v>19494.9286618474</v>
+        <v>19.4949286618474</v>
       </c>
       <c r="E64">
-        <v>6407.6731827450903</v>
+        <v>6.4076731827450901</v>
       </c>
       <c r="F64">
-        <v>2537.6722560847402</v>
+        <v>2.53767225608475</v>
       </c>
       <c r="G64">
-        <v>834.09253472844205</v>
+        <v>0.83409253472844203</v>
       </c>
       <c r="H64">
-        <v>8849.7745490981906</v>
+        <v>8.8497745490981892</v>
       </c>
       <c r="I64">
-        <v>2908.7802287050099</v>
+        <v>2.9087802287050102</v>
       </c>
       <c r="J64">
-        <v>3937.9208416833599</v>
+        <v>3.93792084168336</v>
       </c>
       <c r="K64">
-        <v>1294.33198811389</v>
+        <v>1.2943319881138899</v>
       </c>
       <c r="L64">
-        <v>14165.412700400801</v>
+        <v>14.1654127004008</v>
       </c>
       <c r="M64">
-        <v>4655.9459979205403</v>
+        <v>4.65594599792054</v>
       </c>
       <c r="N64">
-        <v>19937.527304609201</v>
+        <v>19.937527304609201</v>
       </c>
       <c r="O64">
-        <v>6553.14832159463</v>
+        <v>6.5531483215946302</v>
       </c>
       <c r="P64">
-        <v>11723.6848697394</v>
+        <v>11.723684869739399</v>
       </c>
       <c r="Q64">
-        <v>3853.38887080929</v>
+        <v>3.8533888708092898</v>
       </c>
       <c r="R64">
-        <v>1054.39867741935</v>
+        <v>1.0543986774193499</v>
       </c>
       <c r="S64">
-        <v>346.56408578935702</v>
+        <v>0.34656408578935699</v>
       </c>
       <c r="T64">
-        <v>8083.8900300601199</v>
+        <v>8.08389003006012</v>
       </c>
       <c r="U64">
-        <v>2657.0461608946398</v>
+        <v>2.6570461608946401</v>
       </c>
       <c r="V64">
-        <v>2574.77758064516</v>
+        <v>2.57477758064516</v>
       </c>
       <c r="W64">
-        <v>846.288465128952</v>
+        <v>0.84628846512895195</v>
       </c>
       <c r="X64">
-        <v>2936.5438104838699</v>
+        <v>2.9365438104838701</v>
       </c>
       <c r="Y64">
-        <v>965.19527466741999</v>
+        <v>0.96519527466741994</v>
       </c>
       <c r="Z64" s="4"/>
       <c r="AA64" s="4"/>
@@ -8322,76 +8322,76 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="B65">
-        <v>12756.139497866699</v>
+        <v>12.7561394978667</v>
       </c>
       <c r="C65">
-        <v>4192.7402963930599</v>
+        <v>4.19274029639306</v>
       </c>
       <c r="D65">
-        <v>19084.8439731121</v>
+        <v>19.0848439731121</v>
       </c>
       <c r="E65">
-        <v>6272.8848637806004</v>
+        <v>6.2728848637806003</v>
       </c>
       <c r="F65">
-        <v>2517.0081082729898</v>
+        <v>2.5170081082729898</v>
       </c>
       <c r="G65">
-        <v>827.30055779565305</v>
+        <v>0.82730055779565304</v>
       </c>
       <c r="H65">
-        <v>8681.2074148296597</v>
+        <v>8.6812074148296592</v>
       </c>
       <c r="I65">
-        <v>2853.3748910153899</v>
+        <v>2.85337489101539</v>
       </c>
       <c r="J65">
-        <v>3862.9128256513</v>
+        <v>3.8629128256512999</v>
       </c>
       <c r="K65">
-        <v>1269.6780454831501</v>
+        <v>1.26967804548315</v>
       </c>
       <c r="L65">
-        <v>13895.595315631201</v>
+        <v>13.8955953156312</v>
       </c>
       <c r="M65">
-        <v>4567.2613122458597</v>
+        <v>4.5672613122458596</v>
       </c>
       <c r="N65">
-        <v>19557.764879759499</v>
+        <v>19.5577648797595</v>
       </c>
       <c r="O65">
-        <v>6428.3264488023497</v>
+        <v>6.4283264488023502</v>
       </c>
       <c r="P65">
-        <v>11500.3765865063</v>
+        <v>11.500376586506301</v>
       </c>
       <c r="Q65">
-        <v>3779.9909875557801</v>
+        <v>3.77999098755578</v>
       </c>
       <c r="R65">
-        <v>1052.1151935483799</v>
+        <v>1.0521151935483799</v>
       </c>
       <c r="S65">
-        <v>345.813540936538</v>
+        <v>0.34581354093653799</v>
       </c>
       <c r="T65">
-        <v>7929.9111723446804</v>
+        <v>7.9299111723446796</v>
       </c>
       <c r="U65">
-        <v>2606.43575782998</v>
+        <v>2.6064357578299799</v>
       </c>
       <c r="V65">
-        <v>2569.2014516129002</v>
+        <v>2.5692014516129</v>
       </c>
       <c r="W65">
-        <v>844.45568014762296</v>
+        <v>0.84445568014762296</v>
       </c>
       <c r="X65">
-        <v>2930.1842137096701</v>
+        <v>2.9301842137096701</v>
       </c>
       <c r="Y65">
-        <v>963.10497629239603</v>
+        <v>0.963104976292396</v>
       </c>
       <c r="Z65" s="4"/>
       <c r="AA65" s="4"/>
@@ -8446,76 +8446,76 @@
         <v>0.65625</v>
       </c>
       <c r="B66">
-        <v>12544.8611059215</v>
+        <v>12.5448611059215</v>
       </c>
       <c r="C66">
-        <v>4123.2964471929299</v>
+        <v>4.1232964471929296</v>
       </c>
       <c r="D66">
-        <v>18729.4728565361</v>
+        <v>18.729472856536098</v>
       </c>
       <c r="E66">
-        <v>6156.0800263224</v>
+        <v>6.1560800263223996</v>
       </c>
       <c r="F66">
-        <v>2503.3802623391898</v>
+        <v>2.5033802623391899</v>
       </c>
       <c r="G66">
-        <v>822.82130144938503</v>
+        <v>0.82282130144938503</v>
       </c>
       <c r="H66">
-        <v>8529.4969939879702</v>
+        <v>8.5294969939879692</v>
       </c>
       <c r="I66">
-        <v>2803.5100870947399</v>
+        <v>2.80351008709474</v>
       </c>
       <c r="J66">
-        <v>3795.4056112224398</v>
+        <v>3.7954056112224399</v>
       </c>
       <c r="K66">
-        <v>1247.4894971154799</v>
+        <v>1.24748949711548</v>
       </c>
       <c r="L66">
-        <v>13652.7596693386</v>
+        <v>13.6527596693386</v>
       </c>
       <c r="M66">
-        <v>4487.4450951386498</v>
+        <v>4.48744509513865</v>
       </c>
       <c r="N66">
-        <v>19215.978697394701</v>
+        <v>19.2159786973947</v>
       </c>
       <c r="O66">
-        <v>6315.9867632893001</v>
+        <v>6.3159867632892999</v>
       </c>
       <c r="P66">
-        <v>11299.3991315965</v>
+        <v>11.2993991315965</v>
       </c>
       <c r="Q66">
-        <v>3713.9328926276198</v>
+        <v>3.7139328926276201</v>
       </c>
       <c r="R66">
-        <v>1053.2569354838699</v>
+        <v>1.0532569354838699</v>
       </c>
       <c r="S66">
-        <v>346.18881336294697</v>
+        <v>0.34618881336294699</v>
       </c>
       <c r="T66">
-        <v>7791.3302004008001</v>
+        <v>7.7913302004008003</v>
       </c>
       <c r="U66">
-        <v>2560.88639507179</v>
+        <v>2.5608863950717899</v>
       </c>
       <c r="V66">
-        <v>2571.9895161290301</v>
+        <v>2.57198951612903</v>
       </c>
       <c r="W66">
-        <v>845.37207263828805</v>
+        <v>0.84537207263828795</v>
       </c>
       <c r="X66">
-        <v>2933.3640120967698</v>
+        <v>2.9333640120967699</v>
       </c>
       <c r="Y66">
-        <v>964.15012547990796</v>
+        <v>0.96415012547990797</v>
       </c>
       <c r="Z66" s="4"/>
       <c r="AA66" s="4"/>
@@ -8570,76 +8570,76 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="B67">
-        <v>12371.6601932251</v>
+        <v>12.3716601932251</v>
       </c>
       <c r="C67">
-        <v>4066.3680601871702</v>
+        <v>4.0663680601871697</v>
       </c>
       <c r="D67">
-        <v>18432.3814663884</v>
+        <v>18.432381466388399</v>
       </c>
       <c r="E67">
-        <v>6058.4308085953298</v>
+        <v>6.0584308085953298</v>
       </c>
       <c r="F67">
-        <v>2505.46060597</v>
+        <v>2.5054606059700002</v>
       </c>
       <c r="G67">
-        <v>823.50507733414304</v>
+        <v>0.82350507733414302</v>
       </c>
       <c r="H67">
-        <v>8401.3859719438806</v>
+        <v>8.4013859719438795</v>
       </c>
       <c r="I67">
-        <v>2761.4020304506298</v>
+        <v>2.7614020304506299</v>
       </c>
       <c r="J67">
-        <v>3738.3995190380701</v>
+        <v>3.7383995190380701</v>
       </c>
       <c r="K67">
-        <v>1228.75250071612</v>
+        <v>1.22875250071612</v>
       </c>
       <c r="L67">
-        <v>13447.6984569138</v>
+        <v>13.4476984569138</v>
       </c>
       <c r="M67">
-        <v>4420.0447340258997</v>
+        <v>4.4200447340258897</v>
       </c>
       <c r="N67">
-        <v>18927.359254509</v>
+        <v>18.927359254509</v>
       </c>
       <c r="O67">
-        <v>6221.1221399671704</v>
+        <v>6.2211221399671697</v>
       </c>
       <c r="P67">
-        <v>11129.6848363393</v>
+        <v>11.129684836339299</v>
       </c>
       <c r="Q67">
-        <v>3658.1505013549499</v>
+        <v>3.65815050135495</v>
       </c>
       <c r="R67">
-        <v>1062.9617419354799</v>
+        <v>1.06296174193548</v>
       </c>
       <c r="S67">
-        <v>349.37862898742998</v>
+        <v>0.34937862898743</v>
       </c>
       <c r="T67">
-        <v>7674.3062685370696</v>
+        <v>7.6743062685370704</v>
       </c>
       <c r="U67">
-        <v>2522.4224887426399</v>
+        <v>2.5224224887426399</v>
       </c>
       <c r="V67">
-        <v>2595.68806451612</v>
+        <v>2.59568806451612</v>
       </c>
       <c r="W67">
-        <v>853.16140880893897</v>
+        <v>0.85316140880893898</v>
       </c>
       <c r="X67">
-        <v>2960.3922983870898</v>
+        <v>2.9603922983870898</v>
       </c>
       <c r="Y67">
-        <v>973.03389357376</v>
+        <v>0.97303389357376002</v>
       </c>
       <c r="Z67" s="4"/>
       <c r="AA67" s="4"/>
@@ -8694,76 +8694,76 @@
         <v>0.67708333333333304</v>
       </c>
       <c r="B68">
-        <v>12307.1898259098</v>
+        <v>12.3071898259098</v>
       </c>
       <c r="C68">
-        <v>4045.1776751955899</v>
+        <v>4.0451776751955899</v>
       </c>
       <c r="D68">
-        <v>18304.134538726001</v>
+        <v>18.304134538726</v>
       </c>
       <c r="E68">
-        <v>6016.2780819346999</v>
+        <v>6.0162780819346997</v>
       </c>
       <c r="F68">
-        <v>2528.3834077024999</v>
+        <v>2.5283834077025</v>
       </c>
       <c r="G68">
-        <v>831.03943790978099</v>
+        <v>0.83103943790978096</v>
       </c>
       <c r="H68">
-        <v>8347.4444889779497</v>
+        <v>8.3474444889779509</v>
       </c>
       <c r="I68">
-        <v>2743.6723223899498</v>
+        <v>2.74367232238995</v>
       </c>
       <c r="J68">
-        <v>3714.3969539078098</v>
+        <v>3.7143969539078099</v>
       </c>
       <c r="K68">
-        <v>1220.86323907428</v>
+        <v>1.22086323907428</v>
       </c>
       <c r="L68">
-        <v>13361.356893787501</v>
+        <v>13.3613568937875</v>
       </c>
       <c r="M68">
-        <v>4391.6656346099999</v>
+        <v>4.3916656346099998</v>
       </c>
       <c r="N68">
-        <v>18805.835278557101</v>
+        <v>18.805835278557101</v>
       </c>
       <c r="O68">
-        <v>6181.1791406736402</v>
+        <v>6.18117914067364</v>
       </c>
       <c r="P68">
-        <v>11058.2261857047</v>
+        <v>11.058226185704701</v>
       </c>
       <c r="Q68">
-        <v>3634.6631787138299</v>
+        <v>3.6346631787138302</v>
       </c>
       <c r="R68">
-        <v>1081.22961290322</v>
+        <v>1.0812296129032199</v>
       </c>
       <c r="S68">
-        <v>355.38298780998502</v>
+        <v>0.35538298780998501</v>
       </c>
       <c r="T68">
-        <v>7625.0330340681303</v>
+        <v>7.6250330340681298</v>
       </c>
       <c r="U68">
-        <v>2506.2271597619501</v>
+        <v>2.5062271597619499</v>
       </c>
       <c r="V68">
-        <v>2640.2970967741899</v>
+        <v>2.6402970967741899</v>
       </c>
       <c r="W68">
-        <v>867.82368865957505</v>
+        <v>0.86782368865957504</v>
       </c>
       <c r="X68">
-        <v>3011.2690725806401</v>
+        <v>3.0112690725806401</v>
       </c>
       <c r="Y68">
-        <v>989.75628057395397</v>
+        <v>0.98975628057395404</v>
       </c>
       <c r="Z68" s="4"/>
       <c r="AA68" s="4"/>
@@ -8818,76 +8818,76 @@
         <v>0.6875</v>
       </c>
       <c r="B69">
-        <v>12445.0287264529</v>
+        <v>12.4450287264529</v>
       </c>
       <c r="C69">
-        <v>4090.4831308794101</v>
+        <v>4.0904831308794103</v>
       </c>
       <c r="D69">
-        <v>18491.166437141899</v>
+        <v>18.491166437141899</v>
       </c>
       <c r="E69">
-        <v>6077.7524941054098</v>
+        <v>6.0777524941054102</v>
       </c>
       <c r="F69">
-        <v>2589.3018324148202</v>
+        <v>2.5893018324148298</v>
       </c>
       <c r="G69">
-        <v>851.06235582525903</v>
+        <v>0.85106235582525902</v>
       </c>
       <c r="H69">
-        <v>8431.7280561122207</v>
+        <v>8.4317280561122203</v>
       </c>
       <c r="I69">
-        <v>2771.3749912347598</v>
+        <v>2.7713749912347598</v>
       </c>
       <c r="J69">
-        <v>3751.90096192384</v>
+        <v>3.7519009619238401</v>
       </c>
       <c r="K69">
-        <v>1233.19021038965</v>
+        <v>1.2331902103896499</v>
       </c>
       <c r="L69">
-        <v>13496.2655861723</v>
+        <v>13.496265586172299</v>
       </c>
       <c r="M69">
-        <v>4436.0079774473397</v>
+        <v>4.43600797744734</v>
       </c>
       <c r="N69">
-        <v>18995.7164909819</v>
+        <v>18.995716490981899</v>
       </c>
       <c r="O69">
-        <v>6243.5900770697699</v>
+        <v>6.2435900770697703</v>
       </c>
       <c r="P69">
-        <v>11169.8803273213</v>
+        <v>11.1698803273213</v>
       </c>
       <c r="Q69">
-        <v>3671.3621203405901</v>
+        <v>3.6713621203405902</v>
       </c>
       <c r="R69">
-        <v>1114.9110000000001</v>
+        <v>1.114911</v>
       </c>
       <c r="S69">
-        <v>366.45352438907099</v>
+        <v>0.36645352438907097</v>
       </c>
       <c r="T69">
-        <v>7702.02246292585</v>
+        <v>7.70202246292585</v>
       </c>
       <c r="U69">
-        <v>2531.5323612942798</v>
+        <v>2.5315323612942802</v>
       </c>
       <c r="V69">
-        <v>2722.5450000000001</v>
+        <v>2.7225450000000002</v>
       </c>
       <c r="W69">
-        <v>894.85726713418796</v>
+        <v>0.89485726713418801</v>
       </c>
       <c r="X69">
-        <v>3105.0731249999999</v>
+        <v>3.1050731250000001</v>
       </c>
       <c r="Y69">
-        <v>1020.58818160556</v>
+        <v>1.02058818160556</v>
       </c>
       <c r="Z69" s="4"/>
       <c r="AA69" s="4"/>
@@ -8942,76 +8942,76 @@
         <v>0.69791666666666696</v>
       </c>
       <c r="B70">
-        <v>12890.843811203</v>
+        <v>12.890843811203</v>
       </c>
       <c r="C70">
-        <v>4237.0154630857596</v>
+        <v>4.2370154630857604</v>
       </c>
       <c r="D70">
-        <v>19149.7933790643</v>
+        <v>19.149793379064299</v>
       </c>
       <c r="E70">
-        <v>6294.23270115787</v>
+        <v>6.2942327011578696</v>
       </c>
       <c r="F70">
-        <v>2701.0710196602799</v>
+        <v>2.7010710196602798</v>
       </c>
       <c r="G70">
-        <v>887.79911112160096</v>
+        <v>0.88779911112160104</v>
       </c>
       <c r="H70">
-        <v>8728.4062124248394</v>
+        <v>8.72840621242484</v>
       </c>
       <c r="I70">
-        <v>2868.8883855684899</v>
+        <v>2.8688883855684901</v>
       </c>
       <c r="J70">
-        <v>3883.91507014028</v>
+        <v>3.8839150701402798</v>
       </c>
       <c r="K70">
-        <v>1276.5811494197501</v>
+        <v>1.2765811494197501</v>
       </c>
       <c r="L70">
-        <v>13971.1441833667</v>
+        <v>13.9711441833667</v>
       </c>
       <c r="M70">
-        <v>4592.0930242347704</v>
+        <v>4.5920930242347699</v>
       </c>
       <c r="N70">
-        <v>19664.098358717401</v>
+        <v>19.6640983587174</v>
       </c>
       <c r="O70">
-        <v>6463.2765731841901</v>
+        <v>6.4632765731841904</v>
       </c>
       <c r="P70">
-        <v>11562.902905811599</v>
+        <v>11.562902905811599</v>
       </c>
       <c r="Q70">
-        <v>3800.5423948667599</v>
+        <v>3.8005423948667598</v>
       </c>
       <c r="R70">
-        <v>1167.4311290322501</v>
+        <v>1.1674311290322501</v>
       </c>
       <c r="S70">
-        <v>383.716056003917</v>
+        <v>0.38371605600391701</v>
       </c>
       <c r="T70">
-        <v>7973.025252505</v>
+        <v>7.9730252525050096</v>
       </c>
       <c r="U70">
-        <v>2620.6066706880802</v>
+        <v>2.6206066706880802</v>
       </c>
       <c r="V70">
-        <v>2850.7959677419299</v>
+        <v>2.8507959677419299</v>
       </c>
       <c r="W70">
-        <v>937.01132170476899</v>
+        <v>0.93701132170476897</v>
       </c>
       <c r="X70">
-        <v>3251.3438508064501</v>
+        <v>3.2513438508064501</v>
       </c>
       <c r="Y70">
-        <v>1068.66504423111</v>
+        <v>1.0686650442311101</v>
       </c>
       <c r="Z70" s="4"/>
       <c r="AA70" s="4"/>
@@ -9066,76 +9066,76 @@
         <v>0.70833333333333304</v>
       </c>
       <c r="B71">
-        <v>13686.401554140501</v>
+        <v>13.686401554140501</v>
       </c>
       <c r="C71">
-        <v>4498.50264794128</v>
+        <v>4.4985026479412804</v>
       </c>
       <c r="D71">
-        <v>20346.224984455701</v>
+        <v>20.346224984455699</v>
       </c>
       <c r="E71">
-        <v>6687.4807527836601</v>
+        <v>6.6874807527836602</v>
       </c>
       <c r="F71">
-        <v>2877.0790040564998</v>
+        <v>2.87707900405649</v>
       </c>
       <c r="G71">
-        <v>945.65013797720496</v>
+        <v>0.94565013797720499</v>
       </c>
       <c r="H71">
-        <v>9264.4496993987905</v>
+        <v>9.2644496993987904</v>
       </c>
       <c r="I71">
-        <v>3045.0773594214802</v>
+        <v>3.0450773594214802</v>
       </c>
       <c r="J71">
-        <v>4122.4405611222401</v>
+        <v>4.1224405611222403</v>
       </c>
       <c r="K71">
-        <v>1354.9806869855099</v>
+        <v>1.3549806869855101</v>
       </c>
       <c r="L71">
-        <v>14829.1634669338</v>
+        <v>14.829163466933799</v>
       </c>
       <c r="M71">
-        <v>4874.1103246802404</v>
+        <v>4.87411032468024</v>
       </c>
       <c r="N71">
-        <v>20871.742869739399</v>
+        <v>20.8717428697394</v>
       </c>
       <c r="O71">
-        <v>6860.2101286636298</v>
+        <v>6.8602101286636303</v>
       </c>
       <c r="P71">
-        <v>12273.023246492899</v>
+        <v>12.273023246492899</v>
       </c>
       <c r="Q71">
-        <v>4033.9476636129298</v>
+        <v>4.0339476636129303</v>
       </c>
       <c r="R71">
-        <v>1245.6404516129001</v>
+        <v>1.2456404516129</v>
       </c>
       <c r="S71">
-        <v>409.42221721298199</v>
+        <v>0.409422217212982</v>
       </c>
       <c r="T71">
-        <v>8462.6780200400808</v>
+        <v>8.4626780200400802</v>
       </c>
       <c r="U71">
-        <v>2781.5477524337002</v>
+        <v>2.7815477524337</v>
       </c>
       <c r="V71">
-        <v>3041.7783870967701</v>
+        <v>3.0417783870967701</v>
       </c>
       <c r="W71">
-        <v>999.78420731530798</v>
+        <v>0.99978420731530804</v>
       </c>
       <c r="X71">
-        <v>3469.1600403225798</v>
+        <v>3.46916004032258</v>
       </c>
       <c r="Y71">
-        <v>1140.25776357569</v>
+        <v>1.1402577635756901</v>
       </c>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
@@ -9190,76 +9190,76 @@
         <v>0.71875</v>
       </c>
       <c r="B72">
-        <v>14735.9621732174</v>
+        <v>14.7359621732174</v>
       </c>
       <c r="C72">
-        <v>4843.4765408535304</v>
+        <v>4.8434765408535299</v>
       </c>
       <c r="D72">
-        <v>21911.0485550634</v>
+        <v>21.911048555063399</v>
       </c>
       <c r="E72">
-        <v>7201.8133878516401</v>
+        <v>7.2018133878516402</v>
       </c>
       <c r="F72">
-        <v>3142.2899945455401</v>
+        <v>3.14228999454554</v>
       </c>
       <c r="G72">
-        <v>1032.8207750696899</v>
+        <v>1.0328207750696901</v>
       </c>
       <c r="H72">
-        <v>9962.3176352705395</v>
+        <v>9.96231763527053</v>
       </c>
       <c r="I72">
-        <v>3274.4554574565</v>
+        <v>3.2744554574564999</v>
       </c>
       <c r="J72">
-        <v>4432.9737474949898</v>
+        <v>4.43297374749499</v>
       </c>
       <c r="K72">
-        <v>1457.04800947678</v>
+        <v>1.4570480094767799</v>
       </c>
       <c r="L72">
-        <v>15946.207439879699</v>
+        <v>15.9462074398797</v>
       </c>
       <c r="M72">
-        <v>5241.2649233734001</v>
+        <v>5.2412649233734001</v>
       </c>
       <c r="N72">
-        <v>22443.959308617199</v>
+        <v>22.443959308617199</v>
       </c>
       <c r="O72">
-        <v>7376.9726820236701</v>
+        <v>7.3769726820236698</v>
       </c>
       <c r="P72">
-        <v>13197.519539078099</v>
+        <v>13.197519539078099</v>
       </c>
       <c r="Q72">
-        <v>4337.8149002824603</v>
+        <v>4.33781490028246</v>
       </c>
       <c r="R72">
-        <v>1370.66119354838</v>
+        <v>1.3706611935483799</v>
       </c>
       <c r="S72">
-        <v>450.51454790484399</v>
+        <v>0.45051454790484402</v>
       </c>
       <c r="T72">
-        <v>9100.1504909819596</v>
+        <v>9.1001504909819602</v>
       </c>
       <c r="U72">
-        <v>2991.07482112139</v>
+        <v>2.9910748211213898</v>
       </c>
       <c r="V72">
-        <v>3347.0714516129001</v>
+        <v>3.3470714516129001</v>
       </c>
       <c r="W72">
-        <v>1100.1291850431001</v>
+        <v>1.1001291850431001</v>
       </c>
       <c r="X72">
-        <v>3817.3479637096698</v>
+        <v>3.8173479637096701</v>
       </c>
       <c r="Y72">
-        <v>1254.70159960827</v>
+        <v>1.25470159960827</v>
       </c>
       <c r="Z72" s="4"/>
       <c r="AA72" s="4"/>
@@ -9314,76 +9314,76 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="B73">
-        <v>15884.936051651601</v>
+        <v>15.8849360516516</v>
       </c>
       <c r="C73">
-        <v>5221.12599196059</v>
+        <v>5.2211259919605997</v>
       </c>
       <c r="D73">
-        <v>23587.670104106499</v>
+        <v>23.5876701041065</v>
       </c>
       <c r="E73">
-        <v>7752.8922414224699</v>
+        <v>7.7528922414224697</v>
       </c>
       <c r="F73">
-        <v>3523.4308595416601</v>
+        <v>3.5234308595416599</v>
       </c>
       <c r="G73">
-        <v>1158.09571922804</v>
+        <v>1.1580957192280401</v>
       </c>
       <c r="H73">
-        <v>10700.641683366701</v>
+        <v>10.700641683366699</v>
       </c>
       <c r="I73">
-        <v>3517.1308365370301</v>
+        <v>3.5171308365370302</v>
       </c>
       <c r="J73">
-        <v>4761.5088577154302</v>
+        <v>4.7615088577154303</v>
       </c>
       <c r="K73">
-        <v>1565.03227819942</v>
+        <v>1.5650322781994199</v>
       </c>
       <c r="L73">
-        <v>17128.0075851703</v>
+        <v>17.128007585170302</v>
       </c>
       <c r="M73">
-        <v>5629.7038466284903</v>
+        <v>5.6297038466284901</v>
       </c>
       <c r="N73">
-        <v>24107.318729458901</v>
+        <v>24.1073187294589</v>
       </c>
       <c r="O73">
-        <v>7923.6924848538501</v>
+        <v>7.9236924848538504</v>
       </c>
       <c r="P73">
-        <v>14175.609819639199</v>
+        <v>14.175609819639201</v>
       </c>
       <c r="Q73">
-        <v>4659.2976289328399</v>
+        <v>4.6592976289328396</v>
       </c>
       <c r="R73">
-        <v>1567.6116774193499</v>
+        <v>1.56761167741935</v>
       </c>
       <c r="S73">
-        <v>515.24904146051699</v>
+        <v>0.51524904146051698</v>
       </c>
       <c r="T73">
-        <v>9774.5778877755492</v>
+        <v>9.7745778877755498</v>
       </c>
       <c r="U73">
-        <v>3212.7483865446002</v>
+        <v>3.21274838654461</v>
       </c>
       <c r="V73">
-        <v>3828.0125806451601</v>
+        <v>3.8280125806451601</v>
       </c>
       <c r="W73">
-        <v>1258.20688968278</v>
+        <v>1.25820688968278</v>
       </c>
       <c r="X73">
-        <v>4365.8631854838704</v>
+        <v>4.3658631854838701</v>
       </c>
       <c r="Y73">
-        <v>1434.9898344541</v>
+        <v>1.4349898344541001</v>
       </c>
       <c r="Z73" s="4"/>
       <c r="AA73" s="4"/>
@@ -9438,76 +9438,76 @@
         <v>0.73958333333333304</v>
       </c>
       <c r="B74">
-        <v>16987.813578253201</v>
+        <v>16.987813578253199</v>
       </c>
       <c r="C74">
-        <v>5583.6243049135201</v>
+        <v>5.5836243049135197</v>
       </c>
       <c r="D74">
-        <v>25122.028481615202</v>
+        <v>25.1220284816152</v>
       </c>
       <c r="E74">
-        <v>8257.2114517576101</v>
+        <v>8.2572114517576107</v>
       </c>
       <c r="F74">
-        <v>4047.0255567586701</v>
+        <v>4.0470255567586699</v>
       </c>
       <c r="G74">
-        <v>1330.19297375921</v>
+        <v>1.33019297375921</v>
       </c>
       <c r="H74">
-        <v>11364.7961923847</v>
+        <v>11.3647961923847</v>
       </c>
       <c r="I74">
-        <v>3735.42786703413</v>
+        <v>3.7354278670341299</v>
       </c>
       <c r="J74">
-        <v>5057.0404408817603</v>
+        <v>5.0570404408817602</v>
       </c>
       <c r="K74">
-        <v>1662.16881216454</v>
+        <v>1.6621688121645399</v>
       </c>
       <c r="L74">
-        <v>18191.088081162299</v>
+        <v>18.191088081162299</v>
       </c>
       <c r="M74">
-        <v>5979.1215081867203</v>
+        <v>5.9791215081867204</v>
       </c>
       <c r="N74">
-        <v>25603.582683366702</v>
+        <v>25.6035826833667</v>
       </c>
       <c r="O74">
-        <v>8415.4906636554297</v>
+        <v>8.4154906636554294</v>
       </c>
       <c r="P74">
-        <v>15055.444455577801</v>
+        <v>15.055444455577801</v>
       </c>
       <c r="Q74">
-        <v>4948.4852889516696</v>
+        <v>4.9484852889516704</v>
       </c>
       <c r="R74">
-        <v>1861.0393548387101</v>
+        <v>1.8610393548387101</v>
       </c>
       <c r="S74">
-        <v>611.69405504781002</v>
+        <v>0.61169405504781005</v>
       </c>
       <c r="T74">
-        <v>10381.2545871743</v>
+        <v>10.3812545871743</v>
       </c>
       <c r="U74">
-        <v>3412.15337461936</v>
+        <v>3.41215337461936</v>
       </c>
       <c r="V74">
-        <v>4544.5451612903198</v>
+        <v>4.54454516129032</v>
       </c>
       <c r="W74">
-        <v>1493.71975978364</v>
+        <v>1.49371975978364</v>
       </c>
       <c r="X74">
-        <v>5183.0713709677402</v>
+        <v>5.1830713709677401</v>
       </c>
       <c r="Y74">
-        <v>1703.5931756447101</v>
+        <v>1.70359317564471</v>
       </c>
       <c r="Z74" s="4"/>
       <c r="AA74" s="4"/>
@@ -9562,76 +9562,76 @@
         <v>0.75</v>
       </c>
       <c r="B75">
-        <v>17926.214277102499</v>
+        <v>17.926214277102499</v>
       </c>
       <c r="C75">
-        <v>5892.0616989140199</v>
+        <v>5.89206169891402</v>
       </c>
       <c r="D75">
-        <v>26324.222306232699</v>
+        <v>26.324222306232699</v>
       </c>
       <c r="E75">
-        <v>8652.3534532535596</v>
+        <v>8.6523534532535606</v>
       </c>
       <c r="F75">
-        <v>4714.8244454634996</v>
+        <v>4.7148244454635</v>
       </c>
       <c r="G75">
-        <v>1549.6878539326001</v>
+        <v>1.5496878539326</v>
       </c>
       <c r="H75">
-        <v>11867.126252505001</v>
+        <v>11.867126252505001</v>
       </c>
       <c r="I75">
-        <v>3900.5357733492001</v>
+        <v>3.9005357733491999</v>
       </c>
       <c r="J75">
-        <v>5280.5643286573104</v>
+        <v>5.2805643286573103</v>
       </c>
       <c r="K75">
-        <v>1735.63756120415</v>
+        <v>1.7356375612041499</v>
       </c>
       <c r="L75">
-        <v>18995.143887775499</v>
+        <v>18.995143887775502</v>
       </c>
       <c r="M75">
-        <v>6243.4018714972499</v>
+        <v>6.2434018714972499</v>
       </c>
       <c r="N75">
-        <v>26735.274709418802</v>
+        <v>26.7352747094188</v>
       </c>
       <c r="O75">
-        <v>8787.4598445764204</v>
+        <v>8.7874598445764196</v>
       </c>
       <c r="P75">
-        <v>15720.903139612499</v>
+        <v>15.720903139612499</v>
       </c>
       <c r="Q75">
-        <v>5167.2109810471302</v>
+        <v>5.1672109810471296</v>
       </c>
       <c r="R75">
-        <v>2257.7946774193501</v>
+        <v>2.25779467741935</v>
       </c>
       <c r="S75">
-        <v>742.10122322517998</v>
+        <v>0.74210122322518002</v>
       </c>
       <c r="T75">
-        <v>10840.111583166299</v>
+        <v>10.8401115831663</v>
       </c>
       <c r="U75">
-        <v>3562.9723757520501</v>
+        <v>3.5629723757520502</v>
       </c>
       <c r="V75">
-        <v>5513.3975806451599</v>
+        <v>5.5133975806451598</v>
       </c>
       <c r="W75">
-        <v>1812.16615028966</v>
+        <v>1.81216615028966</v>
       </c>
       <c r="X75">
-        <v>6288.0513104838701</v>
+        <v>6.28805131048387</v>
       </c>
       <c r="Y75">
-        <v>2066.78251830516</v>
+        <v>2.06678251830516</v>
       </c>
       <c r="Z75" s="4"/>
       <c r="AA75" s="4"/>
@@ -9686,76 +9686,76 @@
         <v>0.76041666666666696</v>
       </c>
       <c r="B76">
-        <v>18685.904412179199</v>
+        <v>18.685904412179099</v>
       </c>
       <c r="C76">
-        <v>6141.7597711748904</v>
+        <v>6.1417597711748897</v>
       </c>
       <c r="D76">
-        <v>27205.504515586999</v>
+        <v>27.205504515586998</v>
       </c>
       <c r="E76">
-        <v>8942.0169076452294</v>
+        <v>8.9420169076452307</v>
       </c>
       <c r="F76">
-        <v>5430.0286864050604</v>
+        <v>5.43002868640506</v>
       </c>
       <c r="G76">
-        <v>1784.7641198865999</v>
+        <v>1.7847641198866</v>
       </c>
       <c r="H76">
-        <v>12224.488577154299</v>
+        <v>12.2244885771543</v>
       </c>
       <c r="I76">
-        <v>4017.9950892511902</v>
+        <v>4.0179950892511904</v>
       </c>
       <c r="J76">
-        <v>5439.5813226452901</v>
+        <v>5.4395813226452896</v>
       </c>
       <c r="K76">
-        <v>1787.90391958132</v>
+        <v>1.78790391958132</v>
       </c>
       <c r="L76">
-        <v>19567.156743486899</v>
+        <v>19.567156743486901</v>
       </c>
       <c r="M76">
-        <v>6431.4134051275696</v>
+        <v>6.4314134051275698</v>
       </c>
       <c r="N76">
-        <v>27540.371050100199</v>
+        <v>27.540371050100099</v>
       </c>
       <c r="O76">
-        <v>9052.0822148960506</v>
+        <v>9.0520822148960498</v>
       </c>
       <c r="P76">
-        <v>16194.3167000668</v>
+        <v>16.1943167000668</v>
       </c>
       <c r="Q76">
-        <v>5322.8144935445698</v>
+        <v>5.3228144935445698</v>
       </c>
       <c r="R76">
-        <v>2694.51096774193</v>
+        <v>2.6945109677419299</v>
       </c>
       <c r="S76">
-        <v>885.64292632689001</v>
+        <v>0.88564292632689001</v>
       </c>
       <c r="T76">
-        <v>11166.546761523001</v>
+        <v>11.166546761523</v>
       </c>
       <c r="U76">
-        <v>3670.2664302491298</v>
+        <v>3.6702664302491299</v>
       </c>
       <c r="V76">
-        <v>6579.8322580645099</v>
+        <v>6.5798322580645099</v>
       </c>
       <c r="W76">
-        <v>2162.68627796895</v>
+        <v>2.16268627796895</v>
       </c>
       <c r="X76">
-        <v>7504.3241935483802</v>
+        <v>7.5043241935483804</v>
       </c>
       <c r="Y76">
-        <v>2466.5520825285398</v>
+        <v>2.4665520825285401</v>
       </c>
       <c r="Z76" s="4"/>
       <c r="AA76" s="4"/>
@@ -9810,76 +9810,76 @@
         <v>0.77083333333333304</v>
       </c>
       <c r="B77">
-        <v>19308.721415637701</v>
+        <v>19.308721415637699</v>
       </c>
       <c r="C77">
-        <v>6346.4698206468302</v>
+        <v>6.3464698206468304</v>
       </c>
       <c r="D77">
-        <v>27858.096790343901</v>
+        <v>27.8580967903439</v>
       </c>
       <c r="E77">
-        <v>9156.51361552036</v>
+        <v>9.1565136155203604</v>
       </c>
       <c r="F77">
-        <v>6074.8945089776298</v>
+        <v>6.0748945089776303</v>
       </c>
       <c r="G77">
-        <v>1996.7212657393</v>
+        <v>1.9967212657393001</v>
       </c>
       <c r="H77">
-        <v>12500.938677354699</v>
+        <v>12.5009386773547</v>
       </c>
       <c r="I77">
-        <v>4108.8598430621696</v>
+        <v>4.1088598430621701</v>
       </c>
       <c r="J77">
-        <v>5562.5944689378703</v>
+        <v>5.5625944689378697</v>
       </c>
       <c r="K77">
-        <v>1828.3363854957299</v>
+        <v>1.82833638549573</v>
       </c>
       <c r="L77">
-        <v>20009.657254508998</v>
+        <v>20.009657254509001</v>
       </c>
       <c r="M77">
-        <v>6576.85628963404</v>
+        <v>6.5768562896340397</v>
       </c>
       <c r="N77">
-        <v>28163.181426853698</v>
+        <v>28.163181426853701</v>
       </c>
       <c r="O77">
-        <v>9256.7900862753904</v>
+        <v>9.2567900862753891</v>
       </c>
       <c r="P77">
-        <v>16560.542284569099</v>
+        <v>16.560542284569099</v>
       </c>
       <c r="Q77">
-        <v>5443.1870220803303</v>
+        <v>5.4431870220803296</v>
       </c>
       <c r="R77">
-        <v>3091.2662903225801</v>
+        <v>3.0912662903225798</v>
       </c>
       <c r="S77">
-        <v>1016.05009450426</v>
+        <v>1.0160500945042601</v>
       </c>
       <c r="T77">
-        <v>11419.072088176301</v>
+        <v>11.4190720881763</v>
       </c>
       <c r="U77">
-        <v>3753.26749127517</v>
+        <v>3.75326749127517</v>
       </c>
       <c r="V77">
-        <v>7548.68467741935</v>
+        <v>7.5486846774193497</v>
       </c>
       <c r="W77">
-        <v>2481.1326684749702</v>
+        <v>2.4811326684749702</v>
       </c>
       <c r="X77">
-        <v>8609.3041330645101</v>
+        <v>8.6093041330645104</v>
       </c>
       <c r="Y77">
-        <v>2829.74142518899</v>
+        <v>2.8297414251889901</v>
       </c>
       <c r="Z77" s="4"/>
       <c r="AA77" s="4"/>
@@ -9934,76 +9934,76 @@
         <v>0.78125</v>
       </c>
       <c r="B78">
-        <v>19803.531288770999</v>
+        <v>19.803531288771001</v>
       </c>
       <c r="C78">
-        <v>6509.1059610313396</v>
+        <v>6.5091059610313398</v>
       </c>
       <c r="D78">
-        <v>28343.282038462199</v>
+        <v>28.343282038462199</v>
       </c>
       <c r="E78">
-        <v>9315.9862946441099</v>
+        <v>9.3159862946441105</v>
       </c>
       <c r="F78">
-        <v>6529.2821505914999</v>
+        <v>6.5292821505915004</v>
       </c>
       <c r="G78">
-        <v>2146.0712611274898</v>
+        <v>2.1460712611274899</v>
       </c>
       <c r="H78">
-        <v>12736.9326653306</v>
+        <v>12.736932665330601</v>
       </c>
       <c r="I78">
-        <v>4186.4273158276401</v>
+        <v>4.1864273158276397</v>
       </c>
       <c r="J78">
-        <v>5667.6056913827597</v>
+        <v>5.6676056913827599</v>
       </c>
       <c r="K78">
-        <v>1862.85190517877</v>
+        <v>1.86285190517877</v>
       </c>
       <c r="L78">
-        <v>20387.4015931863</v>
+        <v>20.387401593186301</v>
       </c>
       <c r="M78">
-        <v>6701.0148495785897</v>
+        <v>6.7010148495785904</v>
       </c>
       <c r="N78">
-        <v>28694.848821643202</v>
+        <v>28.694848821643198</v>
       </c>
       <c r="O78">
-        <v>9431.5407081845697</v>
+        <v>9.4315407081845795</v>
       </c>
       <c r="P78">
-        <v>16873.173881095499</v>
+        <v>16.8731738810955</v>
       </c>
       <c r="Q78">
-        <v>5545.9440586352403</v>
+        <v>5.5459440586352402</v>
       </c>
       <c r="R78">
-        <v>3368.1387096774201</v>
+        <v>3.36813870967742</v>
       </c>
       <c r="S78">
-        <v>1107.0536579086099</v>
+        <v>1.1070536579086101</v>
       </c>
       <c r="T78">
-        <v>11634.642488977899</v>
+        <v>11.634642488977899</v>
       </c>
       <c r="U78">
-        <v>3824.1220555657001</v>
+        <v>3.8241220555657001</v>
       </c>
       <c r="V78">
-        <v>8224.7903225806403</v>
+        <v>8.22479032258064</v>
       </c>
       <c r="W78">
-        <v>2703.35784746119</v>
+        <v>2.7033578474611901</v>
       </c>
       <c r="X78">
-        <v>9380.4052419354794</v>
+        <v>9.3804052419354793</v>
       </c>
       <c r="Y78">
-        <v>3083.1901031606799</v>
+        <v>3.0831901031606801</v>
       </c>
       <c r="Z78" s="4"/>
       <c r="AA78" s="4"/>
@@ -10058,76 +10058,76 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B79">
-        <v>20185.0423284633</v>
+        <v>20.1850423284633</v>
       </c>
       <c r="C79">
-        <v>6634.5025757284602</v>
+        <v>6.6345025757284599</v>
       </c>
       <c r="D79">
-        <v>28717.569052737501</v>
+        <v>28.717569052737499</v>
       </c>
       <c r="E79">
-        <v>9439.0084870112496</v>
+        <v>9.4390084870112503</v>
       </c>
       <c r="F79">
-        <v>6700.2214390878498</v>
+        <v>6.7002214390878496</v>
       </c>
       <c r="G79">
-        <v>2202.25628820682</v>
+        <v>2.20225628820682</v>
       </c>
       <c r="H79">
-        <v>12969.555310621199</v>
+        <v>12.9695553106212</v>
       </c>
       <c r="I79">
-        <v>4262.8866818393099</v>
+        <v>4.2628866818393103</v>
       </c>
       <c r="J79">
-        <v>5771.1167535070099</v>
+        <v>5.7711167535070098</v>
       </c>
       <c r="K79">
-        <v>1896.87434600919</v>
+        <v>1.8968743460091899</v>
       </c>
       <c r="L79">
-        <v>20759.749584168301</v>
+        <v>20.759749584168301</v>
       </c>
       <c r="M79">
-        <v>6823.3997158096399</v>
+        <v>6.8233997158096402</v>
       </c>
       <c r="N79">
-        <v>29218.920967935799</v>
+        <v>29.218920967935802</v>
       </c>
       <c r="O79">
-        <v>9603.7948926379195</v>
+        <v>9.6037948926379197</v>
       </c>
       <c r="P79">
-        <v>17181.339311957199</v>
+        <v>17.181339311957199</v>
       </c>
       <c r="Q79">
-        <v>5647.2331375250897</v>
+        <v>5.6472331375250899</v>
       </c>
       <c r="R79">
-        <v>3462.9032903225798</v>
+        <v>3.46290329032258</v>
       </c>
       <c r="S79">
-        <v>1138.20126930061</v>
+        <v>1.1382012693006101</v>
       </c>
       <c r="T79">
-        <v>11847.133312625199</v>
+        <v>11.8471333126252</v>
       </c>
       <c r="U79">
-        <v>3893.9644117949301</v>
+        <v>3.8939644117949301</v>
       </c>
       <c r="V79">
-        <v>8456.1996774193503</v>
+        <v>8.4561996774193506</v>
       </c>
       <c r="W79">
-        <v>2779.41842418637</v>
+        <v>2.7794184241863702</v>
       </c>
       <c r="X79">
-        <v>9644.3285080645092</v>
+        <v>9.6443285080645094</v>
       </c>
       <c r="Y79">
-        <v>3169.9374857241801</v>
+        <v>3.16993748572418</v>
       </c>
       <c r="Z79" s="4"/>
       <c r="AA79" s="4"/>
@@ -10182,76 +10182,76 @@
         <v>0.80208333333333304</v>
       </c>
       <c r="B80">
-        <v>20364.211935677798</v>
+        <v>20.364211935677702</v>
       </c>
       <c r="C80">
-        <v>6693.3927777509798</v>
+        <v>6.6933927777509803</v>
       </c>
       <c r="D80">
-        <v>28893.056706514199</v>
+        <v>28.893056706514098</v>
       </c>
       <c r="E80">
-        <v>9496.6884894627692</v>
+        <v>9.4966884894627697</v>
       </c>
       <c r="F80">
-        <v>6606.2613138373499</v>
+        <v>6.6062613138373498</v>
       </c>
       <c r="G80">
-        <v>2171.37308851637</v>
+        <v>2.1713730885163698</v>
       </c>
       <c r="H80">
-        <v>13128.0084168336</v>
+        <v>13.1280084168336</v>
       </c>
       <c r="I80">
-        <v>4314.9676992675504</v>
+        <v>4.3149676992675499</v>
       </c>
       <c r="J80">
-        <v>5841.6242885771499</v>
+        <v>5.8416242885771501</v>
       </c>
       <c r="K80">
-        <v>1920.0490520820899</v>
+        <v>1.9200490520820901</v>
       </c>
       <c r="L80">
-        <v>21013.377925851699</v>
+        <v>21.0133779258517</v>
       </c>
       <c r="M80">
-        <v>6906.76332034384</v>
+        <v>6.9067633203438401</v>
       </c>
       <c r="N80">
-        <v>29575.8976472945</v>
+        <v>29.5758976472945</v>
       </c>
       <c r="O80">
-        <v>9721.1274530626597</v>
+        <v>9.7211274530626604</v>
       </c>
       <c r="P80">
-        <v>17391.249098196298</v>
+        <v>17.391249098196301</v>
       </c>
       <c r="Q80">
-        <v>5716.2271477833901</v>
+        <v>5.7162271477833899</v>
       </c>
       <c r="R80">
-        <v>3392.1152903225802</v>
+        <v>3.3921152903225802</v>
       </c>
       <c r="S80">
-        <v>1114.93437886321</v>
+        <v>1.11493437886321</v>
       </c>
       <c r="T80">
-        <v>11991.873438877699</v>
+        <v>11.9918734388777</v>
       </c>
       <c r="U80">
-        <v>3941.5381906757102</v>
+        <v>3.9415381906757099</v>
       </c>
       <c r="V80">
-        <v>8283.3396774193498</v>
+        <v>8.2833396774193506</v>
       </c>
       <c r="W80">
-        <v>2722.6020897651501</v>
+        <v>2.7226020897651502</v>
       </c>
       <c r="X80">
-        <v>9447.18100806451</v>
+        <v>9.4471810080645096</v>
       </c>
       <c r="Y80">
-        <v>3105.1382360984298</v>
+        <v>3.1051382360984299</v>
       </c>
       <c r="Z80" s="4"/>
       <c r="AA80" s="4"/>
@@ -10306,76 +10306,76 @@
         <v>0.8125</v>
       </c>
       <c r="B81">
-        <v>20248.759801376898</v>
+        <v>20.248759801376899</v>
       </c>
       <c r="C81">
-        <v>6655.4454962973095</v>
+        <v>6.6554454962973102</v>
       </c>
       <c r="D81">
-        <v>28764.365749276199</v>
+        <v>28.764365749276202</v>
       </c>
       <c r="E81">
-        <v>9454.3898173384005</v>
+        <v>9.4543898173384004</v>
       </c>
       <c r="F81">
-        <v>6293.3232153419704</v>
+        <v>6.29332321534197</v>
       </c>
       <c r="G81">
-        <v>2068.51530963604</v>
+        <v>2.06851530963604</v>
       </c>
       <c r="H81">
-        <v>13131.379759519001</v>
+        <v>13.131379759519</v>
       </c>
       <c r="I81">
-        <v>4316.0758060213402</v>
+        <v>4.31607580602134</v>
       </c>
       <c r="J81">
-        <v>5843.12444889779</v>
+        <v>5.8431244488977896</v>
       </c>
       <c r="K81">
-        <v>1920.5421309347</v>
+        <v>1.9205421309347099</v>
       </c>
       <c r="L81">
-        <v>21018.774273546998</v>
+        <v>21.018774273547098</v>
       </c>
       <c r="M81">
-        <v>6908.5370140573305</v>
+        <v>6.9085370140573303</v>
       </c>
       <c r="N81">
-        <v>29583.4928957915</v>
+        <v>29.583492895791501</v>
       </c>
       <c r="O81">
-        <v>9723.6238905185091</v>
+        <v>9.7236238905185104</v>
       </c>
       <c r="P81">
-        <v>17395.715263860999</v>
+        <v>17.395715263861</v>
       </c>
       <c r="Q81">
-        <v>5717.6951054484598</v>
+        <v>5.7176951054484597</v>
       </c>
       <c r="R81">
-        <v>3190.5978387096702</v>
+        <v>3.1905978387096701</v>
       </c>
       <c r="S81">
-        <v>1048.6987956019</v>
+        <v>1.0486987956019</v>
       </c>
       <c r="T81">
-        <v>11994.953016031999</v>
+        <v>11.994953016031999</v>
       </c>
       <c r="U81">
-        <v>3942.5503987369998</v>
+        <v>3.9425503987370001</v>
       </c>
       <c r="V81">
-        <v>7791.2462903225796</v>
+        <v>7.7912462903225803</v>
       </c>
       <c r="W81">
-        <v>2560.8588151628101</v>
+        <v>2.5608588151628102</v>
       </c>
       <c r="X81">
-        <v>8885.9465927419296</v>
+        <v>8.8859465927419308</v>
       </c>
       <c r="Y81">
-        <v>2920.6694045025502</v>
+        <v>2.9206694045025499</v>
       </c>
       <c r="Z81" s="4"/>
       <c r="AA81" s="4"/>
@@ -10430,76 +10430,76 @@
         <v>0.82291666666666696</v>
       </c>
       <c r="B82">
-        <v>19719.165599747801</v>
+        <v>19.7191655997478</v>
       </c>
       <c r="C82">
-        <v>6481.37630002695</v>
+        <v>6.48137630002695</v>
       </c>
       <c r="D82">
-        <v>28199.354612887601</v>
+        <v>28.1993546128876</v>
       </c>
       <c r="E82">
-        <v>9268.6796375584308</v>
+        <v>9.2686796375584297</v>
       </c>
       <c r="F82">
-        <v>5807.9373162049897</v>
+        <v>5.8079373162049901</v>
       </c>
       <c r="G82">
-        <v>1908.97667971176</v>
+        <v>1.90897667971176</v>
       </c>
       <c r="H82">
-        <v>12878.529058116201</v>
+        <v>12.8785290581162</v>
       </c>
       <c r="I82">
-        <v>4232.9677994869198</v>
+        <v>4.2329677994869197</v>
       </c>
       <c r="J82">
-        <v>5730.6124248496899</v>
+        <v>5.7306124248496904</v>
       </c>
       <c r="K82">
-        <v>1883.5612169885901</v>
+        <v>1.88356121698859</v>
       </c>
       <c r="L82">
-        <v>20614.048196392701</v>
+        <v>20.614048196392702</v>
       </c>
       <c r="M82">
-        <v>6775.50998554532</v>
+        <v>6.7755099855453196</v>
       </c>
       <c r="N82">
-        <v>29013.849258516999</v>
+        <v>29.013849258516998</v>
       </c>
       <c r="O82">
-        <v>9536.3910813300899</v>
+        <v>9.5363910813300894</v>
       </c>
       <c r="P82">
-        <v>17060.7528390113</v>
+        <v>17.0607528390113</v>
       </c>
       <c r="Q82">
-        <v>5607.5982805681897</v>
+        <v>5.6075982805681903</v>
       </c>
       <c r="R82">
-        <v>2894.8866774193498</v>
+        <v>2.89488667741935</v>
       </c>
       <c r="S82">
-        <v>951.50323716179298</v>
+        <v>0.95150323716179297</v>
       </c>
       <c r="T82">
-        <v>11763.9847294589</v>
+        <v>11.763984729458899</v>
       </c>
       <c r="U82">
-        <v>3866.6347941400099</v>
+        <v>3.8666347941400101</v>
       </c>
       <c r="V82">
-        <v>7069.1375806451597</v>
+        <v>7.06913758064516</v>
       </c>
       <c r="W82">
-        <v>2323.5131600806199</v>
+        <v>2.32351316008062</v>
       </c>
       <c r="X82">
-        <v>8062.3788104838704</v>
+        <v>8.0623788104838692</v>
       </c>
       <c r="Y82">
-        <v>2649.9757649369099</v>
+        <v>2.6499757649369098</v>
       </c>
       <c r="Z82" s="4"/>
       <c r="AA82" s="4"/>
@@ -10554,76 +10554,76 @@
         <v>0.83333333333333304</v>
       </c>
       <c r="B83">
-        <v>18743.700872616198</v>
+        <v>18.743700872616198</v>
       </c>
       <c r="C83">
-        <v>6160.7565490561301</v>
+        <v>6.1607565490561296</v>
       </c>
       <c r="D83">
-        <v>27156.690261035201</v>
+        <v>27.156690261035202</v>
       </c>
       <c r="E83">
-        <v>8925.9724380679199</v>
+        <v>8.9259724380679195</v>
       </c>
       <c r="F83">
-        <v>5198.6997966497502</v>
+        <v>5.1986997966497501</v>
       </c>
       <c r="G83">
-        <v>1708.7299907553599</v>
+        <v>1.7087299907553599</v>
       </c>
       <c r="H83">
-        <v>12332.371543086099</v>
+        <v>12.332371543086101</v>
       </c>
       <c r="I83">
-        <v>4053.4545053725501</v>
+        <v>4.0534545053725504</v>
       </c>
       <c r="J83">
-        <v>5487.5864529058099</v>
+        <v>5.48758645290581</v>
       </c>
       <c r="K83">
-        <v>1803.68244286499</v>
+        <v>1.80368244286499</v>
       </c>
       <c r="L83">
-        <v>19739.8398697394</v>
+        <v>19.739839869739399</v>
       </c>
       <c r="M83">
-        <v>6488.1716039593603</v>
+        <v>6.4881716039593602</v>
       </c>
       <c r="N83">
-        <v>27783.419002004001</v>
+        <v>27.783419002003999</v>
       </c>
       <c r="O83">
-        <v>9131.9682134831091</v>
+        <v>9.1319682134831108</v>
       </c>
       <c r="P83">
-        <v>16337.234001336001</v>
+        <v>16.337234001336</v>
       </c>
       <c r="Q83">
-        <v>5369.7891388268199</v>
+        <v>5.3697891388268202</v>
       </c>
       <c r="R83">
-        <v>2538.6631935483801</v>
+        <v>2.5386631935483801</v>
       </c>
       <c r="S83">
-        <v>834.41824012196605</v>
+        <v>0.83441824012196597</v>
       </c>
       <c r="T83">
-        <v>11265.0932304609</v>
+        <v>11.2650932304609</v>
       </c>
       <c r="U83">
-        <v>3702.6570882105102</v>
+        <v>3.7026570882105099</v>
       </c>
       <c r="V83">
-        <v>6199.2614516128997</v>
+        <v>6.1992614516128999</v>
       </c>
       <c r="W83">
-        <v>2037.5987029932</v>
+        <v>2.0375987029932001</v>
       </c>
       <c r="X83">
-        <v>7070.2817137096699</v>
+        <v>7.0702817137096696</v>
       </c>
       <c r="Y83">
-        <v>2323.8892184331398</v>
+        <v>2.3238892184331399</v>
       </c>
       <c r="Z83" s="4"/>
       <c r="AA83" s="4"/>
@@ -10678,76 +10678,76 @@
         <v>0.84375</v>
       </c>
       <c r="B84">
-        <v>17478.760375686801</v>
+        <v>17.4787603756868</v>
       </c>
       <c r="C84">
-        <v>5744.9907137184</v>
+        <v>5.7449907137184004</v>
       </c>
       <c r="D84">
-        <v>25792.344887304102</v>
+        <v>25.7923448873041</v>
       </c>
       <c r="E84">
-        <v>8477.5337997481893</v>
+        <v>8.4775337997481905</v>
       </c>
       <c r="F84">
-        <v>4539.0931729992199</v>
+        <v>4.5390931729992197</v>
       </c>
       <c r="G84">
-        <v>1491.9277778907301</v>
+        <v>1.4919277778907301</v>
       </c>
       <c r="H84">
-        <v>11587.3048096192</v>
+        <v>11.5873048096192</v>
       </c>
       <c r="I84">
-        <v>3808.56291278443</v>
+        <v>3.80856291278443</v>
       </c>
       <c r="J84">
-        <v>5156.0510220440801</v>
+        <v>5.1560510220440801</v>
       </c>
       <c r="K84">
-        <v>1694.7120164371199</v>
+        <v>1.6947120164371201</v>
       </c>
       <c r="L84">
-        <v>18547.2470290581</v>
+        <v>18.547247029058099</v>
       </c>
       <c r="M84">
-        <v>6096.1852932772899</v>
+        <v>6.0961852932772898</v>
       </c>
       <c r="N84">
-        <v>26104.869084168298</v>
+        <v>26.1048690841683</v>
       </c>
       <c r="O84">
-        <v>8580.2555357412293</v>
+        <v>8.5802555357412302</v>
       </c>
       <c r="P84">
-        <v>15350.2113894455</v>
+        <v>15.3502113894455</v>
       </c>
       <c r="Q84">
-        <v>5045.3704948463001</v>
+        <v>5.0453704948463001</v>
       </c>
       <c r="R84">
-        <v>2163.03009677419</v>
+        <v>2.16303009677419</v>
       </c>
       <c r="S84">
-        <v>710.95361183317505</v>
+        <v>0.71095361183317496</v>
       </c>
       <c r="T84">
-        <v>10584.506679358699</v>
+        <v>10.5845066793587</v>
       </c>
       <c r="U84">
-        <v>3478.9591066647199</v>
+        <v>3.4789591066647199</v>
       </c>
       <c r="V84">
-        <v>5281.9882258064499</v>
+        <v>5.2819882258064501</v>
       </c>
       <c r="W84">
-        <v>1736.10557356448</v>
+        <v>1.7361055735644799</v>
       </c>
       <c r="X84">
-        <v>6024.1280443548303</v>
+        <v>6.02412804435484</v>
       </c>
       <c r="Y84">
-        <v>1980.03513574166</v>
+        <v>1.9800351357416599</v>
       </c>
       <c r="Z84" s="4"/>
       <c r="AA84" s="4"/>
@@ -10802,76 +10802,76 @@
         <v>0.85416666666666696</v>
       </c>
       <c r="B85">
-        <v>16149.3495114422</v>
+        <v>16.1493495114422</v>
       </c>
       <c r="C85">
-        <v>5308.0344933891001</v>
+        <v>5.3080344933891004</v>
       </c>
       <c r="D85">
-        <v>24326.585272686101</v>
+        <v>24.326585272686099</v>
       </c>
       <c r="E85">
-        <v>7995.7619124101502</v>
+        <v>7.99576191241015</v>
       </c>
       <c r="F85">
-        <v>3902.4093510811899</v>
+        <v>3.9024093510811899</v>
       </c>
       <c r="G85">
-        <v>1282.65992560175</v>
+        <v>1.2826599256017499</v>
       </c>
       <c r="H85">
-        <v>10788.2965931863</v>
+        <v>10.788296593186301</v>
       </c>
       <c r="I85">
-        <v>3545.9416121356398</v>
+        <v>3.54594161213564</v>
       </c>
       <c r="J85">
-        <v>4800.5130260521</v>
+        <v>4.8005130260520996</v>
       </c>
       <c r="K85">
-        <v>1577.8523283674101</v>
+        <v>1.57785232836741</v>
       </c>
       <c r="L85">
-        <v>17268.312625250499</v>
+        <v>17.268312625250498</v>
       </c>
       <c r="M85">
-        <v>5675.8198831793197</v>
+        <v>5.6758198831793196</v>
       </c>
       <c r="N85">
-        <v>24304.795190380701</v>
+        <v>24.304795190380698</v>
       </c>
       <c r="O85">
-        <v>7988.5998587058302</v>
+        <v>7.9885998587058298</v>
       </c>
       <c r="P85">
-        <v>14291.7301269205</v>
+        <v>14.2917301269205</v>
       </c>
       <c r="Q85">
-        <v>4697.4645282246602</v>
+        <v>4.6974645282246597</v>
       </c>
       <c r="R85">
-        <v>1805.6648709677399</v>
+        <v>1.8056648709677401</v>
       </c>
       <c r="S85">
-        <v>593.49334236693903</v>
+        <v>0.59349334236693896</v>
       </c>
       <c r="T85">
-        <v>9854.6468937875707</v>
+        <v>9.8546468937875709</v>
       </c>
       <c r="U85">
-        <v>3239.0657961382299</v>
+        <v>3.2390657961382301</v>
       </c>
       <c r="V85">
-        <v>4409.3240322580596</v>
+        <v>4.40932403225806</v>
       </c>
       <c r="W85">
-        <v>1449.27472398639</v>
+        <v>1.4492747239863899</v>
       </c>
       <c r="X85">
-        <v>5028.8511491935396</v>
+        <v>5.0288511491935397</v>
       </c>
       <c r="Y85">
-        <v>1652.9034400503699</v>
+        <v>1.6529034400503699</v>
       </c>
       <c r="Z85" s="4"/>
       <c r="AA85" s="4"/>
@@ -10926,76 +10926,76 @@
         <v>0.86458333333333304</v>
       </c>
       <c r="B86">
-        <v>14972.755289676101</v>
+        <v>14.972755289676099</v>
       </c>
       <c r="C86">
-        <v>4921.3066744492799</v>
+        <v>4.9213066744492799</v>
       </c>
       <c r="D86">
-        <v>22979.575044096298</v>
+        <v>22.9795750440963</v>
       </c>
       <c r="E86">
-        <v>7553.0210607593499</v>
+        <v>7.5530210607593498</v>
       </c>
       <c r="F86">
-        <v>3365.6930667787101</v>
+        <v>3.3656930667787099</v>
       </c>
       <c r="G86">
-        <v>1106.2498139608599</v>
+        <v>1.1062498139608601</v>
       </c>
       <c r="H86">
-        <v>10073.5719438877</v>
+        <v>10.0735719438877</v>
       </c>
       <c r="I86">
-        <v>3311.0229803316502</v>
+        <v>3.31102298033165</v>
       </c>
       <c r="J86">
-        <v>4482.4790380761497</v>
+        <v>4.4824790380761499</v>
       </c>
       <c r="K86">
-        <v>1473.31961161307</v>
+        <v>1.47331961161307</v>
       </c>
       <c r="L86">
-        <v>16124.2869138276</v>
+        <v>16.1242869138276</v>
       </c>
       <c r="M86">
-        <v>5299.7968159186903</v>
+        <v>5.2997968159186897</v>
       </c>
       <c r="N86">
-        <v>22694.602509018001</v>
+        <v>22.694602509018001</v>
       </c>
       <c r="O86">
-        <v>7459.35511806657</v>
+        <v>7.4593551180665703</v>
       </c>
       <c r="P86">
-        <v>13344.903006012</v>
+        <v>13.344903006012</v>
       </c>
       <c r="Q86">
-        <v>4386.25750322978</v>
+        <v>4.3862575032297801</v>
       </c>
       <c r="R86">
-        <v>1507.09935483871</v>
+        <v>1.5070993548387099</v>
       </c>
       <c r="S86">
-        <v>495.35960286080302</v>
+        <v>0.49535960286080299</v>
       </c>
       <c r="T86">
-        <v>9201.7765370741399</v>
+        <v>9.2017765370741404</v>
       </c>
       <c r="U86">
-        <v>3024.4776871440699</v>
+        <v>3.0244776871440702</v>
       </c>
       <c r="V86">
-        <v>3680.2451612903201</v>
+        <v>3.68024516129032</v>
       </c>
       <c r="W86">
-        <v>1209.6380876775499</v>
+        <v>1.2096380876775501</v>
       </c>
       <c r="X86">
-        <v>4197.33387096774</v>
+        <v>4.1973338709677401</v>
       </c>
       <c r="Y86">
-        <v>1379.59692751596</v>
+        <v>1.3795969275159601</v>
       </c>
       <c r="Z86" s="4"/>
       <c r="AA86" s="4"/>
@@ -11050,76 +11050,76 @@
         <v>0.875</v>
       </c>
       <c r="B87">
-        <v>14117.7456224384</v>
+        <v>14.117745622438401</v>
       </c>
       <c r="C87">
-        <v>4640.2785870539801</v>
+        <v>4.64027858705398</v>
       </c>
       <c r="D87">
-        <v>21916.412729010299</v>
+        <v>21.9164127290103</v>
       </c>
       <c r="E87">
-        <v>7203.5765065654195</v>
+        <v>7.2035765065654198</v>
       </c>
       <c r="F87">
-        <v>2986.9338577558301</v>
+        <v>2.98693385775583</v>
       </c>
       <c r="G87">
-        <v>981.75768226492596</v>
+        <v>0.98175768226492599</v>
       </c>
       <c r="H87">
-        <v>9551.0138276553098</v>
+        <v>9.5510138276553107</v>
       </c>
       <c r="I87">
-        <v>3139.2664334938299</v>
+        <v>3.1392664334938298</v>
       </c>
       <c r="J87">
-        <v>4249.9541883767497</v>
+        <v>4.2499541883767504</v>
       </c>
       <c r="K87">
-        <v>1396.8923894577699</v>
+        <v>1.3968923894577701</v>
       </c>
       <c r="L87">
-        <v>15287.853021041999</v>
+        <v>15.287853021042</v>
       </c>
       <c r="M87">
-        <v>5024.8742903271896</v>
+        <v>5.0248742903271904</v>
       </c>
       <c r="N87">
-        <v>21517.338991983899</v>
+        <v>21.517338991983902</v>
       </c>
       <c r="O87">
-        <v>7072.4073124105098</v>
+        <v>7.07240731241051</v>
       </c>
       <c r="P87">
-        <v>12652.6473279893</v>
+        <v>12.6526473279893</v>
       </c>
       <c r="Q87">
-        <v>4158.7240651438997</v>
+        <v>4.1587240651439004</v>
       </c>
       <c r="R87">
-        <v>1297.5897096774099</v>
+        <v>1.2975897096774101</v>
       </c>
       <c r="S87">
-        <v>426.49711261462301</v>
+        <v>0.42649711261462298</v>
       </c>
       <c r="T87">
-        <v>8724.4420781563094</v>
+        <v>8.7244420781563097</v>
       </c>
       <c r="U87">
-        <v>2867.58543764362</v>
+        <v>2.8675854376436201</v>
       </c>
       <c r="V87">
-        <v>3168.6353225806401</v>
+        <v>3.1686353225806401</v>
       </c>
       <c r="W87">
-        <v>1041.48006564055</v>
+        <v>1.0414800656405501</v>
       </c>
       <c r="X87">
-        <v>3613.8408669354799</v>
+        <v>3.61384086693548</v>
       </c>
       <c r="Y87">
-        <v>1187.81205160749</v>
+        <v>1.1878120516074899</v>
       </c>
       <c r="Z87" s="4"/>
       <c r="AA87" s="4"/>
@@ -11174,76 +11174,76 @@
         <v>0.88541666666666696</v>
       </c>
       <c r="B88">
-        <v>13529.0487882216</v>
+        <v>13.5290487882216</v>
       </c>
       <c r="C88">
-        <v>4446.7832948777996</v>
+        <v>4.4467832948778003</v>
       </c>
       <c r="D88">
-        <v>21080.2864556358</v>
+        <v>21.0802864556358</v>
       </c>
       <c r="E88">
-        <v>6928.7550905847602</v>
+        <v>6.9287550905847599</v>
       </c>
       <c r="F88">
-        <v>2741.4093621921202</v>
+        <v>2.7414093621921198</v>
       </c>
       <c r="G88">
-        <v>901.05768314107695</v>
+        <v>0.90105768314107604</v>
       </c>
       <c r="H88">
-        <v>9186.9088176352707</v>
+        <v>9.1869088176352705</v>
       </c>
       <c r="I88">
-        <v>3019.5909040842498</v>
+        <v>3.0195909040842501</v>
       </c>
       <c r="J88">
-        <v>4087.9368737474902</v>
+        <v>4.0879368737474904</v>
       </c>
       <c r="K88">
-        <v>1343.6398733753699</v>
+        <v>1.3436398733753701</v>
       </c>
       <c r="L88">
-        <v>14705.0474699398</v>
+        <v>14.705047469939799</v>
       </c>
       <c r="M88">
-        <v>4833.3153692698897</v>
+        <v>4.83331536926989</v>
       </c>
       <c r="N88">
-        <v>20697.0521543086</v>
+        <v>20.697052154308601</v>
       </c>
       <c r="O88">
-        <v>6802.7920671791799</v>
+        <v>6.8027920671791797</v>
       </c>
       <c r="P88">
-        <v>12170.3014362057</v>
+        <v>12.170301436205699</v>
       </c>
       <c r="Q88">
-        <v>4000.1846373163098</v>
+        <v>4.0001846373163099</v>
       </c>
       <c r="R88">
-        <v>1163.4350322580599</v>
+        <v>1.16343503225806</v>
       </c>
       <c r="S88">
-        <v>382.402602511483</v>
+        <v>0.382402602511483</v>
       </c>
       <c r="T88">
-        <v>8391.8477454909807</v>
+        <v>8.3918477454909794</v>
       </c>
       <c r="U88">
-        <v>2758.2669670239602</v>
+        <v>2.7582669670239599</v>
       </c>
       <c r="V88">
-        <v>2841.03774193548</v>
+        <v>2.8410377419354802</v>
       </c>
       <c r="W88">
-        <v>933.80394798744203</v>
+        <v>0.93380394798744204</v>
       </c>
       <c r="X88">
-        <v>3240.21455645161</v>
+        <v>3.2402145564516101</v>
       </c>
       <c r="Y88">
-        <v>1065.00702207482</v>
+        <v>1.06500702207482</v>
       </c>
       <c r="Z88" s="4"/>
       <c r="AA88" s="4"/>
@@ -11298,76 +11298,76 @@
         <v>0.89583333333333304</v>
       </c>
       <c r="B89">
-        <v>13113.655989495101</v>
+        <v>13.113655989495101</v>
       </c>
       <c r="C89">
-        <v>4310.2502845306399</v>
+        <v>4.3102502845306399</v>
       </c>
       <c r="D89">
-        <v>20374.380334608501</v>
+        <v>20.3743803346085</v>
       </c>
       <c r="E89">
-        <v>6696.7349688546301</v>
+        <v>6.6967349688546296</v>
       </c>
       <c r="F89">
-        <v>2589.57650854127</v>
+        <v>2.5895765085412701</v>
       </c>
       <c r="G89">
-        <v>851.15263750209397</v>
+        <v>0.85115263750209302</v>
       </c>
       <c r="H89">
-        <v>8923.9440881763494</v>
+        <v>8.9239440881763503</v>
       </c>
       <c r="I89">
-        <v>2933.15857728845</v>
+        <v>2.9331585772884501</v>
       </c>
       <c r="J89">
-        <v>3970.9243687374701</v>
+        <v>3.97092436873747</v>
       </c>
       <c r="K89">
-        <v>1305.1797228714099</v>
+        <v>1.3051797228714099</v>
       </c>
       <c r="L89">
-        <v>14284.132349699301</v>
+        <v>14.2841323496993</v>
       </c>
       <c r="M89">
-        <v>4694.9672596173896</v>
+        <v>4.6949672596173899</v>
       </c>
       <c r="N89">
-        <v>20104.622771543</v>
+        <v>20.104622771542999</v>
       </c>
       <c r="O89">
-        <v>6608.0699456232296</v>
+        <v>6.6080699456232299</v>
       </c>
       <c r="P89">
-        <v>11821.940514362001</v>
+        <v>11.821940514362</v>
       </c>
       <c r="Q89">
-        <v>3885.6839394408398</v>
+        <v>3.88568393944084</v>
       </c>
       <c r="R89">
-        <v>1082.9422258064501</v>
+        <v>1.0829422258064501</v>
       </c>
       <c r="S89">
-        <v>355.94589644959899</v>
+        <v>0.35594589644959901</v>
       </c>
       <c r="T89">
-        <v>8151.6407274549101</v>
+        <v>8.1516407274549092</v>
       </c>
       <c r="U89">
-        <v>2679.3147382430898</v>
+        <v>2.67931473824309</v>
       </c>
       <c r="V89">
-        <v>2644.47919354838</v>
+        <v>2.64447919354838</v>
       </c>
       <c r="W89">
-        <v>869.19827739557297</v>
+        <v>0.86919827739557298</v>
       </c>
       <c r="X89">
-        <v>3016.0387701612899</v>
+        <v>3.0160387701612899</v>
       </c>
       <c r="Y89">
-        <v>991.32400435522197</v>
+        <v>0.99132400435522205</v>
       </c>
       <c r="Z89" s="4"/>
       <c r="AA89" s="4"/>
@@ -11422,76 +11422,76 @@
         <v>0.90625</v>
       </c>
       <c r="B90">
-        <v>12768.7976166849</v>
+        <v>12.7687976166849</v>
       </c>
       <c r="C90">
-        <v>4196.9008188501002</v>
+        <v>4.1969008188501</v>
       </c>
       <c r="D90">
-        <v>19694.9219316667</v>
+        <v>19.694921931666698</v>
       </c>
       <c r="E90">
-        <v>6473.4077916774504</v>
+        <v>6.4734077916774497</v>
       </c>
       <c r="F90">
-        <v>2490.3201762799699</v>
+        <v>2.4903201762799698</v>
       </c>
       <c r="G90">
-        <v>818.52865874945303</v>
+        <v>0.81852865874945302</v>
       </c>
       <c r="H90">
-        <v>8698.0641282565102</v>
+        <v>8.6980641282565099</v>
       </c>
       <c r="I90">
-        <v>2858.9154247843599</v>
+        <v>2.8589154247843598</v>
       </c>
       <c r="J90">
-        <v>3870.4136272545002</v>
+        <v>3.8704136272545</v>
       </c>
       <c r="K90">
-        <v>1272.1434397462201</v>
+        <v>1.2721434397462199</v>
       </c>
       <c r="L90">
-        <v>13922.5770541082</v>
+        <v>13.922577054108199</v>
       </c>
       <c r="M90">
-        <v>4576.1297808133304</v>
+        <v>4.5761297808133303</v>
       </c>
       <c r="N90">
-        <v>19595.741122244399</v>
+        <v>19.595741122244402</v>
       </c>
       <c r="O90">
-        <v>6440.8086360815796</v>
+        <v>6.4408086360815799</v>
       </c>
       <c r="P90">
-        <v>11522.7074148296</v>
+        <v>11.5227074148296</v>
       </c>
       <c r="Q90">
-        <v>3787.3307758811302</v>
+        <v>3.7873307758811299</v>
       </c>
       <c r="R90">
-        <v>1033.8473225806399</v>
+        <v>1.0338473225806399</v>
       </c>
       <c r="S90">
-        <v>339.80918211398199</v>
+        <v>0.33980918211398198</v>
       </c>
       <c r="T90">
-        <v>7945.3090581162296</v>
+        <v>7.94530905811623</v>
       </c>
       <c r="U90">
-        <v>2611.4967981364498</v>
+        <v>2.6114967981364501</v>
       </c>
       <c r="V90">
-        <v>2524.5924193548299</v>
+        <v>2.5245924193548301</v>
       </c>
       <c r="W90">
-        <v>829.79340029698596</v>
+        <v>0.82979340029698601</v>
       </c>
       <c r="X90">
-        <v>2879.3074395161202</v>
+        <v>2.8793074395161198</v>
       </c>
       <c r="Y90">
-        <v>946.38258929220206</v>
+        <v>0.94638258929220198</v>
       </c>
       <c r="Z90" s="4"/>
       <c r="AA90" s="4"/>
@@ -11546,76 +11546,76 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B91">
-        <v>12412.246893981501</v>
+        <v>12.4122468939815</v>
       </c>
       <c r="C91">
-        <v>4079.7082636074301</v>
+        <v>4.0797082636074302</v>
       </c>
       <c r="D91">
-        <v>18960.229048878002</v>
+        <v>18.960229048877999</v>
       </c>
       <c r="E91">
-        <v>6231.9259189167497</v>
+        <v>6.2319259189167502</v>
       </c>
       <c r="F91">
-        <v>2408.3317823550301</v>
+        <v>2.4083317823550301</v>
       </c>
       <c r="G91">
-        <v>791.58037685718</v>
+        <v>0.79158037685717997</v>
       </c>
       <c r="H91">
-        <v>8458.6987975951906</v>
+        <v>8.4586987975951899</v>
       </c>
       <c r="I91">
-        <v>2780.2398452651</v>
+        <v>2.7802398452651</v>
       </c>
       <c r="J91">
-        <v>3763.9022444889702</v>
+        <v>3.7639022444889698</v>
       </c>
       <c r="K91">
-        <v>1237.1348412105699</v>
+        <v>1.23713484121057</v>
       </c>
       <c r="L91">
-        <v>13539.436367735399</v>
+        <v>13.5394363677354</v>
       </c>
       <c r="M91">
-        <v>4450.1975271552901</v>
+        <v>4.4501975271552903</v>
       </c>
       <c r="N91">
-        <v>19056.478478957899</v>
+        <v>19.056478478957899</v>
       </c>
       <c r="O91">
-        <v>6263.56157671654</v>
+        <v>6.2635615767165396</v>
       </c>
       <c r="P91">
-        <v>11205.609652638601</v>
+        <v>11.2056096526386</v>
       </c>
       <c r="Q91">
-        <v>3683.1057816611501</v>
+        <v>3.6831057816611499</v>
       </c>
       <c r="R91">
-        <v>996.74070967741898</v>
+        <v>0.99674070967741901</v>
       </c>
       <c r="S91">
-        <v>327.61282825566701</v>
+        <v>0.32761282825566701</v>
       </c>
       <c r="T91">
-        <v>7726.6590801603197</v>
+        <v>7.7266590801603199</v>
       </c>
       <c r="U91">
-        <v>2539.6300257846301</v>
+        <v>2.5396300257846298</v>
       </c>
       <c r="V91">
-        <v>2433.9803225806399</v>
+        <v>2.43398032258064</v>
       </c>
       <c r="W91">
-        <v>800.01064435037995</v>
+        <v>0.80001064435037905</v>
       </c>
       <c r="X91">
-        <v>2775.96399193548</v>
+        <v>2.7759639919354799</v>
       </c>
       <c r="Y91">
-        <v>912.41524069805905</v>
+        <v>0.91241524069805902</v>
       </c>
       <c r="Z91" s="4"/>
       <c r="AA91" s="4"/>
@@ -11670,76 +11670,76 @@
         <v>0.92708333333333304</v>
       </c>
       <c r="B92">
-        <v>12006.9475518133</v>
+        <v>12.006947551813299</v>
       </c>
       <c r="C92">
-        <v>3946.4928119972901</v>
+        <v>3.94649281199729</v>
       </c>
       <c r="D92">
-        <v>18146.8697904293</v>
+        <v>18.146869790429299</v>
       </c>
       <c r="E92">
-        <v>5964.5876588645997</v>
+        <v>5.9645876588646001</v>
       </c>
       <c r="F92">
-        <v>2330.5655767179501</v>
+        <v>2.3305655767179498</v>
       </c>
       <c r="G92">
-        <v>766.01986114420095</v>
+        <v>0.76601986114420095</v>
       </c>
       <c r="H92">
-        <v>8182.2486973947798</v>
+        <v>8.1822486973947797</v>
       </c>
       <c r="I92">
-        <v>2689.3750914541201</v>
+        <v>2.6893750914541199</v>
       </c>
       <c r="J92">
-        <v>3640.88909819639</v>
+        <v>3.6408890981963902</v>
       </c>
       <c r="K92">
-        <v>1196.70237529615</v>
+        <v>1.1967023752961501</v>
       </c>
       <c r="L92">
-        <v>13096.9358567134</v>
+        <v>13.096935856713401</v>
       </c>
       <c r="M92">
-        <v>4304.7546426488198</v>
+        <v>4.3047546426488097</v>
       </c>
       <c r="N92">
-        <v>18433.668102204399</v>
+        <v>18.4336681022044</v>
       </c>
       <c r="O92">
-        <v>6058.8537053372002</v>
+        <v>6.0588537053372002</v>
       </c>
       <c r="P92">
-        <v>10839.3840681362</v>
+        <v>10.8393840681362</v>
       </c>
       <c r="Q92">
-        <v>3562.7332531253901</v>
+        <v>3.5627332531253901</v>
       </c>
       <c r="R92">
-        <v>964.77193548387095</v>
+        <v>0.96477193548387097</v>
       </c>
       <c r="S92">
-        <v>317.10520031619598</v>
+        <v>0.31710520031619599</v>
       </c>
       <c r="T92">
-        <v>7474.1337535070097</v>
+        <v>7.4741337535070098</v>
       </c>
       <c r="U92">
-        <v>2456.62896475859</v>
+        <v>2.4566289647585902</v>
       </c>
       <c r="V92">
-        <v>2355.9145161290298</v>
+        <v>2.35591451612903</v>
       </c>
       <c r="W92">
-        <v>774.35165461176496</v>
+        <v>0.77435165461176503</v>
       </c>
       <c r="X92">
-        <v>2686.92963709677</v>
+        <v>2.6869296370967701</v>
       </c>
       <c r="Y92">
-        <v>883.15106344772005</v>
+        <v>0.88315106344771999</v>
       </c>
       <c r="Z92" s="4"/>
       <c r="AA92" s="4"/>
@@ -11794,76 +11794,76 @@
         <v>0.9375</v>
       </c>
       <c r="B93">
-        <v>11540.7559555562</v>
+        <v>11.5407559555562</v>
       </c>
       <c r="C93">
-        <v>3793.2630443396401</v>
+        <v>3.79326304433964</v>
       </c>
       <c r="D93">
-        <v>17259.9634155313</v>
+        <v>17.259963415531299</v>
       </c>
       <c r="E93">
-        <v>5673.0756306538196</v>
+        <v>5.6730756306538197</v>
       </c>
       <c r="F93">
-        <v>2249.2371515207801</v>
+        <v>2.2492371515207799</v>
       </c>
       <c r="G93">
-        <v>739.28850048266304</v>
+        <v>0.73928850048266304</v>
       </c>
       <c r="H93">
-        <v>7861.9711422845603</v>
+        <v>7.8619711422845597</v>
       </c>
       <c r="I93">
-        <v>2584.1049498438401</v>
+        <v>2.58410494984384</v>
       </c>
       <c r="J93">
-        <v>3498.37386773547</v>
+        <v>3.4983738677354701</v>
       </c>
       <c r="K93">
-        <v>1149.8598842977501</v>
+        <v>1.1498598842977501</v>
       </c>
       <c r="L93">
-        <v>12584.2828256513</v>
+        <v>12.5842828256513</v>
       </c>
       <c r="M93">
-        <v>4136.2537398669301</v>
+        <v>4.1362537398669303</v>
       </c>
       <c r="N93">
-        <v>17712.1194949899</v>
+        <v>17.712119494989899</v>
       </c>
       <c r="O93">
-        <v>5821.6921470318803</v>
+        <v>5.8216921470318796</v>
       </c>
       <c r="P93">
-        <v>10415.0983299933</v>
+        <v>10.415098329993301</v>
       </c>
       <c r="Q93">
-        <v>3423.2772749437199</v>
+        <v>3.4232772749437199</v>
       </c>
       <c r="R93">
-        <v>933.37403225806395</v>
+        <v>0.93337403225806403</v>
       </c>
       <c r="S93">
-        <v>306.78520858992903</v>
+        <v>0.30678520858992903</v>
       </c>
       <c r="T93">
-        <v>7181.5739238476899</v>
+        <v>7.1815739238476901</v>
       </c>
       <c r="U93">
-        <v>2360.4691989357302</v>
+        <v>2.3604691989357298</v>
       </c>
       <c r="V93">
-        <v>2279.2427419354799</v>
+        <v>2.2792427419354802</v>
       </c>
       <c r="W93">
-        <v>749.150861118482</v>
+        <v>0.74915086111848295</v>
       </c>
       <c r="X93">
-        <v>2599.4851814516101</v>
+        <v>2.5994851814516098</v>
       </c>
       <c r="Y93">
-        <v>854.40946079113803</v>
+        <v>0.854409460791138</v>
       </c>
       <c r="Z93" s="4"/>
       <c r="AA93" s="4"/>
@@ -11918,76 +11918,76 @@
         <v>0.94791666666666696</v>
       </c>
       <c r="B94">
-        <v>11002.890083489499</v>
+        <v>11.0028900834895</v>
       </c>
       <c r="C94">
-        <v>3616.4750814731501</v>
+        <v>3.6164750814731499</v>
       </c>
       <c r="D94">
-        <v>16306.8410374379</v>
+        <v>16.306841037437898</v>
       </c>
       <c r="E94">
-        <v>5359.7994546842501</v>
+        <v>5.35979945468425</v>
       </c>
       <c r="F94">
-        <v>2160.1120182704099</v>
+        <v>2.1601120182704099</v>
       </c>
       <c r="G94">
-        <v>709.99448581131799</v>
+        <v>0.70999448581131797</v>
       </c>
       <c r="H94">
-        <v>7491.1234468937801</v>
+        <v>7.4911234468937797</v>
       </c>
       <c r="I94">
-        <v>2462.21320692668</v>
+        <v>2.46221320692668</v>
       </c>
       <c r="J94">
-        <v>3333.3562324649201</v>
+        <v>3.33335623246492</v>
       </c>
       <c r="K94">
-        <v>1095.6212105101199</v>
+        <v>1.09562121051012</v>
       </c>
       <c r="L94">
-        <v>11990.6845791583</v>
+        <v>11.9906845791583</v>
       </c>
       <c r="M94">
-        <v>3941.1474313826402</v>
+        <v>3.9411474313826398</v>
       </c>
       <c r="N94">
-        <v>16876.6421603206</v>
+        <v>16.8766421603206</v>
       </c>
       <c r="O94">
-        <v>5547.0840268888596</v>
+        <v>5.5470840268888599</v>
       </c>
       <c r="P94">
-        <v>9923.8201068804192</v>
+        <v>9.9238201068804202</v>
       </c>
       <c r="Q94">
-        <v>3261.8019317859998</v>
+        <v>3.2618019317860001</v>
       </c>
       <c r="R94">
-        <v>900.26351612903204</v>
+        <v>0.90026351612903199</v>
       </c>
       <c r="S94">
-        <v>295.902308224048</v>
+        <v>0.29590230822404801</v>
       </c>
       <c r="T94">
-        <v>6842.8204368737397</v>
+        <v>6.8428204368737404</v>
       </c>
       <c r="U94">
-        <v>2249.1263121934799</v>
+        <v>2.2491263121934799</v>
       </c>
       <c r="V94">
-        <v>2198.3888709677399</v>
+        <v>2.1983888709677402</v>
       </c>
       <c r="W94">
-        <v>722.57547888920305</v>
+        <v>0.72257547888920304</v>
       </c>
       <c r="X94">
-        <v>2507.2710282257999</v>
+        <v>2.5072710282258002</v>
       </c>
       <c r="Y94">
-        <v>824.10013435328699</v>
+        <v>0.82410013435328699</v>
       </c>
       <c r="Z94" s="4"/>
       <c r="AA94" s="4"/>
@@ -12042,76 +12042,76 @@
         <v>0.95833333333333304</v>
       </c>
       <c r="B95">
-        <v>10386.937715075301</v>
+        <v>10.3869377150753</v>
       </c>
       <c r="C95">
-        <v>3414.0213284281099</v>
+        <v>3.41402132842811</v>
       </c>
       <c r="D95">
-        <v>15296.5079321921</v>
+        <v>15.2965079321921</v>
       </c>
       <c r="E95">
-        <v>5027.7190220539696</v>
+        <v>5.0277190220539696</v>
       </c>
       <c r="F95">
-        <v>2058.41049320415</v>
+        <v>2.0584104932041498</v>
       </c>
       <c r="G95">
-        <v>676.56681104958795</v>
+        <v>0.67656681104958805</v>
       </c>
       <c r="H95">
-        <v>7066.3342685370699</v>
+        <v>7.0663342685370703</v>
       </c>
       <c r="I95">
-        <v>2322.5917559488398</v>
+        <v>2.32259175594884</v>
       </c>
       <c r="J95">
-        <v>3144.33603206412</v>
+        <v>3.1443360320641198</v>
       </c>
       <c r="K95">
-        <v>1033.4932750806499</v>
+        <v>1.03349327508065</v>
       </c>
       <c r="L95">
-        <v>11310.744769539</v>
+        <v>11.310744769538999</v>
       </c>
       <c r="M95">
-        <v>3717.66202348245</v>
+        <v>3.71766202348245</v>
       </c>
       <c r="N95">
-        <v>15919.640849699401</v>
+        <v>15.9196408496994</v>
       </c>
       <c r="O95">
-        <v>5232.5329074523197</v>
+        <v>5.2325329074523204</v>
       </c>
       <c r="P95">
-        <v>9361.0832331329293</v>
+        <v>9.3610832331329306</v>
       </c>
       <c r="Q95">
-        <v>3076.8392659871502</v>
+        <v>3.0768392659871502</v>
       </c>
       <c r="R95">
-        <v>862.58603225806405</v>
+        <v>0.86258603225806396</v>
       </c>
       <c r="S95">
-        <v>283.518318152527</v>
+        <v>0.28351831815252798</v>
       </c>
       <c r="T95">
-        <v>6454.7937154308602</v>
+        <v>6.4547937154308599</v>
       </c>
       <c r="U95">
-        <v>2121.5880964705402</v>
+        <v>2.12158809647054</v>
       </c>
       <c r="V95">
-        <v>2106.3827419354802</v>
+        <v>2.1063827419354801</v>
       </c>
       <c r="W95">
-        <v>692.33452669726398</v>
+        <v>0.69233452669726403</v>
       </c>
       <c r="X95">
-        <v>2402.33768145161</v>
+        <v>2.40233768145161</v>
       </c>
       <c r="Y95">
-        <v>789.61021116538802</v>
+        <v>0.78961021116538799</v>
       </c>
       <c r="Z95" s="4"/>
       <c r="AA95" s="4"/>
@@ -12166,76 +12166,76 @@
         <v>0.96875</v>
       </c>
       <c r="B96">
-        <v>9713.1012808520209</v>
+        <v>9.7131012808520207</v>
       </c>
       <c r="C96">
-        <v>3192.5420030085102</v>
+        <v>3.1925420030085099</v>
       </c>
       <c r="D96">
-        <v>14251.9424344541</v>
+        <v>14.251942434454101</v>
       </c>
       <c r="E96">
-        <v>4684.3869461292197</v>
+        <v>4.6843869461292202</v>
       </c>
       <c r="F96">
-        <v>1949.0516339533899</v>
+        <v>1.9490516339533901</v>
       </c>
       <c r="G96">
-        <v>640.62229225337103</v>
+        <v>0.64062229225337097</v>
       </c>
       <c r="H96">
-        <v>6601.0889779559102</v>
+        <v>6.6010889779559099</v>
       </c>
       <c r="I96">
-        <v>2169.6730239254898</v>
+        <v>2.16967302392549</v>
       </c>
       <c r="J96">
-        <v>2937.31390781563</v>
+        <v>2.9373139078156298</v>
       </c>
       <c r="K96">
-        <v>965.44839341981003</v>
+        <v>0.96544839341981004</v>
       </c>
       <c r="L96">
-        <v>10566.048787575101</v>
+        <v>10.566048787575101</v>
       </c>
       <c r="M96">
-        <v>3472.8922910203501</v>
+        <v>3.4728922910203499</v>
       </c>
       <c r="N96">
-        <v>14871.4965571142</v>
+        <v>14.871496557114201</v>
       </c>
       <c r="O96">
-        <v>4888.0245385456301</v>
+        <v>4.88802453854563</v>
       </c>
       <c r="P96">
-        <v>8744.7523714094805</v>
+        <v>8.7447523714094793</v>
       </c>
       <c r="Q96">
-        <v>2874.26110820746</v>
+        <v>2.8742611082074601</v>
       </c>
       <c r="R96">
-        <v>822.62506451612899</v>
+        <v>0.82262506451612905</v>
       </c>
       <c r="S96">
-        <v>270.38378322818801</v>
+        <v>0.27038378322818801</v>
       </c>
       <c r="T96">
-        <v>6029.8120681362698</v>
+        <v>6.0298120681362697</v>
       </c>
       <c r="U96">
-        <v>1981.9033840120801</v>
+        <v>1.9819033840120801</v>
       </c>
       <c r="V96">
-        <v>2008.8004838709601</v>
+        <v>2.0088004838709601</v>
       </c>
       <c r="W96">
-        <v>660.26078952399598</v>
+        <v>0.66026078952399603</v>
       </c>
       <c r="X96">
-        <v>2291.0447379032198</v>
+        <v>2.2910447379032202</v>
       </c>
       <c r="Y96">
-        <v>753.02998960246396</v>
+        <v>0.75302998960246403</v>
       </c>
       <c r="Z96" s="4"/>
       <c r="AA96" s="4"/>
@@ -12290,76 +12290,76 @@
         <v>0.97916666666666696</v>
       </c>
       <c r="B97">
-        <v>9016.7350342620703</v>
+        <v>9.0167350342620693</v>
       </c>
       <c r="C97">
-        <v>2963.6574863713299</v>
+        <v>2.9636574863713299</v>
       </c>
       <c r="D97">
-        <v>13209.540342475701</v>
+        <v>13.2095403424757</v>
       </c>
       <c r="E97">
-        <v>4341.7659472907299</v>
+        <v>4.34176594729073</v>
       </c>
       <c r="F97">
-        <v>1840.6437913730599</v>
+        <v>1.84064379137306</v>
       </c>
       <c r="G97">
-        <v>604.99035752048701</v>
+        <v>0.60499035752048702</v>
       </c>
       <c r="H97">
-        <v>6118.98697394789</v>
+        <v>6.1189869739478899</v>
       </c>
       <c r="I97">
-        <v>2011.2137581331799</v>
+        <v>2.0112137581331799</v>
       </c>
       <c r="J97">
-        <v>2722.7909819639199</v>
+        <v>2.7227909819639202</v>
       </c>
       <c r="K97">
-        <v>894.93811749589099</v>
+        <v>0.89493811749589103</v>
       </c>
       <c r="L97">
-        <v>9794.3710671342596</v>
+        <v>9.7943710671342696</v>
       </c>
       <c r="M97">
-        <v>3219.2540899907699</v>
+        <v>3.2192540899907698</v>
       </c>
       <c r="N97">
-        <v>13785.376022044</v>
+        <v>13.785376022044</v>
       </c>
       <c r="O97">
-        <v>4531.0339823597096</v>
+        <v>4.5310339823597099</v>
       </c>
       <c r="P97">
-        <v>8106.0906813627198</v>
+        <v>8.1060906813627192</v>
       </c>
       <c r="Q97">
-        <v>2664.3431621024201</v>
+        <v>2.6643431621024201</v>
       </c>
       <c r="R97">
-        <v>784.37670967741894</v>
+        <v>0.78437670967741902</v>
       </c>
       <c r="S97">
-        <v>257.81215694346298</v>
+        <v>0.25781215694346299</v>
       </c>
       <c r="T97">
-        <v>5589.4325350701401</v>
+        <v>5.5894325350701397</v>
       </c>
       <c r="U97">
-        <v>1837.15763124715</v>
+        <v>1.83715763124715</v>
       </c>
       <c r="V97">
-        <v>1915.40032258064</v>
+        <v>1.91540032258064</v>
       </c>
       <c r="W97">
-        <v>629.56164108672499</v>
+        <v>0.62956164108672497</v>
       </c>
       <c r="X97">
-        <v>2184.5214919354798</v>
+        <v>2.1845214919354801</v>
       </c>
       <c r="Y97">
-        <v>718.01749182080903</v>
+        <v>0.71801749182080898</v>
       </c>
       <c r="Z97" s="4"/>
       <c r="AA97" s="4"/>
@@ -12414,76 +12414,76 @@
         <v>0.98958333333333304</v>
       </c>
       <c r="B98">
-        <v>8329.50423401642</v>
+        <v>8.3295042340164205</v>
       </c>
       <c r="C98">
-        <v>2737.7756457412302</v>
+        <v>2.7377756457412299</v>
       </c>
       <c r="D98">
-        <v>12200.197243709101</v>
+        <v>12.2001972437091</v>
       </c>
       <c r="E98">
-        <v>4010.0109140541799</v>
+        <v>4.0100109140541802</v>
       </c>
       <c r="F98">
-        <v>1744.11547126511</v>
+        <v>1.7441154712651099</v>
       </c>
       <c r="G98">
-        <v>573.26303300138397</v>
+        <v>0.57326303300138404</v>
       </c>
       <c r="H98">
-        <v>5640.2563126252498</v>
+        <v>5.6402563126252501</v>
       </c>
       <c r="I98">
-        <v>1853.86259909466</v>
+        <v>1.85386259909466</v>
       </c>
       <c r="J98">
-        <v>2509.7682164328598</v>
+        <v>2.5097682164328599</v>
       </c>
       <c r="K98">
-        <v>824.92092042458705</v>
+        <v>0.82492092042458698</v>
       </c>
       <c r="L98">
-        <v>9028.0896943887692</v>
+        <v>9.0280896943887701</v>
       </c>
       <c r="M98">
-        <v>2967.3895826746898</v>
+        <v>2.9673895826746901</v>
       </c>
       <c r="N98">
-        <v>12706.8507354709</v>
+        <v>12.706850735470899</v>
       </c>
       <c r="O98">
-        <v>4176.5398636296404</v>
+        <v>4.1765398636296398</v>
       </c>
       <c r="P98">
-        <v>7471.8951569806204</v>
+        <v>7.4718951569806196</v>
       </c>
       <c r="Q98">
-        <v>2455.89317366245</v>
+        <v>2.4558931736624499</v>
       </c>
       <c r="R98">
-        <v>753.54967741935502</v>
+        <v>0.75354967741935497</v>
       </c>
       <c r="S98">
-        <v>247.679801430401</v>
+        <v>0.247679801430401</v>
       </c>
       <c r="T98">
-        <v>5152.1325791583104</v>
+        <v>5.1521325791583097</v>
       </c>
       <c r="U98">
-        <v>1693.4240865435099</v>
+        <v>1.69342408654351</v>
       </c>
       <c r="V98">
-        <v>1840.12258064516</v>
+        <v>1.84012258064516</v>
       </c>
       <c r="W98">
-        <v>604.81904383877497</v>
+        <v>0.60481904383877505</v>
       </c>
       <c r="X98">
-        <v>2098.66693548387</v>
+        <v>2.0986669354838701</v>
       </c>
       <c r="Y98">
-        <v>689.79846375798297</v>
+        <v>0.68979846375798304</v>
       </c>
     </row>
   </sheetData>
@@ -12498,6 +12498,14 @@
     <protectedRange sqref="T3:W97" name="Plage1_13"/>
   </protectedRanges>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12510,14 +12518,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12852,6 +12852,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12864,14 +12872,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
